--- a/research/traditional_assets/database/data/new_zealand/new_zealand_utility_general.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_utility_general.xlsx
@@ -650,10 +650,10 @@
         <v>0.0223574711215998</v>
       </c>
       <c r="X2">
-        <v>0.07318521864634953</v>
+        <v>0.07316761238559424</v>
       </c>
       <c r="Y2">
-        <v>-0.05082774752474972</v>
+        <v>-0.05081014126399444</v>
       </c>
       <c r="Z2">
         <v>0.2230853180971946</v>
@@ -662,10 +662,10 @@
         <v>0.03221095204468126</v>
       </c>
       <c r="AB2">
-        <v>0.06113096183189312</v>
+        <v>0.06111987025831817</v>
       </c>
       <c r="AC2">
-        <v>-0.02892000978721186</v>
+        <v>-0.02890891821363691</v>
       </c>
       <c r="AD2">
         <v>1282.9</v>
@@ -787,10 +787,10 @@
         <v>0.0223574711215998</v>
       </c>
       <c r="X3">
-        <v>0.07318521864634953</v>
+        <v>0.07316761238559424</v>
       </c>
       <c r="Y3">
-        <v>-0.05082774752474972</v>
+        <v>-0.05081014126399444</v>
       </c>
       <c r="Z3">
         <v>0.2230853180971946</v>
@@ -799,10 +799,10 @@
         <v>0.03221095204468126</v>
       </c>
       <c r="AB3">
-        <v>0.06113096183189312</v>
+        <v>0.06111987025831817</v>
       </c>
       <c r="AC3">
-        <v>-0.02892000978721186</v>
+        <v>-0.02890891821363691</v>
       </c>
       <c r="AD3">
         <v>1282.9</v>
@@ -1139,49 +1139,49 @@
         <v>2.75824175824176</v>
       </c>
       <c r="F2">
-        <v>4.53266734586492</v>
+        <v>4.58212901485079</v>
       </c>
       <c r="G2">
         <v>4.05595953208979</v>
       </c>
       <c r="H2">
-        <v>3.06920012646222</v>
+        <v>3.17881441669301</v>
       </c>
       <c r="I2">
         <v>0.370021055060425</v>
       </c>
       <c r="J2">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="K2">
         <v>2184.2</v>
       </c>
       <c r="L2">
-        <v>2237.55100807032</v>
+        <v>2329.28873203495</v>
       </c>
       <c r="M2">
         <v>3420</v>
       </c>
       <c r="N2">
-        <v>3161.23900807032</v>
+        <v>3287.64773203495</v>
       </c>
       <c r="O2">
         <v>1282.9</v>
       </c>
       <c r="P2">
-        <v>970.788</v>
+        <v>1005.459</v>
       </c>
       <c r="Q2">
-        <v>0.0611309618318931</v>
+        <v>0.0611198702583182</v>
       </c>
       <c r="R2">
-        <v>0.0623858669120624</v>
+        <v>0.0617366089538486</v>
       </c>
       <c r="S2">
         <v>0.040608</v>
       </c>
       <c r="T2">
-        <v>0.041688</v>
+        <v>0.039816</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0731852186463495</v>
+        <v>0.0731676123855942</v>
       </c>
       <c r="X2">
-        <v>0.0704350373778645</v>
+        <v>0.0706900971180966</v>
       </c>
       <c r="Y2">
         <v>0.6320464754178809</v>
       </c>
       <c r="Z2">
-        <v>0.568572730696184</v>
+        <v>0.574829032750499</v>
       </c>
       <c r="AA2">
         <v>1282.9</v>
@@ -1236,7 +1236,7 @@
         <v>2184.2</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04329999999999999</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.06504612295145662</v>
+        <v>0.06503374940558185</v>
       </c>
       <c r="C2">
-        <v>2771.383202249117</v>
+        <v>2771.163581084343</v>
       </c>
       <c r="D2">
-        <v>2724.283202249117</v>
+        <v>2724.063581084343</v>
       </c>
       <c r="E2">
         <v>-1282.9</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.06504612295145662</v>
+        <v>0.06503374940558185</v>
       </c>
       <c r="T2">
         <v>0.4441974458563937</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.28</v>
       </c>
       <c r="W2">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.06490647380719253</v>
+        <v>0.06488405490724621</v>
       </c>
       <c r="C3">
-        <v>2756.623977795263</v>
+        <v>2757.860017574477</v>
       </c>
       <c r="D3">
-        <v>2744.194977795263</v>
+        <v>2745.431017574477</v>
       </c>
       <c r="E3">
         <v>-1248.229</v>
@@ -1539,37 +1539,37 @@
         <v>254.775</v>
       </c>
       <c r="M3">
-        <v>1.7924907</v>
+        <v>1.7439513</v>
       </c>
       <c r="N3">
-        <v>252.9825093</v>
+        <v>253.0310487</v>
       </c>
       <c r="O3">
-        <v>70.83510260400001</v>
+        <v>70.84869363600001</v>
       </c>
       <c r="P3">
-        <v>182.147406696</v>
+        <v>182.182355064</v>
       </c>
       <c r="Q3">
-        <v>322.747406696</v>
+        <v>322.782355064</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.06518609475473994</v>
+        <v>0.06517363121944061</v>
       </c>
       <c r="T3">
         <v>0.4474279727353493</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.28</v>
       </c>
       <c r="W3">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>142.1346286482825</v>
+        <v>146.090662050024</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.06476682466292846</v>
+        <v>0.06473436040891058</v>
       </c>
       <c r="C4">
-        <v>2742.157966619348</v>
+        <v>2744.894314717626</v>
       </c>
       <c r="D4">
-        <v>2764.399966619348</v>
+        <v>2767.136314717627</v>
       </c>
       <c r="E4">
         <v>-1213.558</v>
@@ -1621,37 +1621,37 @@
         <v>254.775</v>
       </c>
       <c r="M4">
-        <v>3.5849814</v>
+        <v>3.4879026</v>
       </c>
       <c r="N4">
-        <v>251.1900186</v>
+        <v>251.2870974</v>
       </c>
       <c r="O4">
-        <v>70.33320520800001</v>
+        <v>70.36038727200001</v>
       </c>
       <c r="P4">
-        <v>180.856813392</v>
+        <v>180.926710128</v>
       </c>
       <c r="Q4">
-        <v>321.456813392</v>
+        <v>321.526710128</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.0653289231254372</v>
+        <v>0.06531636776419447</v>
       </c>
       <c r="T4">
         <v>0.4507244287342835</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.28</v>
       </c>
       <c r="W4">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>71.06731432414126</v>
+        <v>73.04533102501199</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.06462717551866438</v>
+        <v>0.06458466591057495</v>
       </c>
       <c r="C5">
-        <v>2727.991693383027</v>
+        <v>2732.274549721214</v>
       </c>
       <c r="D5">
-        <v>2784.904693383027</v>
+        <v>2789.187549721214</v>
       </c>
       <c r="E5">
         <v>-1178.887</v>
@@ -1703,37 +1703,37 @@
         <v>254.775</v>
       </c>
       <c r="M5">
-        <v>5.377472099999999</v>
+        <v>5.231853899999999</v>
       </c>
       <c r="N5">
-        <v>249.3975279</v>
+        <v>249.5431461</v>
       </c>
       <c r="O5">
-        <v>69.83130781200001</v>
+        <v>69.872080908</v>
       </c>
       <c r="P5">
-        <v>179.566220088</v>
+        <v>179.671065192</v>
       </c>
       <c r="Q5">
-        <v>320.166220088</v>
+        <v>320.271065192</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.06547469641099421</v>
+        <v>0.06546204733048964</v>
       </c>
       <c r="T5">
         <v>0.4540888528981443</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.28</v>
       </c>
       <c r="W5">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>47.37820954942752</v>
+        <v>48.69688735000801</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.06448752637440031</v>
+        <v>0.06443497141223933</v>
       </c>
       <c r="C6">
-        <v>2714.131877779305</v>
+        <v>2720.009059329091</v>
       </c>
       <c r="D6">
-        <v>2805.715877779306</v>
+        <v>2811.593059329091</v>
       </c>
       <c r="E6">
         <v>-1144.216</v>
@@ -1785,37 +1785,37 @@
         <v>254.775</v>
       </c>
       <c r="M6">
-        <v>7.1699628</v>
+        <v>6.9758052</v>
       </c>
       <c r="N6">
-        <v>247.6050372</v>
+        <v>247.7991948</v>
       </c>
       <c r="O6">
-        <v>69.329410416</v>
+        <v>69.383774544</v>
       </c>
       <c r="P6">
-        <v>178.275626784</v>
+        <v>178.415420256</v>
       </c>
       <c r="Q6">
-        <v>318.875626784</v>
+        <v>319.015420256</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.06562350664000033</v>
+        <v>0.06561076188774931</v>
       </c>
       <c r="T6">
         <v>0.4575233692320855</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.28</v>
       </c>
       <c r="W6">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.53365716207063</v>
+        <v>36.522665512506</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.06434787723013621</v>
+        <v>0.06428527691390371</v>
       </c>
       <c r="C7">
-        <v>2700.585441874621</v>
+        <v>2708.106450330236</v>
       </c>
       <c r="D7">
-        <v>2826.840441874621</v>
+        <v>2834.361450330236</v>
       </c>
       <c r="E7">
         <v>-1109.545</v>
@@ -1867,37 +1867,37 @@
         <v>254.775</v>
       </c>
       <c r="M7">
-        <v>8.962453500000002</v>
+        <v>8.719756500000001</v>
       </c>
       <c r="N7">
-        <v>245.8125465</v>
+        <v>246.0552435</v>
       </c>
       <c r="O7">
-        <v>68.82751302000001</v>
+        <v>68.89546818000001</v>
       </c>
       <c r="P7">
-        <v>176.98503348</v>
+        <v>177.15977532</v>
       </c>
       <c r="Q7">
-        <v>317.58503348</v>
+        <v>317.75977532</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.06577544971593287</v>
+        <v>0.06576260727779337</v>
       </c>
       <c r="T7">
         <v>0.461030191173057</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.28</v>
       </c>
       <c r="W7">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.4269257296565</v>
+        <v>29.2181324100048</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.06420822808587213</v>
+        <v>0.06413558241556806</v>
       </c>
       <c r="C8">
-        <v>2687.359517785097</v>
+        <v>2696.575610582186</v>
       </c>
       <c r="D8">
-        <v>2848.285517785097</v>
+        <v>2857.501610582186</v>
       </c>
       <c r="E8">
         <v>-1074.874</v>
@@ -1949,37 +1949,37 @@
         <v>254.775</v>
       </c>
       <c r="M8">
-        <v>10.7549442</v>
+        <v>10.4637078</v>
       </c>
       <c r="N8">
-        <v>244.0200558</v>
+        <v>244.3112922</v>
       </c>
       <c r="O8">
-        <v>68.32561562400001</v>
+        <v>68.407161816</v>
       </c>
       <c r="P8">
-        <v>175.694440176</v>
+        <v>175.904130384</v>
       </c>
       <c r="Q8">
-        <v>316.294440176</v>
+        <v>316.504130384</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.06593062562326824</v>
+        <v>0.06591768342081709</v>
       </c>
       <c r="T8">
         <v>0.4646116263468152</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.28</v>
       </c>
       <c r="W8">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.68910477471375</v>
+        <v>24.348443675004</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.06406857894160807</v>
+        <v>0.06398588791723243</v>
       </c>
       <c r="C9">
-        <v>2674.461455704887</v>
+        <v>2685.425720578912</v>
       </c>
       <c r="D9">
-        <v>2870.058455704887</v>
+        <v>2881.022720578912</v>
       </c>
       <c r="E9">
         <v>-1040.203</v>
@@ -2031,37 +2031,37 @@
         <v>254.775</v>
       </c>
       <c r="M9">
-        <v>12.5474349</v>
+        <v>12.2076591</v>
       </c>
       <c r="N9">
-        <v>242.2275651</v>
+        <v>242.5673409</v>
       </c>
       <c r="O9">
-        <v>67.823718228</v>
+        <v>67.918855452</v>
       </c>
       <c r="P9">
-        <v>174.403846872</v>
+        <v>174.648485448</v>
       </c>
       <c r="Q9">
-        <v>315.0038468719999</v>
+        <v>315.248485448</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.06608913864689039</v>
+        <v>0.06607609453465854</v>
       </c>
       <c r="T9">
         <v>0.468270081631837</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.28</v>
       </c>
       <c r="W9">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.30494694975464</v>
+        <v>20.87009457857486</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.06392892979734399</v>
+        <v>0.06383619341889682</v>
       </c>
       <c r="C10">
-        <v>2661.898832305572</v>
+        <v>2674.666265594764</v>
       </c>
       <c r="D10">
-        <v>2892.166832305572</v>
+        <v>2904.934265594764</v>
       </c>
       <c r="E10">
         <v>-1005.532</v>
@@ -2113,37 +2113,37 @@
         <v>254.775</v>
       </c>
       <c r="M10">
-        <v>14.3399256</v>
+        <v>13.9516104</v>
       </c>
       <c r="N10">
-        <v>240.4350744</v>
+        <v>240.8233896</v>
       </c>
       <c r="O10">
-        <v>67.32182083200001</v>
+        <v>67.43054908800001</v>
       </c>
       <c r="P10">
-        <v>173.113253568</v>
+        <v>173.392840512</v>
       </c>
       <c r="Q10">
-        <v>313.713253568</v>
+        <v>313.992840512</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.06625109760580869</v>
+        <v>0.06623794936836611</v>
       </c>
       <c r="T10">
         <v>0.4720080685534896</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.28</v>
       </c>
       <c r="W10">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.76682858103532</v>
+        <v>18.261332756253</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.06378928065307991</v>
+        <v>0.06368649892056119</v>
       </c>
       <c r="C11">
-        <v>2649.679459526768</v>
+        <v>2664.307048438209</v>
       </c>
       <c r="D11">
-        <v>2914.618459526768</v>
+        <v>2929.246048438209</v>
       </c>
       <c r="E11">
         <v>-970.8610000000001</v>
@@ -2195,37 +2195,37 @@
         <v>254.775</v>
       </c>
       <c r="M11">
-        <v>16.1324163</v>
+        <v>15.6955617</v>
       </c>
       <c r="N11">
-        <v>238.6425837</v>
+        <v>239.0794383</v>
       </c>
       <c r="O11">
-        <v>66.81992343600001</v>
+        <v>66.94224272400001</v>
       </c>
       <c r="P11">
-        <v>171.822660264</v>
+        <v>172.137195576</v>
       </c>
       <c r="Q11">
-        <v>312.422660264</v>
+        <v>312.737195576</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.06641661610228562</v>
+        <v>0.06640336145116614</v>
       </c>
       <c r="T11">
         <v>0.47582820903386</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.28</v>
       </c>
       <c r="W11">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.79273651647584</v>
+        <v>16.232295783336</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.06364963150881583</v>
+        <v>0.06353680442222555</v>
       </c>
       <c r="C12">
-        <v>2637.811393779398</v>
+        <v>2654.358202851387</v>
       </c>
       <c r="D12">
-        <v>2937.421393779398</v>
+        <v>2953.968202851388</v>
       </c>
       <c r="E12">
         <v>-936.1900000000001</v>
@@ -2277,37 +2277,37 @@
         <v>254.775</v>
       </c>
       <c r="M12">
-        <v>17.924907</v>
+        <v>17.439513</v>
       </c>
       <c r="N12">
-        <v>236.850093</v>
+        <v>237.335487</v>
       </c>
       <c r="O12">
-        <v>66.31802604000001</v>
+        <v>66.45393636</v>
       </c>
       <c r="P12">
-        <v>170.53206696</v>
+        <v>170.88155064</v>
       </c>
       <c r="Q12">
-        <v>311.13206696</v>
+        <v>311.48155064</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.06658581278757315</v>
+        <v>0.06657244935802839</v>
       </c>
       <c r="T12">
         <v>0.4797332415249052</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.28</v>
       </c>
       <c r="W12">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.21346286482825</v>
+        <v>14.6090662050024</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.06350998236455176</v>
+        <v>0.06338710992388992</v>
       </c>
       <c r="C13">
-        <v>2626.302945584383</v>
+        <v>2644.830207594002</v>
       </c>
       <c r="D13">
-        <v>2960.583945584382</v>
+        <v>2979.111207594002</v>
       </c>
       <c r="E13">
         <v>-901.5190000000001</v>
@@ -2359,37 +2359,37 @@
         <v>254.775</v>
       </c>
       <c r="M13">
-        <v>19.7173977</v>
+        <v>19.1834643</v>
       </c>
       <c r="N13">
-        <v>235.0576023</v>
+        <v>235.5915357</v>
       </c>
       <c r="O13">
-        <v>65.81612864400002</v>
+        <v>65.965629996</v>
       </c>
       <c r="P13">
-        <v>169.241473656</v>
+        <v>169.625905704</v>
       </c>
       <c r="Q13">
-        <v>309.8414736559999</v>
+        <v>310.225905704</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.06675881164556377</v>
+        <v>0.06674533699313474</v>
       </c>
       <c r="T13">
         <v>0.483726027555075</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.28</v>
       </c>
       <c r="W13">
-        <v>0.037224</v>
+        <v>0.036216</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.92132987711659</v>
+        <v>13.28096927727491</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.06346537322028767</v>
+        <v>0.0633670154255543</v>
       </c>
       <c r="C14">
-        <v>2599.108103301947</v>
+        <v>2613.566943270919</v>
       </c>
       <c r="D14">
-        <v>2968.060103301947</v>
+        <v>2982.518943270919</v>
       </c>
       <c r="E14">
         <v>-866.8480000000002</v>
@@ -2441,37 +2441,37 @@
         <v>254.775</v>
       </c>
       <c r="M14">
-        <v>21.9675456</v>
+        <v>21.5514936</v>
       </c>
       <c r="N14">
-        <v>232.8074544</v>
+        <v>233.2235064</v>
       </c>
       <c r="O14">
-        <v>65.18608723200001</v>
+        <v>65.30258179200001</v>
       </c>
       <c r="P14">
-        <v>167.621367168</v>
+        <v>167.920924608</v>
       </c>
       <c r="Q14">
-        <v>308.221367168</v>
+        <v>308.520924608</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.06693574229578145</v>
+        <v>0.06692215389267533</v>
       </c>
       <c r="T14">
         <v>0.4878095587222941</v>
       </c>
       <c r="U14">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.28</v>
       </c>
       <c r="W14">
-        <v>0.038016</v>
+        <v>0.037296</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.59779087928694</v>
+        <v>11.82168645610716</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.06333364407602358</v>
+        <v>0.06322812092721866</v>
       </c>
       <c r="C15">
-        <v>2586.735948643914</v>
+        <v>2602.665314285277</v>
       </c>
       <c r="D15">
-        <v>2990.358948643914</v>
+        <v>3006.288314285277</v>
       </c>
       <c r="E15">
         <v>-832.1770000000001</v>
@@ -2523,37 +2523,37 @@
         <v>254.775</v>
       </c>
       <c r="M15">
-        <v>23.7981744</v>
+        <v>23.3474514</v>
       </c>
       <c r="N15">
-        <v>230.9768256</v>
+        <v>231.4275486</v>
       </c>
       <c r="O15">
-        <v>64.673511168</v>
+        <v>64.799713608</v>
       </c>
       <c r="P15">
-        <v>166.303314432</v>
+        <v>166.627834992</v>
       </c>
       <c r="Q15">
-        <v>306.903314432</v>
+        <v>307.227834992</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.0671167403172685</v>
+        <v>0.0671030355485272</v>
       </c>
       <c r="T15">
         <v>0.4919869641692194</v>
       </c>
       <c r="U15">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.28</v>
       </c>
       <c r="W15">
-        <v>0.038016</v>
+        <v>0.037296</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.70565311934179</v>
+        <v>10.91232595948353</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.06320191493175953</v>
+        <v>0.06308922642888302</v>
       </c>
       <c r="C16">
-        <v>2574.701389914426</v>
+        <v>2592.14559190215</v>
       </c>
       <c r="D16">
-        <v>3012.995389914426</v>
+        <v>3030.43959190215</v>
       </c>
       <c r="E16">
         <v>-797.5060000000001</v>
@@ -2605,37 +2605,37 @@
         <v>254.775</v>
       </c>
       <c r="M16">
-        <v>25.6288032</v>
+        <v>25.1434092</v>
       </c>
       <c r="N16">
-        <v>229.1461968</v>
+        <v>229.6315908</v>
       </c>
       <c r="O16">
-        <v>64.160935104</v>
+        <v>64.29684542400001</v>
       </c>
       <c r="P16">
-        <v>164.985261696</v>
+        <v>165.334745376</v>
       </c>
       <c r="Q16">
-        <v>305.585261696</v>
+        <v>305.934745376</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.06730194759506922</v>
+        <v>0.06728812375451515</v>
       </c>
       <c r="T16">
         <v>0.4962615185800268</v>
       </c>
       <c r="U16">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.28</v>
       </c>
       <c r="W16">
-        <v>0.038016</v>
+        <v>0.037296</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.940963610817379</v>
+        <v>10.1328741052347</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.06330778578749544</v>
+        <v>0.06313393193054741</v>
       </c>
       <c r="C17">
-        <v>2521.810587357417</v>
+        <v>2549.658862455282</v>
       </c>
       <c r="D17">
-        <v>2994.775587357417</v>
+        <v>3022.623862455282</v>
       </c>
       <c r="E17">
         <v>-762.8350000000002</v>
@@ -2687,37 +2687,37 @@
         <v>254.775</v>
       </c>
       <c r="M17">
-        <v>28.603575</v>
+        <v>27.8234775</v>
       </c>
       <c r="N17">
-        <v>226.171425</v>
+        <v>226.9515225</v>
       </c>
       <c r="O17">
-        <v>63.32799900000001</v>
+        <v>63.54642630000001</v>
       </c>
       <c r="P17">
-        <v>162.843426</v>
+        <v>163.4050962</v>
       </c>
       <c r="Q17">
-        <v>303.443426</v>
+        <v>304.0050962</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.06749151269117111</v>
+        <v>0.0674775669771146</v>
       </c>
       <c r="T17">
         <v>0.5006366507416766</v>
       </c>
       <c r="U17">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.28</v>
       </c>
       <c r="W17">
-        <v>0.0396</v>
+        <v>0.03852</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.907103395292372</v>
+        <v>9.156835266188422</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.06319189664323135</v>
+        <v>0.06300727743221177</v>
       </c>
       <c r="C18">
-        <v>2507.094971591883</v>
+        <v>2537.235943853677</v>
       </c>
       <c r="D18">
-        <v>3014.730971591883</v>
+        <v>3044.871943853677</v>
       </c>
       <c r="E18">
         <v>-728.1640000000001</v>
@@ -2769,37 +2769,37 @@
         <v>254.775</v>
       </c>
       <c r="M18">
-        <v>30.51048</v>
+        <v>29.678376</v>
       </c>
       <c r="N18">
-        <v>224.26452</v>
+        <v>225.096624</v>
       </c>
       <c r="O18">
-        <v>62.79406560000001</v>
+        <v>63.02705472000001</v>
       </c>
       <c r="P18">
-        <v>161.4704544</v>
+        <v>162.06956928</v>
       </c>
       <c r="Q18">
-        <v>302.0704544</v>
+        <v>302.66956928</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.06768559124194209</v>
+        <v>0.06767152075263307</v>
       </c>
       <c r="T18">
         <v>0.5051159527166992</v>
       </c>
       <c r="U18">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.28</v>
       </c>
       <c r="W18">
-        <v>0.0396</v>
+        <v>0.03852</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.350409433086599</v>
+        <v>8.584533062051644</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.06307600749896729</v>
+        <v>0.06288062293387614</v>
       </c>
       <c r="C19">
-        <v>2492.647081156118</v>
+        <v>2525.142968673846</v>
       </c>
       <c r="D19">
-        <v>3034.954081156118</v>
+        <v>3067.449968673846</v>
       </c>
       <c r="E19">
         <v>-693.4930000000001</v>
@@ -2851,37 +2851,37 @@
         <v>254.775</v>
       </c>
       <c r="M19">
-        <v>32.417385</v>
+        <v>31.5332745</v>
       </c>
       <c r="N19">
-        <v>222.357615</v>
+        <v>223.2417255</v>
       </c>
       <c r="O19">
-        <v>62.26013220000001</v>
+        <v>62.50768314</v>
       </c>
       <c r="P19">
-        <v>160.0974828</v>
+        <v>160.73404236</v>
       </c>
       <c r="Q19">
-        <v>300.6974828</v>
+        <v>301.33404236</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.06788434638429794</v>
+        <v>0.0678701481131038</v>
       </c>
       <c r="T19">
         <v>0.5097031896790715</v>
       </c>
       <c r="U19">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.28</v>
       </c>
       <c r="W19">
-        <v>0.0396</v>
+        <v>0.03852</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.859208878199151</v>
+        <v>8.079560528989781</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.0631545183547032</v>
+        <v>0.06275396843554053</v>
       </c>
       <c r="C20">
-        <v>2444.246121202133</v>
+        <v>2513.387331435614</v>
       </c>
       <c r="D20">
-        <v>3021.224121202133</v>
+        <v>3090.365331435614</v>
       </c>
       <c r="E20">
         <v>-658.8220000000001</v>
@@ -2933,45 +2933,45 @@
         <v>254.775</v>
       </c>
       <c r="M20">
-        <v>35.260407</v>
+        <v>33.38817299999999</v>
       </c>
       <c r="N20">
-        <v>219.514593</v>
+        <v>221.386827</v>
       </c>
       <c r="O20">
-        <v>61.46408604000001</v>
+        <v>61.98831156000001</v>
       </c>
       <c r="P20">
-        <v>158.05050696</v>
+        <v>159.39851544</v>
       </c>
       <c r="Q20">
-        <v>298.65050696</v>
+        <v>299.99851544</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.0680879492130527</v>
+        <v>0.0680736200433421</v>
       </c>
       <c r="T20">
         <v>0.5144023104697945</v>
       </c>
       <c r="U20">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.28</v>
       </c>
       <c r="W20">
-        <v>0.04068</v>
+        <v>0.03852</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.22552635311328</v>
+        <v>7.630696055157018</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.06304942921043914</v>
+        <v>0.06273675393720489</v>
       </c>
       <c r="C21">
-        <v>2427.981403152316</v>
+        <v>2481.857375407308</v>
       </c>
       <c r="D21">
-        <v>3039.630403152317</v>
+        <v>3093.506375407308</v>
       </c>
       <c r="E21">
         <v>-624.1510000000001</v>
@@ -3015,37 +3015,37 @@
         <v>254.775</v>
       </c>
       <c r="M21">
-        <v>37.2193185</v>
+        <v>35.77007070000001</v>
       </c>
       <c r="N21">
-        <v>217.5556815</v>
+        <v>219.0049293</v>
       </c>
       <c r="O21">
-        <v>60.91559082000001</v>
+        <v>61.32138020400001</v>
       </c>
       <c r="P21">
-        <v>156.64009068</v>
+        <v>157.683549096</v>
       </c>
       <c r="Q21">
-        <v>297.24009068</v>
+        <v>298.283549096</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.06829657927214708</v>
+        <v>0.06828211597185789</v>
       </c>
       <c r="T21">
         <v>0.5192174589343624</v>
       </c>
       <c r="U21">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.28</v>
       </c>
       <c r="W21">
-        <v>0.04068</v>
+        <v>0.039096</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.845235492423108</v>
+        <v>7.12257468364467</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06294434006617505</v>
+        <v>0.06261585943886926</v>
       </c>
       <c r="C22">
-        <v>2411.94233396525</v>
+        <v>2469.426564956495</v>
       </c>
       <c r="D22">
-        <v>3058.26233396525</v>
+        <v>3115.746564956496</v>
       </c>
       <c r="E22">
         <v>-589.48</v>
@@ -3097,37 +3097,37 @@
         <v>254.775</v>
       </c>
       <c r="M22">
-        <v>39.17823000000001</v>
+        <v>37.652706</v>
       </c>
       <c r="N22">
-        <v>215.59677</v>
+        <v>217.122294</v>
       </c>
       <c r="O22">
-        <v>60.36709560000001</v>
+        <v>60.79424232000001</v>
       </c>
       <c r="P22">
-        <v>155.2296744</v>
+        <v>156.32805168</v>
       </c>
       <c r="Q22">
-        <v>295.8296744</v>
+        <v>296.92805168</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.06851042508271882</v>
+        <v>0.06849582429858657</v>
       </c>
       <c r="T22">
         <v>0.5241529861105445</v>
       </c>
       <c r="U22">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.28</v>
       </c>
       <c r="W22">
-        <v>0.04068</v>
+        <v>0.039096</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.502973717801952</v>
+        <v>6.766445949462437</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.06283925092191098</v>
+        <v>0.06249496494053363</v>
       </c>
       <c r="C23">
-        <v>2396.133088691697</v>
+        <v>2457.317853601789</v>
       </c>
       <c r="D23">
-        <v>3077.124088691697</v>
+        <v>3138.308853601789</v>
       </c>
       <c r="E23">
         <v>-554.8090000000001</v>
@@ -3179,37 +3179,37 @@
         <v>254.775</v>
       </c>
       <c r="M23">
-        <v>41.1371415</v>
+        <v>39.5353413</v>
       </c>
       <c r="N23">
-        <v>213.6378585</v>
+        <v>215.2396587</v>
       </c>
       <c r="O23">
-        <v>59.81860038000001</v>
+        <v>60.26710443600001</v>
       </c>
       <c r="P23">
-        <v>153.81925812</v>
+        <v>154.972554264</v>
       </c>
       <c r="Q23">
-        <v>294.41925812</v>
+        <v>295.572554264</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.06872968471127971</v>
+        <v>0.0687149429627008</v>
       </c>
       <c r="T23">
         <v>0.52921346334182</v>
       </c>
       <c r="U23">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.28</v>
       </c>
       <c r="W23">
-        <v>0.04068</v>
+        <v>0.039096</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.193308302668527</v>
+        <v>6.444234237583274</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06295592177764689</v>
+        <v>0.062374070442198</v>
       </c>
       <c r="C24">
-        <v>2340.535745864638</v>
+        <v>2445.538289703838</v>
       </c>
       <c r="D24">
-        <v>3056.197745864638</v>
+        <v>3161.200289703838</v>
       </c>
       <c r="E24">
         <v>-520.1380000000001</v>
@@ -3261,45 +3261,45 @@
         <v>254.775</v>
       </c>
       <c r="M24">
-        <v>44.1639198</v>
+        <v>41.4179766</v>
       </c>
       <c r="N24">
-        <v>210.6110802</v>
+        <v>213.3570234</v>
       </c>
       <c r="O24">
-        <v>58.971102456</v>
+        <v>59.73996655200001</v>
       </c>
       <c r="P24">
-        <v>151.639977744</v>
+        <v>153.617056848</v>
       </c>
       <c r="Q24">
-        <v>292.239977744</v>
+        <v>294.217056848</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.06895456638159858</v>
+        <v>0.06893968005410001</v>
       </c>
       <c r="T24">
         <v>0.5344036963995383</v>
       </c>
       <c r="U24">
-        <v>0.0579</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.28</v>
       </c>
       <c r="W24">
-        <v>0.041688</v>
+        <v>0.039096</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>5.768849349282624</v>
+        <v>6.151314499511307</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06286091263338281</v>
+        <v>0.06241877594386238</v>
       </c>
       <c r="C25">
-        <v>2322.884159701167</v>
+        <v>2402.363471775841</v>
       </c>
       <c r="D25">
-        <v>3073.217159701167</v>
+        <v>3152.696471775841</v>
       </c>
       <c r="E25">
         <v>-485.4670000000001</v>
@@ -3343,37 +3343,37 @@
         <v>254.775</v>
       </c>
       <c r="M25">
-        <v>46.1713707</v>
+        <v>44.0980449</v>
       </c>
       <c r="N25">
-        <v>208.6036293</v>
+        <v>210.6769551</v>
       </c>
       <c r="O25">
-        <v>58.40901620400001</v>
+        <v>58.98954742800001</v>
       </c>
       <c r="P25">
-        <v>150.194613096</v>
+        <v>151.687407672</v>
       </c>
       <c r="Q25">
-        <v>290.794613096</v>
+        <v>292.287407672</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.06918528913426339</v>
+        <v>0.06917025447254854</v>
       </c>
       <c r="T25">
         <v>0.539728740705509</v>
       </c>
       <c r="U25">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.28</v>
       </c>
       <c r="W25">
-        <v>0.041688</v>
+        <v>0.039816</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.518029812357294</v>
+        <v>5.777467018724906</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.06276590348911873</v>
+        <v>0.06230508144552675</v>
       </c>
       <c r="C26">
-        <v>2305.42319114265</v>
+        <v>2389.409677167772</v>
       </c>
       <c r="D26">
-        <v>3090.42719114265</v>
+        <v>3174.413677167772</v>
       </c>
       <c r="E26">
         <v>-450.7960000000002</v>
@@ -3425,37 +3425,37 @@
         <v>254.775</v>
       </c>
       <c r="M26">
-        <v>48.1788216</v>
+        <v>46.0153512</v>
       </c>
       <c r="N26">
-        <v>206.5961784</v>
+        <v>208.7596488</v>
       </c>
       <c r="O26">
-        <v>57.84692995200001</v>
+        <v>58.45270166400001</v>
       </c>
       <c r="P26">
-        <v>148.749248448</v>
+        <v>150.306947136</v>
       </c>
       <c r="Q26">
-        <v>289.349248448</v>
+        <v>290.906947136</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.06942208353831412</v>
+        <v>0.06940689663885098</v>
       </c>
       <c r="T26">
         <v>0.5451939177563738</v>
       </c>
       <c r="U26">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.28</v>
       </c>
       <c r="W26">
-        <v>0.041688</v>
+        <v>0.039816</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.288111903509073</v>
+        <v>5.536739226278034</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.06267089434485465</v>
+        <v>0.06219138694719111</v>
       </c>
       <c r="C27">
-        <v>2288.156060602033</v>
+        <v>2376.757153804201</v>
       </c>
       <c r="D27">
-        <v>3107.831060602033</v>
+        <v>3196.432153804201</v>
       </c>
       <c r="E27">
         <v>-416.1250000000001</v>
@@ -3507,37 +3507,37 @@
         <v>254.775</v>
       </c>
       <c r="M27">
-        <v>50.1862725</v>
+        <v>47.9326575</v>
       </c>
       <c r="N27">
-        <v>204.5887275</v>
+        <v>206.8423425</v>
       </c>
       <c r="O27">
-        <v>57.2848437</v>
+        <v>57.9158559</v>
       </c>
       <c r="P27">
-        <v>147.3038838</v>
+        <v>148.9264866</v>
       </c>
       <c r="Q27">
-        <v>287.9038838</v>
+        <v>289.5264866</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.06966519245980621</v>
+        <v>0.06964984926292149</v>
       </c>
       <c r="T27">
         <v>0.5508048328619282</v>
       </c>
       <c r="U27">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.28</v>
       </c>
       <c r="W27">
-        <v>0.041688</v>
+        <v>0.039816</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.076587427368709</v>
+        <v>5.315269657226913</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.06257588520059057</v>
+        <v>0.06207769244885548</v>
       </c>
       <c r="C28">
-        <v>2271.086061446671</v>
+        <v>2364.412214536242</v>
       </c>
       <c r="D28">
-        <v>3125.432061446671</v>
+        <v>3218.758214536242</v>
       </c>
       <c r="E28">
         <v>-381.4540000000001</v>
@@ -3589,37 +3589,37 @@
         <v>254.775</v>
       </c>
       <c r="M28">
-        <v>52.1937234</v>
+        <v>49.8499638</v>
       </c>
       <c r="N28">
-        <v>202.5812766</v>
+        <v>204.9250362</v>
       </c>
       <c r="O28">
-        <v>56.722757448</v>
+        <v>57.37901013600001</v>
       </c>
       <c r="P28">
-        <v>145.858519152</v>
+        <v>147.546026064</v>
       </c>
       <c r="Q28">
-        <v>286.458519152</v>
+        <v>288.146026064</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.06991487189268997</v>
+        <v>0.06989936817412903</v>
       </c>
       <c r="T28">
         <v>0.5565673943216869</v>
       </c>
       <c r="U28">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.28</v>
       </c>
       <c r="W28">
-        <v>0.041688</v>
+        <v>0.039816</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.881334064777604</v>
+        <v>5.110836208872031</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.0624808760563265</v>
+        <v>0.06196399795051986</v>
       </c>
       <c r="C29">
-        <v>2254.216562075943</v>
+        <v>2352.381349828613</v>
       </c>
       <c r="D29">
-        <v>3143.233562075944</v>
+        <v>3241.398349828613</v>
       </c>
       <c r="E29">
         <v>-346.783</v>
@@ -3671,37 +3671,37 @@
         <v>254.775</v>
       </c>
       <c r="M29">
-        <v>54.20117430000001</v>
+        <v>51.7672701</v>
       </c>
       <c r="N29">
-        <v>200.5738257</v>
+        <v>203.0077299</v>
       </c>
       <c r="O29">
-        <v>56.160671196</v>
+        <v>56.84216437200001</v>
       </c>
       <c r="P29">
-        <v>144.413154504</v>
+        <v>146.165565528</v>
       </c>
       <c r="Q29">
-        <v>285.013154504</v>
+        <v>286.765565528</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.0701713918579815</v>
+        <v>0.07015572321989022</v>
       </c>
       <c r="T29">
         <v>0.5624878341776032</v>
       </c>
       <c r="U29">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.28</v>
       </c>
       <c r="W29">
-        <v>0.041688</v>
+        <v>0.039816</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.700543914230286</v>
+        <v>4.921545978913808</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.06238586691206241</v>
+        <v>0.06185030345218423</v>
       </c>
       <c r="C30">
-        <v>2237.551008070317</v>
+        <v>2340.671234050371</v>
       </c>
       <c r="D30">
-        <v>3161.239008070318</v>
+        <v>3264.359234050371</v>
       </c>
       <c r="E30">
         <v>-312.1120000000001</v>
@@ -3753,37 +3753,37 @@
         <v>254.775</v>
       </c>
       <c r="M30">
-        <v>56.2086252</v>
+        <v>53.6845764</v>
       </c>
       <c r="N30">
-        <v>198.5663748</v>
+        <v>201.0904236</v>
       </c>
       <c r="O30">
-        <v>55.59858494400001</v>
+        <v>56.30531860800001</v>
       </c>
       <c r="P30">
-        <v>142.967789856</v>
+        <v>144.785104992</v>
       </c>
       <c r="Q30">
-        <v>283.567789856</v>
+        <v>285.385104992</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07043503737786447</v>
+        <v>0.07041919923914476</v>
       </c>
       <c r="T30">
         <v>0.568572730696184</v>
       </c>
       <c r="U30">
-        <v>0.0579</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.28</v>
       </c>
       <c r="W30">
-        <v>0.041688</v>
+        <v>0.039816</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.532667345864919</v>
+        <v>4.745776479666886</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.06283373776779834</v>
+        <v>0.0617366089538486</v>
       </c>
       <c r="C31">
-        <v>2119.761033302089</v>
+        <v>2329.288732034946</v>
       </c>
       <c r="D31">
-        <v>3078.120033302089</v>
+        <v>3287.647732034946</v>
       </c>
       <c r="E31">
         <v>-277.4410000000001</v>
@@ -3835,45 +3835,45 @@
         <v>254.775</v>
       </c>
       <c r="M31">
-        <v>60.83026949999999</v>
+        <v>55.6018827</v>
       </c>
       <c r="N31">
-        <v>193.9447305</v>
+        <v>199.1731173</v>
       </c>
       <c r="O31">
-        <v>54.30452454000001</v>
+        <v>55.76847284400001</v>
       </c>
       <c r="P31">
-        <v>139.64020596</v>
+        <v>143.404644456</v>
       </c>
       <c r="Q31">
-        <v>280.24020596</v>
+        <v>284.004644456</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07070610953211034</v>
+        <v>0.07069009711809662</v>
       </c>
       <c r="T31">
         <v>0.5748290327504993</v>
       </c>
       <c r="U31">
-        <v>0.0605</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.28</v>
       </c>
       <c r="W31">
-        <v>0.04355999999999999</v>
+        <v>0.039816</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.18829313258262</v>
+        <v>4.582129014850787</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.06275744862353426</v>
+        <v>0.06216291445551296</v>
       </c>
       <c r="C32">
-        <v>2098.938056580593</v>
+        <v>2208.964145107548</v>
       </c>
       <c r="D32">
-        <v>3091.968056580593</v>
+        <v>3201.994145107547</v>
       </c>
       <c r="E32">
         <v>-242.7700000000002</v>
@@ -3917,37 +3917,37 @@
         <v>254.775</v>
       </c>
       <c r="M32">
-        <v>62.92786499999999</v>
+        <v>60.119514</v>
       </c>
       <c r="N32">
-        <v>191.847135</v>
+        <v>194.655486</v>
       </c>
       <c r="O32">
-        <v>53.71719780000001</v>
+        <v>54.50353608</v>
       </c>
       <c r="P32">
-        <v>138.1299372</v>
+        <v>140.15194992</v>
       </c>
       <c r="Q32">
-        <v>278.7299372</v>
+        <v>280.75194992</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.07098492660504895</v>
+        <v>0.07096873493644709</v>
       </c>
       <c r="T32">
         <v>0.5812640862920809</v>
       </c>
       <c r="U32">
-        <v>0.0605</v>
+        <v>0.0578</v>
       </c>
       <c r="V32">
         <v>0.28</v>
       </c>
       <c r="W32">
-        <v>0.04355999999999999</v>
+        <v>0.041616</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.048683361496533</v>
+        <v>4.237808708832876</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.06328379947927018</v>
+        <v>0.06206721995717733</v>
       </c>
       <c r="C33">
-        <v>1971.183168583654</v>
+        <v>2193.12938290333</v>
       </c>
       <c r="D33">
-        <v>2998.884168583654</v>
+        <v>3220.83038290333</v>
       </c>
       <c r="E33">
         <v>-208.0990000000002</v>
@@ -3999,45 +3999,45 @@
         <v>254.775</v>
       </c>
       <c r="M33">
-        <v>67.92742320000001</v>
+        <v>62.1234978</v>
       </c>
       <c r="N33">
-        <v>186.8475768</v>
+        <v>192.6515022</v>
       </c>
       <c r="O33">
-        <v>52.31732150400001</v>
+        <v>53.94242061600001</v>
       </c>
       <c r="P33">
-        <v>134.530255296</v>
+        <v>138.709081584</v>
       </c>
       <c r="Q33">
-        <v>275.130255296</v>
+        <v>279.309081584</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.07127182533227563</v>
+        <v>0.07125544921330049</v>
       </c>
       <c r="T33">
         <v>0.5878856631247228</v>
       </c>
       <c r="U33">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.28</v>
       </c>
       <c r="W33">
-        <v>0.045504</v>
+        <v>0.041616</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.750694314575442</v>
+        <v>4.101105202096331</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.06322695033500611</v>
+        <v>0.0627779254588417</v>
       </c>
       <c r="C34">
-        <v>1946.294947294429</v>
+        <v>2023.632612899429</v>
       </c>
       <c r="D34">
-        <v>3008.66694729443</v>
+        <v>3086.00461289943</v>
       </c>
       <c r="E34">
         <v>-173.4280000000001</v>
@@ -4081,37 +4081,37 @@
         <v>254.775</v>
       </c>
       <c r="M34">
-        <v>70.1186304</v>
+        <v>68.01063360000001</v>
       </c>
       <c r="N34">
-        <v>184.6563696</v>
+        <v>186.7643664</v>
       </c>
       <c r="O34">
-        <v>51.70378348800001</v>
+        <v>52.294022592</v>
       </c>
       <c r="P34">
-        <v>132.952586112</v>
+        <v>134.470343808</v>
       </c>
       <c r="Q34">
-        <v>273.552586112</v>
+        <v>275.070343808</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.07156716225736193</v>
+        <v>0.07155059626300252</v>
       </c>
       <c r="T34">
         <v>0.5947019922171483</v>
       </c>
       <c r="U34">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V34">
         <v>0.28</v>
       </c>
       <c r="W34">
-        <v>0.045504</v>
+        <v>0.044136</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.63348511724496</v>
+        <v>3.746105373733792</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.06317010119074203</v>
+        <v>0.06270743096050607</v>
       </c>
       <c r="C35">
-        <v>1921.470760473646</v>
+        <v>2001.828520211128</v>
       </c>
       <c r="D35">
-        <v>3018.513760473646</v>
+        <v>3098.871520211128</v>
       </c>
       <c r="E35">
         <v>-138.7570000000001</v>
@@ -4163,37 +4163,37 @@
         <v>254.775</v>
       </c>
       <c r="M35">
-        <v>72.30983760000001</v>
+        <v>70.1359659</v>
       </c>
       <c r="N35">
-        <v>182.4651624</v>
+        <v>184.6390341</v>
       </c>
       <c r="O35">
-        <v>51.09024547200001</v>
+        <v>51.698929548</v>
       </c>
       <c r="P35">
-        <v>131.374916928</v>
+        <v>132.940104552</v>
       </c>
       <c r="Q35">
-        <v>271.974916928</v>
+        <v>273.540104552</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.07187131521006274</v>
+        <v>0.07185455367239714</v>
       </c>
       <c r="T35">
         <v>0.6017217938197954</v>
       </c>
       <c r="U35">
-        <v>0.06320000000000001</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.28</v>
       </c>
       <c r="W35">
-        <v>0.045504</v>
+        <v>0.044136</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.523379507631476</v>
+        <v>3.632587029075192</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.06426381204647795</v>
+        <v>0.06263693646217046</v>
       </c>
       <c r="C36">
-        <v>1707.996961804124</v>
+        <v>1980.132172322849</v>
       </c>
       <c r="D36">
-        <v>2839.710961804124</v>
+        <v>3111.846172322849</v>
       </c>
       <c r="E36">
         <v>-104.086</v>
@@ -4245,45 +4245,45 @@
         <v>254.775</v>
       </c>
       <c r="M36">
-        <v>80.04147060000001</v>
+        <v>72.2612982</v>
       </c>
       <c r="N36">
-        <v>174.7335294</v>
+        <v>182.5137018</v>
       </c>
       <c r="O36">
-        <v>48.92538823200001</v>
+        <v>51.10383650400001</v>
       </c>
       <c r="P36">
-        <v>125.808141168</v>
+        <v>131.409865296</v>
       </c>
       <c r="Q36">
-        <v>266.408141168</v>
+        <v>272.009865296</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.07218468491890599</v>
+        <v>0.07216772191237948</v>
       </c>
       <c r="T36">
         <v>0.6089543166831289</v>
       </c>
       <c r="U36">
-        <v>0.0679</v>
+        <v>0.0613</v>
       </c>
       <c r="V36">
         <v>0.28</v>
       </c>
       <c r="W36">
-        <v>0.048888</v>
+        <v>0.044136</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.183037469079185</v>
+        <v>3.525746234102393</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.06424080290221387</v>
+        <v>0.06327204196383482</v>
       </c>
       <c r="C37">
-        <v>1676.869154556355</v>
+        <v>1832.346138117559</v>
       </c>
       <c r="D37">
-        <v>2843.254154556355</v>
+        <v>2998.73113811756</v>
       </c>
       <c r="E37">
         <v>-69.41499999999996</v>
@@ -4327,37 +4327,37 @@
         <v>254.775</v>
       </c>
       <c r="M37">
-        <v>82.39563150000001</v>
+        <v>77.78438850000002</v>
       </c>
       <c r="N37">
-        <v>172.3793685</v>
+        <v>176.9906115</v>
       </c>
       <c r="O37">
-        <v>48.26622318</v>
+        <v>49.55737122000001</v>
       </c>
       <c r="P37">
-        <v>124.11314532</v>
+        <v>127.43324028</v>
       </c>
       <c r="Q37">
-        <v>264.71314532</v>
+        <v>268.03324028</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.07250769677263673</v>
+        <v>0.07249052609820741</v>
       </c>
       <c r="T37">
         <v>0.6164093787114879</v>
       </c>
       <c r="U37">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V37">
         <v>0.28</v>
       </c>
       <c r="W37">
-        <v>0.048888</v>
+        <v>0.046152</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.092093541391208</v>
+        <v>3.275400178790374</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.0642177937579498</v>
+        <v>0.0632217074654992</v>
       </c>
       <c r="C38">
-        <v>1645.750200250937</v>
+        <v>1806.339020677835</v>
       </c>
       <c r="D38">
-        <v>2846.806200250937</v>
+        <v>3007.395020677835</v>
       </c>
       <c r="E38">
         <v>-34.74400000000014</v>
@@ -4409,37 +4409,37 @@
         <v>254.775</v>
       </c>
       <c r="M38">
-        <v>84.7497924</v>
+        <v>80.00679960000001</v>
       </c>
       <c r="N38">
-        <v>170.0252076</v>
+        <v>174.7682004</v>
       </c>
       <c r="O38">
-        <v>47.607058128</v>
+        <v>48.93509611200001</v>
       </c>
       <c r="P38">
-        <v>122.418149472</v>
+        <v>125.833104288</v>
       </c>
       <c r="Q38">
-        <v>263.018149472</v>
+        <v>266.433104288</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.07284080274679655</v>
+        <v>0.07282341791484249</v>
       </c>
       <c r="T38">
         <v>0.6240974114282332</v>
       </c>
       <c r="U38">
-        <v>0.0679</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.28</v>
       </c>
       <c r="W38">
-        <v>0.048888</v>
+        <v>0.046152</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.006202054130341</v>
+        <v>3.184416840490643</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.0666723046136857</v>
+        <v>0.06317137296716357</v>
       </c>
       <c r="C39">
-        <v>1276.304634048478</v>
+        <v>1780.382111380338</v>
       </c>
       <c r="D39">
-        <v>2512.031634048478</v>
+        <v>3016.109111380338</v>
       </c>
       <c r="E39">
         <v>-0.07300000000009277</v>
@@ -4491,45 +4491,45 @@
         <v>254.775</v>
       </c>
       <c r="M39">
-        <v>99.03424439999999</v>
+        <v>82.22921070000001</v>
       </c>
       <c r="N39">
-        <v>155.7407556</v>
+        <v>172.5457893</v>
       </c>
       <c r="O39">
-        <v>43.607411568</v>
+        <v>48.312821004</v>
       </c>
       <c r="P39">
-        <v>112.133344032</v>
+        <v>124.232968296</v>
       </c>
       <c r="Q39">
-        <v>252.733344032</v>
+        <v>264.832968296</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.07318448351378684</v>
+        <v>0.07316687772565646</v>
       </c>
       <c r="T39">
         <v>0.6320295086756688</v>
       </c>
       <c r="U39">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V39">
         <v>0.28</v>
       </c>
       <c r="W39">
-        <v>0.05558399999999999</v>
+        <v>0.046152</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.572594980085495</v>
+        <v>3.098351520477382</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.06671625546942164</v>
+        <v>0.06312103846882794</v>
       </c>
       <c r="C40">
-        <v>1236.355158648634</v>
+        <v>1754.475847935832</v>
       </c>
       <c r="D40">
-        <v>2506.753158648634</v>
+        <v>3024.873847935832</v>
       </c>
       <c r="E40">
         <v>34.59799999999996</v>
@@ -4573,45 +4573,45 @@
         <v>254.775</v>
       </c>
       <c r="M40">
-        <v>101.7108456</v>
+        <v>84.45162180000001</v>
       </c>
       <c r="N40">
-        <v>153.0641544</v>
+        <v>170.3233782</v>
       </c>
       <c r="O40">
-        <v>42.857963232</v>
+        <v>47.690545896</v>
       </c>
       <c r="P40">
-        <v>110.206191168</v>
+        <v>122.632832304</v>
       </c>
       <c r="Q40">
-        <v>250.806191168</v>
+        <v>263.232832304</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.07353925075713168</v>
+        <v>0.07352141688520634</v>
       </c>
       <c r="T40">
         <v>0.6402174800278604</v>
       </c>
       <c r="U40">
-        <v>0.07719999999999999</v>
+        <v>0.0641</v>
       </c>
       <c r="V40">
         <v>0.28</v>
       </c>
       <c r="W40">
-        <v>0.05558399999999999</v>
+        <v>0.046152</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.504895112188508</v>
+        <v>3.016815954149029</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.06807996632515756</v>
+        <v>0.06526094397049231</v>
       </c>
       <c r="C41">
-        <v>1048.250960177439</v>
+        <v>1387.192812319616</v>
       </c>
       <c r="D41">
-        <v>2353.319960177439</v>
+        <v>2692.261812319616</v>
       </c>
       <c r="E41">
         <v>69.26900000000001</v>
@@ -4655,45 +4655,45 @@
         <v>254.775</v>
       </c>
       <c r="M41">
-        <v>110.7426411</v>
+        <v>97.22095110000001</v>
       </c>
       <c r="N41">
-        <v>144.0323589</v>
+        <v>157.5540489</v>
       </c>
       <c r="O41">
-        <v>40.329060492</v>
+        <v>44.115133692</v>
       </c>
       <c r="P41">
-        <v>103.703298408</v>
+        <v>113.438915208</v>
       </c>
       <c r="Q41">
-        <v>244.303298408</v>
+        <v>254.038915208</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.07390564971337305</v>
+        <v>0.07388758027949559</v>
       </c>
       <c r="T41">
         <v>0.648673909457173</v>
       </c>
       <c r="U41">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V41">
         <v>0.28</v>
       </c>
       <c r="W41">
-        <v>0.058968</v>
+        <v>0.051768</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.300604333338407</v>
+        <v>2.62057711961635</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.06815775718089348</v>
+        <v>0.06526676947215668</v>
       </c>
       <c r="C42">
-        <v>1005.391894977452</v>
+        <v>1351.716143166807</v>
       </c>
       <c r="D42">
-        <v>2345.131894977453</v>
+        <v>2691.456143166807</v>
       </c>
       <c r="E42">
         <v>103.9400000000001</v>
@@ -4737,45 +4737,45 @@
         <v>254.775</v>
       </c>
       <c r="M42">
-        <v>113.582196</v>
+        <v>99.71379600000002</v>
       </c>
       <c r="N42">
-        <v>141.192804</v>
+        <v>155.061204</v>
       </c>
       <c r="O42">
-        <v>39.53398512</v>
+        <v>43.41713712</v>
       </c>
       <c r="P42">
-        <v>101.65881888</v>
+        <v>111.64406688</v>
       </c>
       <c r="Q42">
-        <v>242.25881888</v>
+        <v>252.24406688</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.0742842619681558</v>
+        <v>0.07426594912026113</v>
       </c>
       <c r="T42">
         <v>0.6574122198674627</v>
       </c>
       <c r="U42">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.28</v>
       </c>
       <c r="W42">
-        <v>0.058968</v>
+        <v>0.051768</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.243089225004947</v>
+        <v>2.555062691625941</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.0682355480366294</v>
+        <v>0.06642387497382105</v>
       </c>
       <c r="C43">
-        <v>962.5896107928161</v>
+        <v>1166.040605236868</v>
       </c>
       <c r="D43">
-        <v>2337.000610792816</v>
+        <v>2540.451605236868</v>
       </c>
       <c r="E43">
         <v>138.6109999999999</v>
@@ -4819,37 +4819,37 @@
         <v>254.775</v>
       </c>
       <c r="M43">
-        <v>116.4217509</v>
+        <v>107.7505338</v>
       </c>
       <c r="N43">
-        <v>138.3532491</v>
+        <v>147.0244662</v>
       </c>
       <c r="O43">
-        <v>38.73890974800001</v>
+        <v>41.16685053600001</v>
       </c>
       <c r="P43">
-        <v>99.61433935200002</v>
+        <v>105.857615664</v>
       </c>
       <c r="Q43">
-        <v>240.214339352</v>
+        <v>246.457615664</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.07467570853666</v>
+        <v>0.07465714402342551</v>
       </c>
       <c r="T43">
         <v>0.6664467441899656</v>
       </c>
       <c r="U43">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V43">
         <v>0.28</v>
       </c>
       <c r="W43">
-        <v>0.058968</v>
+        <v>0.054576</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.188379731712144</v>
+        <v>2.364489446269453</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.06831333889236532</v>
+        <v>0.06645778047548542</v>
       </c>
       <c r="C44">
-        <v>919.8435190332996</v>
+        <v>1127.199975966587</v>
       </c>
       <c r="D44">
-        <v>2328.9255190333</v>
+        <v>2536.281975966587</v>
       </c>
       <c r="E44">
         <v>173.2819999999999</v>
@@ -4901,37 +4901,37 @@
         <v>254.775</v>
       </c>
       <c r="M44">
-        <v>119.2613058</v>
+        <v>110.3785956</v>
       </c>
       <c r="N44">
-        <v>135.5136942</v>
+        <v>144.3964044</v>
       </c>
       <c r="O44">
-        <v>37.94383437600001</v>
+        <v>40.43099323200001</v>
       </c>
       <c r="P44">
-        <v>97.56985982399999</v>
+        <v>103.965411168</v>
       </c>
       <c r="Q44">
-        <v>238.169859824</v>
+        <v>244.565411168</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.07508065326269883</v>
+        <v>0.07506182840600933</v>
       </c>
       <c r="T44">
         <v>0.6757928038339341</v>
       </c>
       <c r="U44">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V44">
         <v>0.28</v>
       </c>
       <c r="W44">
-        <v>0.058968</v>
+        <v>0.054576</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.136275452385664</v>
+        <v>2.308192078501133</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.06839112974810126</v>
+        <v>0.0664916859771498</v>
       </c>
       <c r="C45">
-        <v>877.1530392157358</v>
+        <v>1088.373011447677</v>
       </c>
       <c r="D45">
-        <v>2320.906039215736</v>
+        <v>2532.126011447677</v>
       </c>
       <c r="E45">
         <v>207.9529999999997</v>
@@ -4983,37 +4983,37 @@
         <v>254.775</v>
       </c>
       <c r="M45">
-        <v>122.1008607</v>
+        <v>113.0066574</v>
       </c>
       <c r="N45">
-        <v>132.6741393</v>
+        <v>141.7683426</v>
       </c>
       <c r="O45">
-        <v>37.14875900400001</v>
+        <v>39.69513592800001</v>
       </c>
       <c r="P45">
-        <v>95.52538029600002</v>
+        <v>102.073206672</v>
       </c>
       <c r="Q45">
-        <v>236.125380296</v>
+        <v>242.673206672</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.07549980657561622</v>
+        <v>0.07548071224061367</v>
       </c>
       <c r="T45">
         <v>0.6854667953952349</v>
       </c>
       <c r="U45">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V45">
         <v>0.28</v>
       </c>
       <c r="W45">
-        <v>0.058968</v>
+        <v>0.054576</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.086594627911579</v>
+        <v>2.254513192954595</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.06846892060383718</v>
+        <v>0.06652559147881416</v>
       </c>
       <c r="C46">
-        <v>834.5175988249262</v>
+        <v>1049.559644616637</v>
       </c>
       <c r="D46">
-        <v>2312.941598824926</v>
+        <v>2527.983644616637</v>
       </c>
       <c r="E46">
         <v>242.6239999999998</v>
@@ -5065,37 +5065,37 @@
         <v>254.775</v>
       </c>
       <c r="M46">
-        <v>124.9404156</v>
+        <v>115.6347192</v>
       </c>
       <c r="N46">
-        <v>129.8345844</v>
+        <v>139.1402808</v>
       </c>
       <c r="O46">
-        <v>36.35368363200001</v>
+        <v>38.95927862400001</v>
       </c>
       <c r="P46">
-        <v>93.480900768</v>
+        <v>100.181002176</v>
       </c>
       <c r="Q46">
-        <v>234.080900768</v>
+        <v>240.781002176</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.07593392964970923</v>
+        <v>0.07591455621216815</v>
       </c>
       <c r="T46">
         <v>0.6954862866551537</v>
       </c>
       <c r="U46">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V46">
         <v>0.28</v>
       </c>
       <c r="W46">
-        <v>0.058968</v>
+        <v>0.054576</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.03917202273177</v>
+        <v>2.203274256751081</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.0738279114595731</v>
+        <v>0.06655949698047853</v>
       </c>
       <c r="C47">
-        <v>357.6076936595396</v>
+        <v>1010.759808848091</v>
       </c>
       <c r="D47">
-        <v>1870.70269365954</v>
+        <v>2523.854808848091</v>
       </c>
       <c r="E47">
         <v>277.2949999999998</v>
@@ -5147,45 +5147,45 @@
         <v>254.775</v>
       </c>
       <c r="M47">
-        <v>153.211149</v>
+        <v>118.262781</v>
       </c>
       <c r="N47">
-        <v>101.563851</v>
+        <v>136.512219</v>
       </c>
       <c r="O47">
-        <v>28.43787828</v>
+        <v>38.22342132000001</v>
       </c>
       <c r="P47">
-        <v>73.12597271999999</v>
+        <v>98.28879768000002</v>
       </c>
       <c r="Q47">
-        <v>213.72597272</v>
+        <v>238.88879768</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.07638383901740561</v>
+        <v>0.07636417632814278</v>
       </c>
       <c r="T47">
         <v>0.7058701230517964</v>
       </c>
       <c r="U47">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V47">
         <v>0.28</v>
       </c>
       <c r="W47">
-        <v>0.070704</v>
+        <v>0.054576</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.662901176989411</v>
+        <v>2.154312606601057</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.07402306231530902</v>
+        <v>0.0665934024821429</v>
       </c>
       <c r="C48">
-        <v>310.0015547502114</v>
+        <v>971.9734379512142</v>
       </c>
       <c r="D48">
-        <v>1857.767554750212</v>
+        <v>2519.739437951214</v>
       </c>
       <c r="E48">
         <v>311.9659999999999</v>
@@ -5229,45 +5229,45 @@
         <v>254.775</v>
       </c>
       <c r="M48">
-        <v>156.6158412</v>
+        <v>120.8908428</v>
       </c>
       <c r="N48">
-        <v>98.1591588</v>
+        <v>133.8841572</v>
       </c>
       <c r="O48">
-        <v>27.484564464</v>
+        <v>37.48756401600001</v>
       </c>
       <c r="P48">
-        <v>70.674594336</v>
+        <v>96.396593184</v>
       </c>
       <c r="Q48">
-        <v>211.274594336</v>
+        <v>236.996593184</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.07685041169501668</v>
+        <v>0.07683044904100537</v>
       </c>
       <c r="T48">
         <v>0.7166385459816484</v>
       </c>
       <c r="U48">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V48">
         <v>0.28</v>
       </c>
       <c r="W48">
-        <v>0.070704</v>
+        <v>0.054576</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>1.626751151402685</v>
+        <v>2.107479723848861</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07421821317104493</v>
+        <v>0.06662730798380728</v>
       </c>
       <c r="C49">
-        <v>262.573069756844</v>
+        <v>933.2004661662061</v>
       </c>
       <c r="D49">
-        <v>1845.010069756844</v>
+        <v>2515.637466166206</v>
       </c>
       <c r="E49">
         <v>346.6369999999999</v>
@@ -5311,45 +5311,45 @@
         <v>254.775</v>
       </c>
       <c r="M49">
-        <v>160.0205334</v>
+        <v>123.5189046</v>
       </c>
       <c r="N49">
-        <v>94.7544666</v>
+        <v>131.2560954</v>
       </c>
       <c r="O49">
-        <v>26.531250648</v>
+        <v>36.751706712</v>
       </c>
       <c r="P49">
-        <v>68.223215952</v>
+        <v>94.50438868799999</v>
       </c>
       <c r="Q49">
-        <v>208.823215952</v>
+        <v>235.104388688</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.07733459088876402</v>
+        <v>0.07731431695057976</v>
       </c>
       <c r="T49">
         <v>0.727813324493759</v>
       </c>
       <c r="U49">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.28</v>
       </c>
       <c r="W49">
-        <v>0.070704</v>
+        <v>0.054576</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.592139424777095</v>
+        <v>2.062639729724416</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.07441336402678085</v>
+        <v>0.06666121348547165</v>
       </c>
       <c r="C50">
-        <v>215.3186037366499</v>
+        <v>894.4408281607791</v>
       </c>
       <c r="D50">
-        <v>1832.42660373665</v>
+        <v>2511.548828160779</v>
       </c>
       <c r="E50">
         <v>381.3079999999998</v>
@@ -5393,45 +5393,45 @@
         <v>254.775</v>
       </c>
       <c r="M50">
-        <v>163.4252256</v>
+        <v>126.1469664</v>
       </c>
       <c r="N50">
-        <v>91.3497744</v>
+        <v>128.6280336</v>
       </c>
       <c r="O50">
-        <v>25.577936832</v>
+        <v>36.01584940800001</v>
       </c>
       <c r="P50">
-        <v>65.771837568</v>
+        <v>92.612184192</v>
       </c>
       <c r="Q50">
-        <v>206.371837568</v>
+        <v>233.212184192</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.07783739235919393</v>
+        <v>0.07781679516436854</v>
       </c>
       <c r="T50">
         <v>0.7394179021794122</v>
       </c>
       <c r="U50">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V50">
         <v>0.28</v>
       </c>
       <c r="W50">
-        <v>0.070704</v>
+        <v>0.054576</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.558969853427573</v>
+        <v>2.019668068688492</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.07460851488251677</v>
+        <v>0.07170487898713601</v>
       </c>
       <c r="C51">
-        <v>168.23462024025</v>
+        <v>370.7726710371908</v>
       </c>
       <c r="D51">
-        <v>1820.01362024025</v>
+        <v>2022.551671037191</v>
       </c>
       <c r="E51">
         <v>415.9789999999998</v>
@@ -5475,37 +5475,37 @@
         <v>254.775</v>
       </c>
       <c r="M51">
-        <v>166.8299178</v>
+        <v>152.89911</v>
       </c>
       <c r="N51">
-        <v>87.9450822</v>
+        <v>101.87589</v>
       </c>
       <c r="O51">
-        <v>24.624623016</v>
+        <v>28.52524920000001</v>
       </c>
       <c r="P51">
-        <v>63.320459184</v>
+        <v>73.35064080000001</v>
       </c>
       <c r="Q51">
-        <v>203.920459184</v>
+        <v>213.9506408</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.0783599115343466</v>
+        <v>0.07833897840614903</v>
       </c>
       <c r="T51">
         <v>0.7514775613429342</v>
       </c>
       <c r="U51">
-        <v>0.09820000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V51">
         <v>0.28</v>
       </c>
       <c r="W51">
-        <v>0.070704</v>
+        <v>0.0648</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.527154142133132</v>
+        <v>1.666294852860818</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.100950195475255</v>
+        <v>0.07184102448880039</v>
       </c>
       <c r="C52">
-        <v>-735.739145518988</v>
+        <v>325.5275359061432</v>
       </c>
       <c r="D52">
-        <v>950.7108544810119</v>
+        <v>2011.977535906143</v>
       </c>
       <c r="E52">
         <v>450.6499999999999</v>
@@ -5557,45 +5557,45 @@
         <v>254.775</v>
       </c>
       <c r="M52">
-        <v>283.60878</v>
+        <v>156.0195</v>
       </c>
       <c r="N52">
-        <v>-28.83377999999996</v>
+        <v>98.75550000000001</v>
       </c>
       <c r="O52">
-        <v>-8.073458399999991</v>
+        <v>27.65154000000001</v>
       </c>
       <c r="P52">
-        <v>-20.76032159999997</v>
+        <v>71.10396</v>
       </c>
       <c r="Q52">
-        <v>119.8396784</v>
+        <v>211.70396</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.0794512086367607</v>
+        <v>0.07888204897760077</v>
       </c>
       <c r="T52">
-        <v>0.7766645242853136</v>
+        <v>0.7640196068729972</v>
       </c>
       <c r="U52">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V52">
-        <v>0.2515331154416306</v>
+        <v>0.28</v>
       </c>
       <c r="W52">
-        <v>0.1224491823137492</v>
+        <v>0.0648</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.8983325551486806</v>
+        <v>1.632968955803602</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.102128195475255</v>
+        <v>0.07197716999046476</v>
       </c>
       <c r="C53">
-        <v>-790.2925042050676</v>
+        <v>280.3923913457056</v>
       </c>
       <c r="D53">
-        <v>930.8284957949323</v>
+        <v>2001.513391345705</v>
       </c>
       <c r="E53">
         <v>485.3209999999999</v>
@@ -5639,45 +5639,45 @@
         <v>254.775</v>
       </c>
       <c r="M53">
-        <v>289.2809556</v>
+        <v>159.13989</v>
       </c>
       <c r="N53">
-        <v>-34.50595559999996</v>
+        <v>95.63511</v>
       </c>
       <c r="O53">
-        <v>-9.661667567999991</v>
+        <v>26.7778308</v>
       </c>
       <c r="P53">
-        <v>-24.84428803199997</v>
+        <v>68.85727919999999</v>
       </c>
       <c r="Q53">
-        <v>115.755711968</v>
+        <v>209.4572792</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.08013796799669458</v>
+        <v>0.07944728569482604</v>
       </c>
       <c r="T53">
-        <v>0.7925148206992997</v>
+        <v>0.777073572628777</v>
       </c>
       <c r="U53">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V53">
-        <v>0.2466010935702261</v>
+        <v>0.28</v>
       </c>
       <c r="W53">
-        <v>0.123256061091911</v>
+        <v>0.0648</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>0.8807181913222359</v>
+        <v>1.600949956670197</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.103306195475255</v>
+        <v>0.07211331549212913</v>
       </c>
       <c r="C54">
-        <v>-844.0312926230702</v>
+        <v>235.3655300771313</v>
       </c>
       <c r="D54">
-        <v>911.7607073769299</v>
+        <v>1991.157530077131</v>
       </c>
       <c r="E54">
         <v>519.992</v>
@@ -5721,45 +5721,45 @@
         <v>254.775</v>
       </c>
       <c r="M54">
-        <v>294.9531312</v>
+        <v>162.26028</v>
       </c>
       <c r="N54">
-        <v>-40.17813119999997</v>
+        <v>92.51472000000001</v>
       </c>
       <c r="O54">
-        <v>-11.24987673599999</v>
+        <v>25.90412160000001</v>
       </c>
       <c r="P54">
-        <v>-28.92825446399998</v>
+        <v>66.6105984</v>
       </c>
       <c r="Q54">
-        <v>111.671745536</v>
+        <v>207.2105984</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.08085334232995905</v>
+        <v>0.08003607394193568</v>
       </c>
       <c r="T54">
-        <v>0.8090255461305351</v>
+        <v>0.7906714536243808</v>
       </c>
       <c r="U54">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V54">
-        <v>0.2418587648477217</v>
+        <v>0.28</v>
       </c>
       <c r="W54">
-        <v>0.1240319060709127</v>
+        <v>0.0648</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.8637813030275775</v>
+        <v>1.570162457503463</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.104484195475255</v>
+        <v>0.07224946099379351</v>
       </c>
       <c r="C55">
-        <v>-897.0045647185091</v>
+        <v>190.4452799737448</v>
       </c>
       <c r="D55">
-        <v>893.458435281491</v>
+        <v>1980.908279973745</v>
       </c>
       <c r="E55">
         <v>554.663</v>
@@ -5803,45 +5803,45 @@
         <v>254.775</v>
       </c>
       <c r="M55">
-        <v>300.6253068</v>
+        <v>165.38067</v>
       </c>
       <c r="N55">
-        <v>-45.85030680000003</v>
+        <v>89.39433</v>
       </c>
       <c r="O55">
-        <v>-12.83808590400001</v>
+        <v>25.0304124</v>
       </c>
       <c r="P55">
-        <v>-33.01222089600002</v>
+        <v>64.36391759999999</v>
       </c>
       <c r="Q55">
-        <v>107.587779104</v>
+        <v>204.9639176</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.08159915812421351</v>
+        <v>0.08064991700807128</v>
       </c>
       <c r="T55">
-        <v>0.8262388556226742</v>
+        <v>0.8048479678538403</v>
       </c>
       <c r="U55">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V55">
-        <v>0.2372953919260666</v>
+        <v>0.28</v>
       </c>
       <c r="W55">
-        <v>0.1247784738808955</v>
+        <v>0.0648</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.8474835425930948</v>
+        <v>1.540536750758115</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.105662195475255</v>
+        <v>0.07238560649545786</v>
       </c>
       <c r="C56">
-        <v>-949.2575131987757</v>
+        <v>145.6300031608696</v>
       </c>
       <c r="D56">
-        <v>875.8764868012245</v>
+        <v>1970.76400316087</v>
       </c>
       <c r="E56">
         <v>589.3340000000001</v>
@@ -5885,45 +5885,45 @@
         <v>254.775</v>
       </c>
       <c r="M56">
-        <v>306.2974824</v>
+        <v>168.50106</v>
       </c>
       <c r="N56">
-        <v>-51.52248240000003</v>
+        <v>86.27394000000001</v>
       </c>
       <c r="O56">
-        <v>-14.42629507200001</v>
+        <v>24.15670320000001</v>
       </c>
       <c r="P56">
-        <v>-37.09618732800002</v>
+        <v>62.1172368</v>
       </c>
       <c r="Q56">
-        <v>103.503812672</v>
+        <v>202.7172368</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.08237740069213118</v>
+        <v>0.08129044890316928</v>
       </c>
       <c r="T56">
-        <v>0.844200569875341</v>
+        <v>0.8196408522671891</v>
       </c>
       <c r="U56">
-        <v>0.1636</v>
+        <v>0.09</v>
       </c>
       <c r="V56">
-        <v>0.2329010328163246</v>
+        <v>0.28</v>
       </c>
       <c r="W56">
-        <v>0.1254973910312493</v>
+        <v>0.0648</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.8317894029154449</v>
+        <v>1.512008292410742</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.106840195475255</v>
+        <v>0.09731254861691108</v>
       </c>
       <c r="C57">
-        <v>-1000.831842118653</v>
+        <v>-842.6944572254245</v>
       </c>
       <c r="D57">
-        <v>858.973157881347</v>
+        <v>1017.110542774576</v>
       </c>
       <c r="E57">
         <v>624.0050000000001</v>
@@ -5967,37 +5967,37 @@
         <v>254.775</v>
       </c>
       <c r="M57">
-        <v>311.969658</v>
+        <v>279.933654</v>
       </c>
       <c r="N57">
-        <v>-57.19465800000003</v>
+        <v>-25.15865400000004</v>
       </c>
       <c r="O57">
-        <v>-16.01450424000001</v>
+        <v>-7.044423120000012</v>
       </c>
       <c r="P57">
-        <v>-41.18015376000002</v>
+        <v>-18.11423088000003</v>
       </c>
       <c r="Q57">
-        <v>99.41984623999997</v>
+        <v>122.48576912</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.08319023181862299</v>
+        <v>0.08255101657785875</v>
       </c>
       <c r="T57">
-        <v>0.8629605825392376</v>
+        <v>0.8487532696965071</v>
       </c>
       <c r="U57">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2286664685833005</v>
+        <v>0.2548353832440596</v>
       </c>
       <c r="W57">
-        <v>0.126190165739772</v>
+        <v>0.1093901657397721</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8166659592260731</v>
+        <v>0.9101263687287844</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.108018195475255</v>
+        <v>0.09832254861691106</v>
       </c>
       <c r="C58">
-        <v>-1051.766097140034</v>
+        <v>-896.9243262303366</v>
       </c>
       <c r="D58">
-        <v>842.7099028599658</v>
+        <v>997.5516737696635</v>
       </c>
       <c r="E58">
         <v>658.6759999999999</v>
@@ -6049,37 +6049,37 @@
         <v>254.775</v>
       </c>
       <c r="M58">
-        <v>317.6418336</v>
+        <v>285.0233568</v>
       </c>
       <c r="N58">
-        <v>-62.86683359999998</v>
+        <v>-30.24835680000004</v>
       </c>
       <c r="O58">
-        <v>-17.602713408</v>
+        <v>-8.469539904000012</v>
       </c>
       <c r="P58">
-        <v>-45.26412019199998</v>
+        <v>-21.77881689600003</v>
       </c>
       <c r="Q58">
-        <v>95.33587980800002</v>
+        <v>118.821183104</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.08404000981450077</v>
+        <v>0.08338626695462825</v>
       </c>
       <c r="T58">
-        <v>0.8825733230514928</v>
+        <v>0.868043116735064</v>
       </c>
       <c r="U58">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2245831387871702</v>
+        <v>0.2502847514004157</v>
       </c>
       <c r="W58">
-        <v>0.126858198494419</v>
+        <v>0.110058198494419</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8020826385256077</v>
+        <v>0.8938741121443419</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1395356962752855</v>
+        <v>0.09933254861691107</v>
       </c>
       <c r="C59">
-        <v>-1369.788169282073</v>
+        <v>-950.4161598453663</v>
       </c>
       <c r="D59">
-        <v>559.3588307179273</v>
+        <v>978.7308401546338</v>
       </c>
       <c r="E59">
         <v>693.347</v>
@@ -6131,45 +6131,45 @@
         <v>254.775</v>
       </c>
       <c r="M59">
-        <v>426.4741026</v>
+        <v>290.1130596</v>
       </c>
       <c r="N59">
-        <v>-171.6991026</v>
+        <v>-35.33805960000004</v>
       </c>
       <c r="O59">
-        <v>-48.07574872800001</v>
+        <v>-9.894656688000012</v>
       </c>
       <c r="P59">
-        <v>-123.623353872</v>
+        <v>-25.44340291200002</v>
       </c>
       <c r="Q59">
-        <v>16.97664612799997</v>
+        <v>115.156597088</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.08629094213583918</v>
+        <v>0.08426036618613125</v>
       </c>
       <c r="T59">
-        <v>0.9345244817578984</v>
+        <v>0.8882301659614609</v>
       </c>
       <c r="U59">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1672715871024615</v>
+        <v>0.2458937908495313</v>
       </c>
       <c r="W59">
-        <v>0.1797027915032888</v>
+        <v>0.1107027915032888</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.5973985253659339</v>
+        <v>0.8781921101768972</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1412356962752855</v>
+        <v>0.1003425486169111</v>
       </c>
       <c r="C60">
-        <v>-1414.423051239591</v>
+        <v>-1003.210958120712</v>
       </c>
       <c r="D60">
-        <v>549.3949487604092</v>
+        <v>960.6070418792874</v>
       </c>
       <c r="E60">
         <v>728.0179999999998</v>
@@ -6213,45 +6213,45 @@
         <v>254.775</v>
       </c>
       <c r="M60">
-        <v>433.9561044</v>
+        <v>295.2027624</v>
       </c>
       <c r="N60">
-        <v>-179.1811044</v>
+        <v>-40.42776240000003</v>
       </c>
       <c r="O60">
-        <v>-50.17070923200001</v>
+        <v>-11.31977347200001</v>
       </c>
       <c r="P60">
-        <v>-129.010395168</v>
+        <v>-29.10798892800003</v>
       </c>
       <c r="Q60">
-        <v>11.58960483199999</v>
+        <v>111.492011072</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.08725501218669249</v>
+        <v>0.08517608919056294</v>
       </c>
       <c r="T60">
-        <v>0.9567750646568958</v>
+        <v>0.9093785032462574</v>
       </c>
       <c r="U60">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1643875942213846</v>
+        <v>0.2416542427314359</v>
       </c>
       <c r="W60">
-        <v>0.1803251571670252</v>
+        <v>0.1113251571670252</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.5870985507906592</v>
+        <v>0.8630508668979853</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1429356962752855</v>
+        <v>0.1013525486169111</v>
       </c>
       <c r="C61">
-        <v>-1458.709171619701</v>
+        <v>-1055.346739421543</v>
       </c>
       <c r="D61">
-        <v>539.7798283802994</v>
+        <v>943.142260578457</v>
       </c>
       <c r="E61">
         <v>762.6889999999999</v>
@@ -6295,45 +6295,45 @@
         <v>254.775</v>
       </c>
       <c r="M61">
-        <v>441.4381062</v>
+        <v>300.2924652</v>
       </c>
       <c r="N61">
-        <v>-186.6631062</v>
+        <v>-45.51746520000003</v>
       </c>
       <c r="O61">
-        <v>-52.26566973600001</v>
+        <v>-12.74489025600001</v>
       </c>
       <c r="P61">
-        <v>-134.397436464</v>
+        <v>-32.77257494400002</v>
       </c>
       <c r="Q61">
-        <v>6.202563535999957</v>
+        <v>107.827425056</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.08826611004490449</v>
+        <v>0.08613648160984495</v>
       </c>
       <c r="T61">
-        <v>0.9801110418436493</v>
+        <v>0.9315584667400684</v>
       </c>
       <c r="U61">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1616013638108526</v>
+        <v>0.2375584081088692</v>
       </c>
       <c r="W61">
-        <v>0.180926425689618</v>
+        <v>0.111926425689618</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.5771477278959022</v>
+        <v>0.8484228861031042</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1446356962752855</v>
+        <v>0.102362548616911</v>
       </c>
       <c r="C62">
-        <v>-1502.664526795291</v>
+        <v>-1106.858806637871</v>
       </c>
       <c r="D62">
-        <v>530.4954732047091</v>
+        <v>926.3011933621291</v>
       </c>
       <c r="E62">
         <v>797.3599999999997</v>
@@ -6377,45 +6377,45 @@
         <v>254.775</v>
       </c>
       <c r="M62">
-        <v>448.920108</v>
+        <v>305.382168</v>
       </c>
       <c r="N62">
-        <v>-194.145108</v>
+        <v>-50.60716799999997</v>
       </c>
       <c r="O62">
-        <v>-54.36063023999999</v>
+        <v>-14.17000703999999</v>
       </c>
       <c r="P62">
-        <v>-139.78447776</v>
+        <v>-36.43716095999998</v>
       </c>
       <c r="Q62">
-        <v>0.8155222400000355</v>
+        <v>104.16283904</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.08932776279602711</v>
+        <v>0.08714489365009108</v>
       </c>
       <c r="T62">
-        <v>1.004613817889741</v>
+        <v>0.9548474284085701</v>
       </c>
       <c r="U62">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1589080077473385</v>
+        <v>0.2335991013070548</v>
       </c>
       <c r="W62">
-        <v>0.1815076519281244</v>
+        <v>0.1125076519281244</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.5675285990976373</v>
+        <v>0.8342825046680526</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1463356962752855</v>
+        <v>0.1033725486169111</v>
       </c>
       <c r="C63">
-        <v>-1546.305895906563</v>
+        <v>-1157.779985373591</v>
       </c>
       <c r="D63">
-        <v>521.5251040934371</v>
+        <v>910.0510146264085</v>
       </c>
       <c r="E63">
         <v>832.0309999999999</v>
@@ -6459,45 +6459,45 @@
         <v>254.775</v>
       </c>
       <c r="M63">
-        <v>456.4021098000001</v>
+        <v>310.4718708</v>
       </c>
       <c r="N63">
-        <v>-201.6271098000001</v>
+        <v>-55.69687080000003</v>
       </c>
       <c r="O63">
-        <v>-56.45559074400002</v>
+        <v>-15.59512382400001</v>
       </c>
       <c r="P63">
-        <v>-145.171519056</v>
+        <v>-40.10174697600002</v>
       </c>
       <c r="Q63">
-        <v>-4.571519056000028</v>
+        <v>100.498253024</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.09044385927797652</v>
+        <v>0.08820501912829855</v>
       </c>
       <c r="T63">
-        <v>1.03037314655358</v>
+        <v>0.9793306958036618</v>
       </c>
       <c r="U63">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.156302958440005</v>
+        <v>0.2297696078430046</v>
       </c>
       <c r="W63">
-        <v>0.182069821568647</v>
+        <v>0.1130698215686469</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.5582248515714463</v>
+        <v>0.820605742296445</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1480356962752855</v>
+        <v>0.1043825486169111</v>
       </c>
       <c r="C64">
-        <v>-1589.648942063235</v>
+        <v>-1208.140837496333</v>
       </c>
       <c r="D64">
-        <v>512.8530579367646</v>
+        <v>894.3611625036666</v>
       </c>
       <c r="E64">
         <v>866.7019999999998</v>
@@ -6541,45 +6541,45 @@
         <v>254.775</v>
       </c>
       <c r="M64">
-        <v>463.8841116</v>
+        <v>315.5615736</v>
       </c>
       <c r="N64">
-        <v>-209.1091116</v>
+        <v>-60.78657360000003</v>
       </c>
       <c r="O64">
-        <v>-58.55055124800001</v>
+        <v>-17.02024060800001</v>
       </c>
       <c r="P64">
-        <v>-150.558560352</v>
+        <v>-43.76633299200002</v>
       </c>
       <c r="Q64">
-        <v>-9.958560352000035</v>
+        <v>96.83366700799998</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.09161869768002853</v>
+        <v>0.0893209406843064</v>
       </c>
       <c r="T64">
-        <v>1.057488229357622</v>
+        <v>1.005102556219547</v>
       </c>
       <c r="U64">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1537819429812952</v>
+        <v>0.226063646426182</v>
       </c>
       <c r="W64">
-        <v>0.1826138567046365</v>
+        <v>0.1136138567046365</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.5492212249331972</v>
+        <v>0.8073701658077928</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1497356962752855</v>
+        <v>0.1401375125863306</v>
       </c>
       <c r="C65">
-        <v>-1632.70830361501</v>
+        <v>-1581.784641254574</v>
       </c>
       <c r="D65">
-        <v>504.4646963849901</v>
+        <v>555.3883587454258</v>
       </c>
       <c r="E65">
         <v>901.373</v>
@@ -6623,37 +6623,37 @@
         <v>254.775</v>
       </c>
       <c r="M65">
-        <v>471.3661134000001</v>
+        <v>438.6020184</v>
       </c>
       <c r="N65">
-        <v>-216.5911134000001</v>
+        <v>-183.8270184</v>
       </c>
       <c r="O65">
-        <v>-60.64551175200003</v>
+        <v>-51.47156515200001</v>
       </c>
       <c r="P65">
-        <v>-155.945601648</v>
+        <v>-132.355453248</v>
       </c>
       <c r="Q65">
-        <v>-15.34560164800004</v>
+        <v>8.244546751999991</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.09285704086056984</v>
+        <v>0.09245654440393518</v>
       </c>
       <c r="T65">
-        <v>1.086068992313233</v>
+        <v>1.077518346511205</v>
       </c>
       <c r="U65">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1513409597593699</v>
+        <v>0.1626463103390041</v>
       </c>
       <c r="W65">
-        <v>0.183140620883928</v>
+        <v>0.168140620883928</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5405034277120353</v>
+        <v>0.5808796797821576</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1514356962752855</v>
+        <v>0.1416875125863306</v>
       </c>
       <c r="C66">
-        <v>-1675.497676609112</v>
+        <v>-1625.433368727485</v>
       </c>
       <c r="D66">
-        <v>496.346323390888</v>
+        <v>546.4106312725146</v>
       </c>
       <c r="E66">
         <v>936.0439999999999</v>
@@ -6705,37 +6705,37 @@
         <v>254.775</v>
       </c>
       <c r="M66">
-        <v>478.8481152000001</v>
+        <v>445.5639552</v>
       </c>
       <c r="N66">
-        <v>-224.0731152</v>
+        <v>-190.7889552</v>
       </c>
       <c r="O66">
-        <v>-62.74047225600002</v>
+        <v>-53.42090745600001</v>
       </c>
       <c r="P66">
-        <v>-161.332642944</v>
+        <v>-137.368047744</v>
       </c>
       <c r="Q66">
-        <v>-20.73264294400005</v>
+        <v>3.231952256</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.09416418088447456</v>
+        <v>0.09375255952626671</v>
       </c>
       <c r="T66">
-        <v>1.116237575433045</v>
+        <v>1.107449411692072</v>
       </c>
       <c r="U66">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1489762572631298</v>
+        <v>0.1601049617399572</v>
       </c>
       <c r="W66">
-        <v>0.1836509236826166</v>
+        <v>0.1686509236826166</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5320580616540349</v>
+        <v>0.5718034347855614</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1531356962752855</v>
+        <v>0.1432375125863307</v>
       </c>
       <c r="C67">
-        <v>-1718.029889411985</v>
+        <v>-1668.796467447904</v>
       </c>
       <c r="D67">
-        <v>488.4851105880152</v>
+        <v>537.7185325520959</v>
       </c>
       <c r="E67">
         <v>970.7150000000001</v>
@@ -6787,37 +6787,37 @@
         <v>254.775</v>
       </c>
       <c r="M67">
-        <v>486.3301170000001</v>
+        <v>452.5258920000001</v>
       </c>
       <c r="N67">
-        <v>-231.5551170000001</v>
+        <v>-197.7508920000001</v>
       </c>
       <c r="O67">
-        <v>-64.83543276000003</v>
+        <v>-55.37024976000002</v>
       </c>
       <c r="P67">
-        <v>-166.71968424</v>
+        <v>-142.38064224</v>
       </c>
       <c r="Q67">
-        <v>-26.11968424000005</v>
+        <v>-1.780642240000049</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.09554601462403098</v>
+        <v>0.09512263265558862</v>
       </c>
       <c r="T67">
-        <v>1.148130077588275</v>
+        <v>1.139090823454703</v>
       </c>
       <c r="U67">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.146684314843697</v>
+        <v>0.1576418084824194</v>
       </c>
       <c r="W67">
-        <v>0.1841455248567302</v>
+        <v>0.1691455248567302</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5238725530132036</v>
+        <v>0.5630064588657835</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1548356962752855</v>
+        <v>0.1447875125863307</v>
       </c>
       <c r="C68">
-        <v>-1760.316970350314</v>
+        <v>-1711.887355004214</v>
       </c>
       <c r="D68">
-        <v>480.8690296496862</v>
+        <v>529.2986449957856</v>
       </c>
       <c r="E68">
         <v>1005.386</v>
@@ -6869,37 +6869,37 @@
         <v>254.775</v>
       </c>
       <c r="M68">
-        <v>493.8121188000001</v>
+        <v>459.4878288</v>
       </c>
       <c r="N68">
-        <v>-239.0371188000001</v>
+        <v>-204.7128288</v>
       </c>
       <c r="O68">
-        <v>-66.93039326400002</v>
+        <v>-57.31959206400002</v>
       </c>
       <c r="P68">
-        <v>-172.1067255360001</v>
+        <v>-147.393236736</v>
       </c>
       <c r="Q68">
-        <v>-31.50672553600006</v>
+        <v>-6.793236736000011</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.09700913270120837</v>
+        <v>0.09657329832192946</v>
       </c>
       <c r="T68">
-        <v>1.181898609282048</v>
+        <v>1.172593494732782</v>
       </c>
       <c r="U68">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1444618252248531</v>
+        <v>0.1552532962326858</v>
       </c>
       <c r="W68">
-        <v>0.1846251381164767</v>
+        <v>0.1696251381164767</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.515935090088761</v>
+        <v>0.5544760579738777</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1565356962752855</v>
+        <v>0.1463375125863307</v>
       </c>
       <c r="C69">
-        <v>-1802.37020912156</v>
+        <v>-1754.71862154193</v>
       </c>
       <c r="D69">
-        <v>473.4867908784393</v>
+        <v>521.1383784580696</v>
       </c>
       <c r="E69">
         <v>1040.057</v>
@@ -6951,37 +6951,37 @@
         <v>254.775</v>
       </c>
       <c r="M69">
-        <v>501.2941206</v>
+        <v>466.4497656</v>
       </c>
       <c r="N69">
-        <v>-246.5191206</v>
+        <v>-211.6747656</v>
       </c>
       <c r="O69">
-        <v>-69.02535376800002</v>
+        <v>-59.268934368</v>
       </c>
       <c r="P69">
-        <v>-177.493766832</v>
+        <v>-152.405831232</v>
       </c>
       <c r="Q69">
-        <v>-36.89376683200001</v>
+        <v>-11.80583123199997</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.09856092460124498</v>
+        <v>0.09811188311956369</v>
       </c>
       <c r="T69">
-        <v>1.217713718654231</v>
+        <v>1.208126630936806</v>
       </c>
       <c r="U69">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1423056785797061</v>
+        <v>0.1529360828560785</v>
       </c>
       <c r="W69">
-        <v>0.1850904345624994</v>
+        <v>0.1700904345624994</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.508234566356093</v>
+        <v>0.5462002959145662</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1582356962752855</v>
+        <v>0.1478875125863306</v>
       </c>
       <c r="C70">
-        <v>-1844.200212633422</v>
+        <v>-1797.302092579237</v>
       </c>
       <c r="D70">
-        <v>466.3277873665779</v>
+        <v>513.225907420763</v>
       </c>
       <c r="E70">
         <v>1074.728</v>
@@ -7033,37 +7033,37 @@
         <v>254.775</v>
       </c>
       <c r="M70">
-        <v>508.7761224000001</v>
+        <v>473.4117024</v>
       </c>
       <c r="N70">
-        <v>-254.0011224000001</v>
+        <v>-218.6367024</v>
       </c>
       <c r="O70">
-        <v>-71.12031427200003</v>
+        <v>-61.21827667200001</v>
       </c>
       <c r="P70">
-        <v>-182.880808128</v>
+        <v>-157.418425728</v>
       </c>
       <c r="Q70">
-        <v>-42.28080812800005</v>
+        <v>-16.81842572800002</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1002097034950339</v>
+        <v>0.09974662946705007</v>
       </c>
       <c r="T70">
-        <v>1.255767272362176</v>
+        <v>1.245880588153581</v>
       </c>
       <c r="U70">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1402129480123574</v>
+        <v>0.1506870228140774</v>
       </c>
       <c r="W70">
-        <v>0.1855420458189333</v>
+        <v>0.1705420458189333</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5007605286155622</v>
+        <v>0.5381679386217049</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1808596610230128</v>
+        <v>0.1494375125863306</v>
       </c>
       <c r="C71">
-        <v>-1956.986197835921</v>
+        <v>-1839.648886185722</v>
       </c>
       <c r="D71">
-        <v>388.2128021640791</v>
+        <v>505.5501138142779</v>
       </c>
       <c r="E71">
         <v>1109.399</v>
@@ -7115,45 +7115,45 @@
         <v>254.775</v>
       </c>
       <c r="M71">
-        <v>588.0270942000001</v>
+        <v>480.3736392</v>
       </c>
       <c r="N71">
-        <v>-333.2520942000001</v>
+        <v>-225.5986392</v>
       </c>
       <c r="O71">
-        <v>-93.31058637600003</v>
+        <v>-63.16761897600001</v>
       </c>
       <c r="P71">
-        <v>-239.9415078240001</v>
+        <v>-162.431020224</v>
       </c>
       <c r="Q71">
-        <v>-99.34150782400008</v>
+        <v>-21.83102022400001</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1026873221488328</v>
+        <v>0.1014868433208259</v>
       </c>
       <c r="T71">
-        <v>1.312950315440487</v>
+        <v>1.286070284545632</v>
       </c>
       <c r="U71">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1213158385108983</v>
+        <v>0.1485031529182212</v>
       </c>
       <c r="W71">
-        <v>0.2159805668940212</v>
+        <v>0.1709805668940212</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.4332708518246368</v>
+        <v>0.5303684032793613</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1828596610230128</v>
+        <v>0.1509875125863306</v>
       </c>
       <c r="C72">
-        <v>-1997.32207106363</v>
+        <v>-1881.76946510574</v>
       </c>
       <c r="D72">
-        <v>382.54792893637</v>
+        <v>498.1005348942609</v>
       </c>
       <c r="E72">
         <v>1144.07</v>
@@ -7197,45 +7197,45 @@
         <v>254.775</v>
       </c>
       <c r="M72">
-        <v>596.5492260000001</v>
+        <v>487.3355760000001</v>
       </c>
       <c r="N72">
-        <v>-341.7742260000001</v>
+        <v>-232.5605760000001</v>
       </c>
       <c r="O72">
-        <v>-95.69678328000003</v>
+        <v>-65.11696128000003</v>
       </c>
       <c r="P72">
-        <v>-246.0774427200001</v>
+        <v>-167.44361472</v>
       </c>
       <c r="Q72">
-        <v>-105.4774427200001</v>
+        <v>-26.84361472000003</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1045835662204605</v>
+        <v>0.1033430714315201</v>
       </c>
       <c r="T72">
-        <v>1.35671532595517</v>
+        <v>1.328939294030487</v>
       </c>
       <c r="U72">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1195827551035998</v>
+        <v>0.1463816793051037</v>
       </c>
       <c r="W72">
-        <v>0.2164065587955352</v>
+        <v>0.1714065587955352</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y72">
-        <v>0.427081268227142</v>
+        <v>0.5227917118039418</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1848596610230128</v>
+        <v>0.1525375125863306</v>
       </c>
       <c r="C73">
-        <v>-2037.494996296614</v>
+        <v>-1923.673684340276</v>
       </c>
       <c r="D73">
-        <v>377.0460037033859</v>
+        <v>490.8673156597239</v>
       </c>
       <c r="E73">
         <v>1178.741</v>
@@ -7279,45 +7279,45 @@
         <v>254.775</v>
       </c>
       <c r="M73">
-        <v>605.0713578</v>
+        <v>494.2975127999999</v>
       </c>
       <c r="N73">
-        <v>-350.2963578</v>
+        <v>-239.5225127999999</v>
       </c>
       <c r="O73">
-        <v>-98.08298018400001</v>
+        <v>-67.06630358399998</v>
       </c>
       <c r="P73">
-        <v>-252.213377616</v>
+        <v>-172.4562092159999</v>
       </c>
       <c r="Q73">
-        <v>-111.613377616</v>
+        <v>-31.85620921599994</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.106610585745304</v>
+        <v>0.1053273152739863</v>
       </c>
       <c r="T73">
-        <v>1.403498613057072</v>
+        <v>1.374764786928089</v>
       </c>
       <c r="U73">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1178984909472111</v>
+        <v>0.1443199655120741</v>
       </c>
       <c r="W73">
-        <v>0.2168205509251755</v>
+        <v>0.1718205509251755</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.4210660390971823</v>
+        <v>0.5154284482574075</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1868596610230128</v>
+        <v>0.1540875125863307</v>
       </c>
       <c r="C74">
-        <v>-2077.511904559386</v>
+        <v>-1965.37083464238</v>
       </c>
       <c r="D74">
-        <v>371.7000954406136</v>
+        <v>483.8411653576194</v>
       </c>
       <c r="E74">
         <v>1213.412</v>
@@ -7361,45 +7361,45 @@
         <v>254.775</v>
       </c>
       <c r="M74">
-        <v>613.5934896</v>
+        <v>501.2594496</v>
       </c>
       <c r="N74">
-        <v>-358.8184896</v>
+        <v>-246.4844496</v>
       </c>
       <c r="O74">
-        <v>-100.469177088</v>
+        <v>-69.01564588799999</v>
       </c>
       <c r="P74">
-        <v>-258.349312512</v>
+        <v>-177.468803712</v>
       </c>
       <c r="Q74">
-        <v>-117.749312512</v>
+        <v>-36.86880371199999</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1087823923790648</v>
+        <v>0.1074532908194858</v>
       </c>
       <c r="T74">
-        <v>1.453623563523396</v>
+        <v>1.423863529318378</v>
       </c>
       <c r="U74">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1162610119062776</v>
+        <v>0.1423155215466286</v>
       </c>
       <c r="W74">
-        <v>0.217223043273437</v>
+        <v>0.172223043273437</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.415217899665277</v>
+        <v>0.508269719809388</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1888596610230128</v>
+        <v>0.1556375125863306</v>
       </c>
       <c r="C75">
-        <v>-2117.379339288542</v>
+        <v>-2006.869682329798</v>
       </c>
       <c r="D75">
-        <v>366.5036607114578</v>
+        <v>477.0133176702016</v>
       </c>
       <c r="E75">
         <v>1248.083</v>
@@ -7443,45 +7443,45 @@
         <v>254.775</v>
       </c>
       <c r="M75">
-        <v>622.1156214</v>
+        <v>508.2213864</v>
       </c>
       <c r="N75">
-        <v>-367.3406214</v>
+        <v>-253.4463864</v>
       </c>
       <c r="O75">
-        <v>-102.855373992</v>
+        <v>-70.96498819199999</v>
       </c>
       <c r="P75">
-        <v>-264.485247408</v>
+        <v>-182.481398208</v>
       </c>
       <c r="Q75">
-        <v>-123.885247408</v>
+        <v>-41.88139820799998</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1111150735782895</v>
+        <v>0.1097367460350223</v>
       </c>
       <c r="T75">
-        <v>1.507461473283522</v>
+        <v>1.476599215589429</v>
       </c>
       <c r="U75">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1146683953048217</v>
+        <v>0.1403659938542091</v>
       </c>
       <c r="W75">
-        <v>0.2176145084340748</v>
+        <v>0.1726145084340748</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.409529983231506</v>
+        <v>0.5013071209078894</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1908596610230127</v>
+        <v>0.1833800443045851</v>
       </c>
       <c r="C76">
-        <v>-2157.103483051967</v>
+        <v>-2137.728738979918</v>
       </c>
       <c r="D76">
-        <v>361.4505169480332</v>
+        <v>380.8252610200823</v>
       </c>
       <c r="E76">
         <v>1282.754</v>
@@ -7525,37 +7525,37 @@
         <v>254.775</v>
       </c>
       <c r="M76">
-        <v>630.6377532</v>
+        <v>604.9812132000001</v>
       </c>
       <c r="N76">
-        <v>-375.8627532</v>
+        <v>-350.2062132000001</v>
       </c>
       <c r="O76">
-        <v>-105.241570896</v>
+        <v>-98.05773969600004</v>
       </c>
       <c r="P76">
-        <v>-270.621182304</v>
+        <v>-252.148473504</v>
       </c>
       <c r="Q76">
-        <v>-130.021182304</v>
+        <v>-111.548473504</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.113627191792839</v>
+        <v>0.1133209736450403</v>
       </c>
       <c r="T76">
-        <v>1.565440760717503</v>
+        <v>1.559375834758437</v>
       </c>
       <c r="U76">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1131188223952971</v>
+        <v>0.1179160582899238</v>
       </c>
       <c r="W76">
-        <v>0.217995393455236</v>
+        <v>0.207995393455236</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4039957942689182</v>
+        <v>0.4211287796068706</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1928596610230128</v>
+        <v>0.1852800443045851</v>
       </c>
       <c r="C77">
-        <v>-2196.690182087767</v>
+        <v>-2177.587348430041</v>
       </c>
       <c r="D77">
-        <v>356.5348179122321</v>
+        <v>375.6376515699585</v>
       </c>
       <c r="E77">
         <v>1317.425</v>
@@ -7607,37 +7607,37 @@
         <v>254.775</v>
       </c>
       <c r="M77">
-        <v>639.159885</v>
+        <v>613.1566349999999</v>
       </c>
       <c r="N77">
-        <v>-384.3848850000001</v>
+        <v>-358.381635</v>
       </c>
       <c r="O77">
-        <v>-107.6277678</v>
+        <v>-100.3468578</v>
       </c>
       <c r="P77">
-        <v>-276.7571172</v>
+        <v>-258.0347772</v>
       </c>
       <c r="Q77">
-        <v>-136.1571172</v>
+        <v>-117.4347772</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1163402794645526</v>
+        <v>0.1160218125908419</v>
       </c>
       <c r="T77">
-        <v>1.628058391146204</v>
+        <v>1.621750868148775</v>
       </c>
       <c r="U77">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1116105714300265</v>
+        <v>0.1163438441793915</v>
       </c>
       <c r="W77">
-        <v>0.2183661215424995</v>
+        <v>0.2083661215424995</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3986091836786659</v>
+        <v>0.4155137292121124</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1948596610230128</v>
+        <v>0.1871800443045851</v>
       </c>
       <c r="C78">
-        <v>-2236.144968867709</v>
+        <v>-2217.306525784162</v>
       </c>
       <c r="D78">
-        <v>351.7510311322906</v>
+        <v>370.5894742158381</v>
       </c>
       <c r="E78">
         <v>1352.096</v>
@@ -7689,37 +7689,37 @@
         <v>254.775</v>
       </c>
       <c r="M78">
-        <v>647.6820168</v>
+        <v>621.3320568</v>
       </c>
       <c r="N78">
-        <v>-392.9070168000001</v>
+        <v>-366.5570568000001</v>
       </c>
       <c r="O78">
-        <v>-110.013964704</v>
+        <v>-102.635975904</v>
       </c>
       <c r="P78">
-        <v>-282.893052096</v>
+        <v>-263.921080896</v>
       </c>
       <c r="Q78">
-        <v>-142.293052096</v>
+        <v>-123.321080896</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1192794577755756</v>
+        <v>0.1189477214487937</v>
       </c>
       <c r="T78">
-        <v>1.695894157443962</v>
+        <v>1.689323820988307</v>
       </c>
       <c r="U78">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1101420112796314</v>
+        <v>0.1148130041243995</v>
       </c>
       <c r="W78">
-        <v>0.2187270936274666</v>
+        <v>0.2087270936274666</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3933643259986834</v>
+        <v>0.4100464433014266</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1968596610230128</v>
+        <v>0.1890800443045851</v>
       </c>
       <c r="C79">
-        <v>-2275.473082868232</v>
+        <v>-2256.891817962306</v>
       </c>
       <c r="D79">
-        <v>347.0939171317675</v>
+        <v>365.6751820376944</v>
       </c>
       <c r="E79">
         <v>1386.767</v>
@@ -7771,37 +7771,37 @@
         <v>254.775</v>
       </c>
       <c r="M79">
-        <v>656.2041486000001</v>
+        <v>629.5074786</v>
       </c>
       <c r="N79">
-        <v>-401.4291486000001</v>
+        <v>-374.7324786</v>
       </c>
       <c r="O79">
-        <v>-112.400161608</v>
+        <v>-104.925094008</v>
       </c>
       <c r="P79">
-        <v>-289.0289869920001</v>
+        <v>-269.807384592</v>
       </c>
       <c r="Q79">
-        <v>-148.4289869920001</v>
+        <v>-129.207384592</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1224742168092963</v>
+        <v>0.1221280571639586</v>
       </c>
       <c r="T79">
-        <v>1.769628686028482</v>
+        <v>1.762772682770408</v>
       </c>
       <c r="U79">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1087115955487271</v>
+        <v>0.1133219261487579</v>
       </c>
       <c r="W79">
-        <v>0.2190786898141229</v>
+        <v>0.2090786898141229</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3882556983883109</v>
+        <v>0.4047211648169925</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1988596610230128</v>
+        <v>0.1909800443045851</v>
       </c>
       <c r="C80">
-        <v>-2314.679489713013</v>
+        <v>-2296.348481509935</v>
       </c>
       <c r="D80">
-        <v>342.5585102869869</v>
+        <v>360.8895184900655</v>
       </c>
       <c r="E80">
         <v>1421.438</v>
@@ -7853,37 +7853,37 @@
         <v>254.775</v>
       </c>
       <c r="M80">
-        <v>664.7262804000001</v>
+        <v>637.6829004000001</v>
       </c>
       <c r="N80">
-        <v>-409.9512804000001</v>
+        <v>-382.9079004000001</v>
       </c>
       <c r="O80">
-        <v>-114.786358512</v>
+        <v>-107.214212112</v>
       </c>
       <c r="P80">
-        <v>-295.164921888</v>
+        <v>-275.6936882880001</v>
       </c>
       <c r="Q80">
-        <v>-154.564921888</v>
+        <v>-135.0936882880001</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1259594084824462</v>
+        <v>0.1255975143077749</v>
       </c>
       <c r="T80">
-        <v>1.850066353575232</v>
+        <v>1.842898713805426</v>
       </c>
       <c r="U80">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1073178571442562</v>
+        <v>0.1118690809417225</v>
       </c>
       <c r="W80">
-        <v>0.2194212707139418</v>
+        <v>0.2094212707139418</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3832780612294864</v>
+        <v>0.3995324319347233</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2008596610230128</v>
+        <v>0.1928800443045851</v>
       </c>
       <c r="C81">
-        <v>-2353.768898834082</v>
+        <v>-2335.681501353436</v>
       </c>
       <c r="D81">
-        <v>338.1401011659177</v>
+        <v>356.2274986465637</v>
       </c>
       <c r="E81">
         <v>1456.109</v>
@@ -7935,37 +7935,37 @@
         <v>254.775</v>
       </c>
       <c r="M81">
-        <v>673.2484122000001</v>
+        <v>645.8583222</v>
       </c>
       <c r="N81">
-        <v>-418.4734122000001</v>
+        <v>-391.0833222</v>
       </c>
       <c r="O81">
-        <v>-117.172555416</v>
+        <v>-109.503330216</v>
       </c>
       <c r="P81">
-        <v>-301.3008567840001</v>
+        <v>-281.579991984</v>
       </c>
       <c r="Q81">
-        <v>-160.7008567840001</v>
+        <v>-140.979991984</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1297765231720865</v>
+        <v>0.1293973959414785</v>
       </c>
       <c r="T81">
-        <v>1.938164751364529</v>
+        <v>1.930655795415209</v>
       </c>
       <c r="U81">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1059594032563542</v>
+        <v>0.1104530166260046</v>
       </c>
       <c r="W81">
-        <v>0.2197551786795882</v>
+        <v>0.2097551786795881</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.378426440201265</v>
+        <v>0.3944750593785876</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2028596610230128</v>
+        <v>0.1947800443045851</v>
       </c>
       <c r="C82">
-        <v>-2392.745779783569</v>
+        <v>-2374.895608120439</v>
       </c>
       <c r="D82">
-        <v>333.834220216431</v>
+        <v>351.6843918795613</v>
       </c>
       <c r="E82">
         <v>1490.78</v>
@@ -8017,37 +8017,37 @@
         <v>254.775</v>
       </c>
       <c r="M82">
-        <v>681.7705440000001</v>
+        <v>654.0337440000001</v>
       </c>
       <c r="N82">
-        <v>-426.9955440000001</v>
+        <v>-399.2587440000001</v>
       </c>
       <c r="O82">
-        <v>-119.55875232</v>
+        <v>-111.79244832</v>
       </c>
       <c r="P82">
-        <v>-307.4367916800001</v>
+        <v>-287.46629568</v>
       </c>
       <c r="Q82">
-        <v>-166.8367916800001</v>
+        <v>-146.86629568</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1339753493306908</v>
+        <v>0.1335772657385524</v>
       </c>
       <c r="T82">
-        <v>2.035072988932755</v>
+        <v>2.027188585185969</v>
       </c>
       <c r="U82">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1046349107156498</v>
+        <v>0.1090723539181795</v>
       </c>
       <c r="W82">
-        <v>0.2200807389460933</v>
+        <v>0.2100807389460933</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3736961096987492</v>
+        <v>0.3895441211363553</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2048596610230128</v>
+        <v>0.1966800443045851</v>
       </c>
       <c r="C83">
-        <v>-2431.614377314827</v>
+        <v>-2413.995294151457</v>
       </c>
       <c r="D83">
-        <v>329.6366226851733</v>
+        <v>347.2557058485428</v>
       </c>
       <c r="E83">
         <v>1525.451</v>
@@ -8099,37 +8099,37 @@
         <v>254.775</v>
       </c>
       <c r="M83">
-        <v>690.2926758000001</v>
+        <v>662.2091658000001</v>
       </c>
       <c r="N83">
-        <v>-435.5176758000001</v>
+        <v>-407.4341658000001</v>
       </c>
       <c r="O83">
-        <v>-121.944949224</v>
+        <v>-114.081566424</v>
       </c>
       <c r="P83">
-        <v>-313.5727265760001</v>
+        <v>-293.3525993760001</v>
       </c>
       <c r="Q83">
-        <v>-172.9727265760001</v>
+        <v>-152.7525993760001</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1386161571902008</v>
+        <v>0.1381971218300552</v>
       </c>
       <c r="T83">
-        <v>2.142182093613426</v>
+        <v>2.133882721248388</v>
       </c>
       <c r="U83">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.103343121694469</v>
+        <v>0.1077257816475847</v>
       </c>
       <c r="W83">
-        <v>0.2203982606874996</v>
+        <v>0.2103982606874995</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3690825774802462</v>
+        <v>0.3847349344556595</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2068596610230128</v>
+        <v>0.1985800443045851</v>
       </c>
       <c r="C84">
-        <v>-2470.378725339917</v>
+        <v>-2452.984828316802</v>
       </c>
       <c r="D84">
-        <v>325.5432746600825</v>
+        <v>342.9371716831979</v>
       </c>
       <c r="E84">
         <v>1560.122</v>
@@ -8181,37 +8181,37 @@
         <v>254.775</v>
       </c>
       <c r="M84">
-        <v>698.8148076</v>
+        <v>670.3845876</v>
       </c>
       <c r="N84">
-        <v>-444.0398076</v>
+        <v>-415.6095876000001</v>
       </c>
       <c r="O84">
-        <v>-124.331146128</v>
+        <v>-116.370684528</v>
       </c>
       <c r="P84">
-        <v>-319.708661472</v>
+        <v>-299.238903072</v>
       </c>
       <c r="Q84">
-        <v>-179.108661472</v>
+        <v>-158.638903072</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1437726103674342</v>
+        <v>0.1433302952650583</v>
       </c>
       <c r="T84">
-        <v>2.261192209925284</v>
+        <v>2.252431761317744</v>
       </c>
       <c r="U84">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1020828397225852</v>
+        <v>0.1064120526031019</v>
       </c>
       <c r="W84">
-        <v>0.2207080379961886</v>
+        <v>0.2107080379961886</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3645815704378041</v>
+        <v>0.3800430450110783</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2088596610230128</v>
+        <v>0.2004800443045852</v>
       </c>
       <c r="C85">
-        <v>-2509.042659859929</v>
+        <v>-2491.86826974147</v>
       </c>
       <c r="D85">
-        <v>321.5503401400712</v>
+        <v>338.7247302585301</v>
       </c>
       <c r="E85">
         <v>1594.793</v>
@@ -8263,37 +8263,37 @@
         <v>254.775</v>
       </c>
       <c r="M85">
-        <v>707.3369394000001</v>
+        <v>678.5600094000001</v>
       </c>
       <c r="N85">
-        <v>-452.5619394000001</v>
+        <v>-423.7850094000001</v>
       </c>
       <c r="O85">
-        <v>-126.717343032</v>
+        <v>-118.6598026320001</v>
       </c>
       <c r="P85">
-        <v>-325.8445963680001</v>
+        <v>-305.1252067680001</v>
       </c>
       <c r="Q85">
-        <v>-185.2445963680001</v>
+        <v>-164.5252067680001</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1495357050949304</v>
+        <v>0.1490673714571205</v>
       </c>
       <c r="T85">
-        <v>2.394203516391477</v>
+        <v>2.384927747277611</v>
       </c>
       <c r="U85">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1008529259909878</v>
+        <v>0.105129979680173</v>
       </c>
       <c r="W85">
-        <v>0.2210103507914152</v>
+        <v>0.2110103507914152</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3601890213963848</v>
+        <v>0.3754642131434749</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2108596610230128</v>
+        <v>0.2023800443045851</v>
       </c>
       <c r="C86">
-        <v>-2547.609830955243</v>
+        <v>-2530.649480530779</v>
       </c>
       <c r="D86">
-        <v>317.6541690447572</v>
+        <v>334.6145194692211</v>
       </c>
       <c r="E86">
         <v>1629.464</v>
@@ -8345,37 +8345,37 @@
         <v>254.775</v>
       </c>
       <c r="M86">
-        <v>715.8590712</v>
+        <v>686.7354312</v>
       </c>
       <c r="N86">
-        <v>-461.0840712</v>
+        <v>-431.9604312</v>
       </c>
       <c r="O86">
-        <v>-129.103539936</v>
+        <v>-120.948920736</v>
       </c>
       <c r="P86">
-        <v>-331.980531264</v>
+        <v>-311.011510464</v>
       </c>
       <c r="Q86">
-        <v>-191.380531264</v>
+        <v>-170.411510464</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.1560191866633635</v>
+        <v>0.1555215821731905</v>
       </c>
       <c r="T86">
-        <v>2.543841236165943</v>
+        <v>2.53398573148246</v>
       </c>
       <c r="U86">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0996522959196665</v>
+        <v>0.1038784323030281</v>
       </c>
       <c r="W86">
-        <v>0.221305465662946</v>
+        <v>0.211305465662946</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3559010568559517</v>
+        <v>0.3709944010822431</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2128596610230128</v>
+        <v>0.2042800443045851</v>
       </c>
       <c r="C87">
-        <v>-2586.083713914535</v>
+        <v>-2569.332137580607</v>
       </c>
       <c r="D87">
-        <v>313.8512860854653</v>
+        <v>330.6028624193932</v>
       </c>
       <c r="E87">
         <v>1664.135</v>
@@ -8427,37 +8427,37 @@
         <v>254.775</v>
       </c>
       <c r="M87">
-        <v>724.381203</v>
+        <v>694.910853</v>
       </c>
       <c r="N87">
-        <v>-469.6062030000001</v>
+        <v>-440.135853</v>
       </c>
       <c r="O87">
-        <v>-131.48973684</v>
+        <v>-123.23803884</v>
       </c>
       <c r="P87">
-        <v>-338.11646616</v>
+        <v>-316.89781416</v>
       </c>
       <c r="Q87">
-        <v>-197.51646616</v>
+        <v>-176.29781416</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.163367132440921</v>
+        <v>0.1628363543180699</v>
       </c>
       <c r="T87">
-        <v>2.713430651910339</v>
+        <v>2.702918113581291</v>
       </c>
       <c r="U87">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.09847991596767042</v>
+        <v>0.1026563330994631</v>
       </c>
       <c r="W87">
-        <v>0.2215936366551466</v>
+        <v>0.2115936366551466</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3517139855988228</v>
+        <v>0.3666297610695108</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2148596610230128</v>
+        <v>0.2061800443045851</v>
       </c>
       <c r="C88">
-        <v>-2624.46761957383</v>
+        <v>-2607.919743548141</v>
       </c>
       <c r="D88">
-        <v>310.1383804261696</v>
+        <v>326.6862564518585</v>
       </c>
       <c r="E88">
         <v>1698.806</v>
@@ -8509,37 +8509,37 @@
         <v>254.775</v>
       </c>
       <c r="M88">
-        <v>732.9033347999999</v>
+        <v>703.0862748</v>
       </c>
       <c r="N88">
-        <v>-478.1283347999999</v>
+        <v>-448.3112748</v>
       </c>
       <c r="O88">
-        <v>-133.875933744</v>
+        <v>-125.527156944</v>
       </c>
       <c r="P88">
-        <v>-344.2524010559999</v>
+        <v>-322.784117856</v>
       </c>
       <c r="Q88">
-        <v>-203.6524010559999</v>
+        <v>-182.184117856</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.1717647847581297</v>
+        <v>0.1711960939122177</v>
       </c>
       <c r="T88">
-        <v>2.907247127046792</v>
+        <v>2.895983693122812</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.09733480066572077</v>
+        <v>0.1014626548076088</v>
       </c>
       <c r="W88">
-        <v>0.2218751059963659</v>
+        <v>0.2118751059963658</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3476242880918599</v>
+        <v>0.3623666243128887</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2168596610230128</v>
+        <v>0.2080800443045851</v>
       </c>
       <c r="C89">
-        <v>-2662.764703930263</v>
+        <v>-2646.415637051951</v>
       </c>
       <c r="D89">
-        <v>306.5122960697366</v>
+        <v>322.8613629480488</v>
       </c>
       <c r="E89">
         <v>1733.477</v>
@@ -8591,37 +8591,37 @@
         <v>254.775</v>
       </c>
       <c r="M89">
-        <v>741.4254666</v>
+        <v>711.2616966000001</v>
       </c>
       <c r="N89">
-        <v>-486.6504666000001</v>
+        <v>-456.4866966000001</v>
       </c>
       <c r="O89">
-        <v>-136.262130648</v>
+        <v>-127.816275048</v>
       </c>
       <c r="P89">
-        <v>-350.388335952</v>
+        <v>-328.6704215520001</v>
       </c>
       <c r="Q89">
-        <v>-209.788335952</v>
+        <v>-188.0704215520001</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.1814543835856781</v>
+        <v>0.1808419472900807</v>
       </c>
       <c r="T89">
-        <v>3.130881521435007</v>
+        <v>3.118751669516875</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.09621600985347109</v>
+        <v>0.1002964173960271</v>
       </c>
       <c r="W89">
-        <v>0.2221501047780168</v>
+        <v>0.2121501047780168</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3436286066195395</v>
+        <v>0.3582014907000968</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2188596610230128</v>
+        <v>0.2099800443045851</v>
       </c>
       <c r="C90">
-        <v>-2700.977977089217</v>
+        <v>-2684.823002163799</v>
       </c>
       <c r="D90">
-        <v>302.9700229107824</v>
+        <v>319.1249978362011</v>
       </c>
       <c r="E90">
         <v>1768.148</v>
@@ -8673,37 +8673,37 @@
         <v>254.775</v>
       </c>
       <c r="M90">
-        <v>749.9475983999999</v>
+        <v>719.4371184</v>
       </c>
       <c r="N90">
-        <v>-495.1725984</v>
+        <v>-464.6621184000001</v>
       </c>
       <c r="O90">
-        <v>-138.648327552</v>
+        <v>-130.105393152</v>
       </c>
       <c r="P90">
-        <v>-356.524270848</v>
+        <v>-334.556725248</v>
       </c>
       <c r="Q90">
-        <v>-215.924270848</v>
+        <v>-193.956725248</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.1927589155511513</v>
+        <v>0.1920954428975874</v>
       </c>
       <c r="T90">
-        <v>3.391788314887925</v>
+        <v>3.378647641976615</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09512264610513621</v>
+        <v>0.09915668538016317</v>
       </c>
       <c r="W90">
-        <v>0.2224188535873575</v>
+        <v>0.2124188535873575</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3397237360897721</v>
+        <v>0.3541310192148684</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2208596610230128</v>
+        <v>0.2118800443045851</v>
       </c>
       <c r="C91">
-        <v>-2739.110311598154</v>
+        <v>-2723.144877248928</v>
       </c>
       <c r="D91">
-        <v>299.5086884018465</v>
+        <v>315.4741227510716</v>
       </c>
       <c r="E91">
         <v>1802.819</v>
@@ -8755,37 +8755,37 @@
         <v>254.775</v>
       </c>
       <c r="M91">
-        <v>758.4697302000001</v>
+        <v>727.6125402</v>
       </c>
       <c r="N91">
-        <v>-503.6947302000001</v>
+        <v>-472.8375402</v>
       </c>
       <c r="O91">
-        <v>-141.034524456</v>
+        <v>-132.394511256</v>
       </c>
       <c r="P91">
-        <v>-362.6602057440001</v>
+        <v>-340.443028944</v>
       </c>
       <c r="Q91">
-        <v>-222.0602057440001</v>
+        <v>-199.8430289440001</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2061188169648923</v>
+        <v>0.2053950286155499</v>
       </c>
       <c r="T91">
-        <v>3.700132707150463</v>
+        <v>3.685797427610852</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09405385232867398</v>
+        <v>0.09804256531971191</v>
       </c>
       <c r="W91">
-        <v>0.2226815630976119</v>
+        <v>0.2126815630976119</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3359066154595499</v>
+        <v>0.3501520189989711</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2228596610230127</v>
+        <v>0.2137800443045851</v>
       </c>
       <c r="C92">
-        <v>-2777.164450215626</v>
+        <v>-2761.384163206397</v>
       </c>
       <c r="D92">
-        <v>296.1255497843736</v>
+        <v>311.9058367936028</v>
       </c>
       <c r="E92">
         <v>1837.49</v>
@@ -8837,37 +8837,37 @@
         <v>254.775</v>
       </c>
       <c r="M92">
-        <v>766.9918620000001</v>
+        <v>735.787962</v>
       </c>
       <c r="N92">
-        <v>-512.2168620000001</v>
+        <v>-481.012962</v>
       </c>
       <c r="O92">
-        <v>-143.42072136</v>
+        <v>-134.68362936</v>
       </c>
       <c r="P92">
-        <v>-368.7961406400001</v>
+        <v>-346.32933264</v>
       </c>
       <c r="Q92">
-        <v>-228.1961406400001</v>
+        <v>-205.72933264</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2221506986613816</v>
+        <v>0.2213545314771049</v>
       </c>
       <c r="T92">
-        <v>4.07014597786551</v>
+        <v>4.054377170371938</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09300880952502207</v>
+        <v>0.09695320348282621</v>
       </c>
       <c r="W92">
-        <v>0.2229384346187496</v>
+        <v>0.2129384346187496</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3321743197322216</v>
+        <v>0.3462614410100936</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2248596610230128</v>
+        <v>0.2156800443045852</v>
       </c>
       <c r="C93">
-        <v>-2815.143013159648</v>
+        <v>-2799.543631156437</v>
       </c>
       <c r="D93">
-        <v>292.8179868403519</v>
+        <v>308.4173688435634</v>
       </c>
       <c r="E93">
         <v>1872.161</v>
@@ -8919,37 +8919,37 @@
         <v>254.775</v>
       </c>
       <c r="M93">
-        <v>775.5139938000001</v>
+        <v>743.9633838000001</v>
       </c>
       <c r="N93">
-        <v>-520.7389938000001</v>
+        <v>-489.1883838000001</v>
       </c>
       <c r="O93">
-        <v>-145.806918264</v>
+        <v>-136.972747464</v>
       </c>
       <c r="P93">
-        <v>-374.9320755360001</v>
+        <v>-352.2156363360001</v>
       </c>
       <c r="Q93">
-        <v>-234.3320755360001</v>
+        <v>-211.6156363360001</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.2417452207348685</v>
+        <v>0.2408605905301166</v>
       </c>
       <c r="T93">
-        <v>4.522384419850567</v>
+        <v>4.504863522635487</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09198673469507676</v>
+        <v>0.09588778366433362</v>
       </c>
       <c r="W93">
-        <v>0.2231896606119501</v>
+        <v>0.2131896606119502</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3285240524824169</v>
+        <v>0.3424563702297628</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2268596610230128</v>
+        <v>0.2175800443045851</v>
       </c>
       <c r="C94">
-        <v>-2853.048504875648</v>
+        <v>-2837.625929617646</v>
       </c>
       <c r="D94">
-        <v>289.5834951243519</v>
+        <v>305.0060703823536</v>
       </c>
       <c r="E94">
         <v>1906.832</v>
@@ -9001,37 +9001,37 @@
         <v>254.775</v>
       </c>
       <c r="M94">
-        <v>784.0361256000001</v>
+        <v>752.1388056000001</v>
       </c>
       <c r="N94">
-        <v>-529.2611256000001</v>
+        <v>-497.3638056000001</v>
       </c>
       <c r="O94">
-        <v>-148.193115168</v>
+        <v>-139.261865568</v>
       </c>
       <c r="P94">
-        <v>-381.0680104320001</v>
+        <v>-358.101940032</v>
       </c>
       <c r="Q94">
-        <v>-240.4680104320001</v>
+        <v>-217.501940032</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.266238373326727</v>
+        <v>0.2652431643463812</v>
       </c>
       <c r="T94">
-        <v>5.087682472331889</v>
+        <v>5.067971462964925</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09098687888317375</v>
+        <v>0.09484552514624305</v>
       </c>
       <c r="W94">
-        <v>0.2234354251705159</v>
+        <v>0.2134354251705159</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3249531388684775</v>
+        <v>0.3387340183794394</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2288596610230128</v>
+        <v>0.2194800443045851</v>
       </c>
       <c r="C95">
-        <v>-2890.883320360786</v>
+        <v>-2875.633591213093</v>
       </c>
       <c r="D95">
-        <v>286.419679639214</v>
+        <v>301.6694087869077</v>
       </c>
       <c r="E95">
         <v>1941.503</v>
@@ -9083,37 +9083,37 @@
         <v>254.775</v>
       </c>
       <c r="M95">
-        <v>792.5582574000001</v>
+        <v>760.3142274</v>
       </c>
       <c r="N95">
-        <v>-537.7832574000001</v>
+        <v>-505.5392274000001</v>
       </c>
       <c r="O95">
-        <v>-150.5793120720001</v>
+        <v>-141.550983672</v>
       </c>
       <c r="P95">
-        <v>-387.2039453280001</v>
+        <v>-363.988243728</v>
       </c>
       <c r="Q95">
-        <v>-246.6039453280001</v>
+        <v>-223.388243728</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.2977295695162595</v>
+        <v>0.2965921878244357</v>
       </c>
       <c r="T95">
-        <v>5.814494254093589</v>
+        <v>5.791967386245629</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09000852534679553</v>
+        <v>0.09382568078983182</v>
       </c>
       <c r="W95">
-        <v>0.2236759044697577</v>
+        <v>0.2136759044697577</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3214590190956983</v>
+        <v>0.3350917171065422</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2308596610230128</v>
+        <v>0.2213800443045851</v>
       </c>
       <c r="C96">
-        <v>-2928.649751078165</v>
+        <v>-2913.569038940995</v>
       </c>
       <c r="D96">
-        <v>283.3242489218349</v>
+        <v>298.4049610590052</v>
       </c>
       <c r="E96">
         <v>1976.174</v>
@@ -9165,37 +9165,37 @@
         <v>254.775</v>
       </c>
       <c r="M96">
-        <v>801.0803892000001</v>
+        <v>768.4896492</v>
       </c>
       <c r="N96">
-        <v>-546.3053892000001</v>
+        <v>-513.7146492000001</v>
       </c>
       <c r="O96">
-        <v>-152.9655089760001</v>
+        <v>-143.840101776</v>
       </c>
       <c r="P96">
-        <v>-393.3398802240001</v>
+        <v>-369.874547424</v>
       </c>
       <c r="Q96">
-        <v>-252.7398802240001</v>
+        <v>-229.274547424</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.3397178311023028</v>
+        <v>0.338390885795175</v>
       </c>
       <c r="T96">
-        <v>6.783576629775855</v>
+        <v>6.757295283953235</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.08905098784310622</v>
+        <v>0.09282753524951447</v>
       </c>
       <c r="W96">
-        <v>0.2239112671881645</v>
+        <v>0.2139112671881645</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3180392422968078</v>
+        <v>0.3315269116054087</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2328596610230128</v>
+        <v>0.2232800443045851</v>
       </c>
       <c r="C97">
-        <v>-2966.349990491648</v>
+        <v>-2951.434592042634</v>
       </c>
       <c r="D97">
-        <v>280.2950095083517</v>
+        <v>295.2104079573666</v>
       </c>
       <c r="E97">
         <v>2010.845</v>
@@ -9247,37 +9247,37 @@
         <v>254.775</v>
       </c>
       <c r="M97">
-        <v>809.6025210000001</v>
+        <v>776.6650710000001</v>
       </c>
       <c r="N97">
-        <v>-554.8275210000002</v>
+        <v>-521.8900710000001</v>
       </c>
       <c r="O97">
-        <v>-155.3517058800001</v>
+        <v>-146.1292198800001</v>
       </c>
       <c r="P97">
-        <v>-399.4758151200001</v>
+        <v>-375.7608511200001</v>
       </c>
       <c r="Q97">
-        <v>-258.8758151200001</v>
+        <v>-235.1608511200001</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.3985013973227636</v>
+        <v>0.3969090629542102</v>
       </c>
       <c r="T97">
-        <v>8.140291955731032</v>
+        <v>8.108754340743886</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0881136090237051</v>
+        <v>0.09185040329951956</v>
       </c>
       <c r="W97">
-        <v>0.2241416749019733</v>
+        <v>0.2141416749019733</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3146914607989467</v>
+        <v>0.3280371546411412</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2348596610230128</v>
+        <v>0.2251800443045851</v>
       </c>
       <c r="C98">
-        <v>-3003.986139249364</v>
+        <v>-2989.232471497332</v>
       </c>
       <c r="D98">
-        <v>277.3298607506353</v>
+        <v>292.0835285026677</v>
       </c>
       <c r="E98">
         <v>2045.516</v>
@@ -9329,37 +9329,37 @@
         <v>254.775</v>
       </c>
       <c r="M98">
-        <v>818.1246528</v>
+        <v>784.8404928</v>
       </c>
       <c r="N98">
-        <v>-563.3496528000001</v>
+        <v>-530.0654928</v>
       </c>
       <c r="O98">
-        <v>-157.737902784</v>
+        <v>-148.418337984</v>
       </c>
       <c r="P98">
-        <v>-405.611750016</v>
+        <v>-381.647154816</v>
       </c>
       <c r="Q98">
-        <v>-265.0117500160001</v>
+        <v>-241.047154816</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.4866767466534535</v>
+        <v>0.4846863286927618</v>
       </c>
       <c r="T98">
-        <v>10.17536494466376</v>
+        <v>10.13594292592984</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08719575892970818</v>
+        <v>0.09089362826514957</v>
       </c>
       <c r="W98">
-        <v>0.2243672824550777</v>
+        <v>0.2143672824550777</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3114134247489577</v>
+        <v>0.3246201009469627</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2368596610230128</v>
+        <v>0.2270800443045851</v>
       </c>
       <c r="C99">
-        <v>-3041.560210041658</v>
+        <v>-3026.96480517189</v>
       </c>
       <c r="D99">
-        <v>274.4267899583424</v>
+        <v>289.0221948281096</v>
       </c>
       <c r="E99">
         <v>2080.187</v>
@@ -9411,37 +9411,37 @@
         <v>254.775</v>
       </c>
       <c r="M99">
-        <v>826.6467846</v>
+        <v>793.0159146</v>
       </c>
       <c r="N99">
-        <v>-571.8717846000001</v>
+        <v>-538.2409146</v>
       </c>
       <c r="O99">
-        <v>-160.124099688</v>
+        <v>-150.707456088</v>
       </c>
       <c r="P99">
-        <v>-411.7476849120001</v>
+        <v>-387.533458512</v>
       </c>
       <c r="Q99">
-        <v>-271.147684912</v>
+        <v>-246.933458512</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.6336356622046047</v>
+        <v>0.630981771590349</v>
       </c>
       <c r="T99">
-        <v>13.56715325955169</v>
+        <v>13.51459056790645</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08629683357991738</v>
+        <v>0.08995658055107587</v>
       </c>
       <c r="W99">
-        <v>0.2245882383060563</v>
+        <v>0.2145882383060563</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3082029770711334</v>
+        <v>0.3212735019681281</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2388596610230128</v>
+        <v>0.2289800443045851</v>
       </c>
       <c r="C100">
-        <v>-3079.074132157071</v>
+        <v>-3064.63363264954</v>
       </c>
       <c r="D100">
-        <v>271.5838678429284</v>
+        <v>286.0243673504597</v>
       </c>
       <c r="E100">
         <v>2114.858</v>
@@ -9493,37 +9493,37 @@
         <v>254.775</v>
       </c>
       <c r="M100">
-        <v>835.1689164000001</v>
+        <v>801.1913364</v>
       </c>
       <c r="N100">
-        <v>-580.3939164000001</v>
+        <v>-546.4163364</v>
       </c>
       <c r="O100">
-        <v>-162.510296592</v>
+        <v>-152.996574192</v>
       </c>
       <c r="P100">
-        <v>-417.883619808</v>
+        <v>-393.419762208</v>
       </c>
       <c r="Q100">
-        <v>-277.283619808</v>
+        <v>-252.819762208</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>0.9275534933069071</v>
+        <v>0.9235726573855234</v>
       </c>
       <c r="T100">
-        <v>20.35072988932753</v>
+        <v>20.27188585185967</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08541625364542843</v>
+        <v>0.08903865625973836</v>
       </c>
       <c r="W100">
-        <v>0.2248046848539537</v>
+        <v>0.2148046848539537</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3050580487336728</v>
+        <v>0.317995200927637</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2408596610230128</v>
+        <v>0.2308800443045851</v>
       </c>
       <c r="C101">
-        <v>-3116.529755758062</v>
+        <v>-3102.240909761467</v>
       </c>
       <c r="D101">
-        <v>268.7992442419379</v>
+        <v>283.088090238533</v>
       </c>
       <c r="E101">
         <v>2149.529</v>
@@ -9575,37 +9575,37 @@
         <v>254.775</v>
       </c>
       <c r="M101">
-        <v>843.6910482000001</v>
+        <v>809.3667582</v>
       </c>
       <c r="N101">
-        <v>-588.9160482000001</v>
+        <v>-554.5917582000001</v>
       </c>
       <c r="O101">
-        <v>-164.896493496</v>
+        <v>-155.285692296</v>
       </c>
       <c r="P101">
-        <v>-424.019554704</v>
+        <v>-399.306065904</v>
       </c>
       <c r="Q101">
-        <v>-283.419554704</v>
+        <v>-258.7060659040001</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>1.809306986613814</v>
+        <v>1.801345314771047</v>
       </c>
       <c r="T101">
-        <v>40.70145977865506</v>
+        <v>40.54377170371934</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.08455346320456551</v>
+        <v>0.08813927589347838</v>
       </c>
       <c r="W101">
-        <v>0.2250167587443178</v>
+        <v>0.2150167587443178</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3019766543020196</v>
+        <v>0.3147831281909942</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/new_zealand/new_zealand_utility_general.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_utility_general.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06503374940558185</v>
+        <v>0.06488405490724621</v>
       </c>
       <c r="C2">
-        <v>2771.163581084343</v>
+        <v>2757.860017574477</v>
       </c>
       <c r="D2">
-        <v>2724.063581084343</v>
+        <v>2745.431017574477</v>
       </c>
       <c r="E2">
-        <v>-1282.9</v>
+        <v>-1248.229</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>34.671</v>
       </c>
       <c r="G2">
         <v>47.1</v>
@@ -1457,28 +1457,28 @@
         <v>254.775</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.7439513</v>
       </c>
       <c r="N2">
-        <v>254.775</v>
+        <v>253.0310487</v>
       </c>
       <c r="O2">
-        <v>71.337</v>
+        <v>70.84869363600001</v>
       </c>
       <c r="P2">
-        <v>183.438</v>
+        <v>182.182355064</v>
       </c>
       <c r="Q2">
-        <v>324.038</v>
+        <v>322.782355064</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06503374940558185</v>
+        <v>0.06517363121944061</v>
       </c>
       <c r="T2">
-        <v>0.4441974458563937</v>
+        <v>0.4474279727353493</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>146.090662050024</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06488405490724621</v>
+        <v>0.06473436040891058</v>
       </c>
       <c r="C3">
-        <v>2757.860017574477</v>
+        <v>2744.894314717626</v>
       </c>
       <c r="D3">
-        <v>2745.431017574477</v>
+        <v>2767.136314717627</v>
       </c>
       <c r="E3">
-        <v>-1248.229</v>
+        <v>-1213.558</v>
       </c>
       <c r="F3">
-        <v>34.671</v>
+        <v>69.342</v>
       </c>
       <c r="G3">
         <v>47.1</v>
@@ -1539,28 +1539,28 @@
         <v>254.775</v>
       </c>
       <c r="M3">
-        <v>1.7439513</v>
+        <v>3.4879026</v>
       </c>
       <c r="N3">
-        <v>253.0310487</v>
+        <v>251.2870974</v>
       </c>
       <c r="O3">
-        <v>70.84869363600001</v>
+        <v>70.36038727200001</v>
       </c>
       <c r="P3">
-        <v>182.182355064</v>
+        <v>180.926710128</v>
       </c>
       <c r="Q3">
-        <v>322.782355064</v>
+        <v>321.526710128</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06517363121944061</v>
+        <v>0.06531636776419447</v>
       </c>
       <c r="T3">
-        <v>0.4474279727353493</v>
+        <v>0.4507244287342835</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>146.090662050024</v>
+        <v>73.04533102501199</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06473436040891058</v>
+        <v>0.06458466591057495</v>
       </c>
       <c r="C4">
-        <v>2744.894314717626</v>
+        <v>2732.274549721214</v>
       </c>
       <c r="D4">
-        <v>2767.136314717627</v>
+        <v>2789.187549721214</v>
       </c>
       <c r="E4">
-        <v>-1213.558</v>
+        <v>-1178.887</v>
       </c>
       <c r="F4">
-        <v>69.342</v>
+        <v>104.013</v>
       </c>
       <c r="G4">
         <v>47.1</v>
@@ -1621,28 +1621,28 @@
         <v>254.775</v>
       </c>
       <c r="M4">
-        <v>3.4879026</v>
+        <v>5.231853899999999</v>
       </c>
       <c r="N4">
-        <v>251.2870974</v>
+        <v>249.5431461</v>
       </c>
       <c r="O4">
-        <v>70.36038727200001</v>
+        <v>69.872080908</v>
       </c>
       <c r="P4">
-        <v>180.926710128</v>
+        <v>179.671065192</v>
       </c>
       <c r="Q4">
-        <v>321.526710128</v>
+        <v>320.271065192</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06531636776419447</v>
+        <v>0.06546204733048964</v>
       </c>
       <c r="T4">
-        <v>0.4507244287342835</v>
+        <v>0.4540888528981443</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.04533102501199</v>
+        <v>48.69688735000801</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06458466591057495</v>
+        <v>0.06443497141223933</v>
       </c>
       <c r="C5">
-        <v>2732.274549721214</v>
+        <v>2720.009059329091</v>
       </c>
       <c r="D5">
-        <v>2789.187549721214</v>
+        <v>2811.593059329091</v>
       </c>
       <c r="E5">
-        <v>-1178.887</v>
+        <v>-1144.216</v>
       </c>
       <c r="F5">
-        <v>104.013</v>
+        <v>138.684</v>
       </c>
       <c r="G5">
         <v>47.1</v>
@@ -1703,28 +1703,28 @@
         <v>254.775</v>
       </c>
       <c r="M5">
-        <v>5.231853899999999</v>
+        <v>6.9758052</v>
       </c>
       <c r="N5">
-        <v>249.5431461</v>
+        <v>247.7991948</v>
       </c>
       <c r="O5">
-        <v>69.872080908</v>
+        <v>69.383774544</v>
       </c>
       <c r="P5">
-        <v>179.671065192</v>
+        <v>178.415420256</v>
       </c>
       <c r="Q5">
-        <v>320.271065192</v>
+        <v>319.015420256</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06546204733048964</v>
+        <v>0.06561076188774931</v>
       </c>
       <c r="T5">
-        <v>0.4540888528981443</v>
+        <v>0.4575233692320855</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.69688735000801</v>
+        <v>36.522665512506</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06443497141223933</v>
+        <v>0.06428527691390371</v>
       </c>
       <c r="C6">
-        <v>2720.009059329091</v>
+        <v>2708.106450330236</v>
       </c>
       <c r="D6">
-        <v>2811.593059329091</v>
+        <v>2834.361450330236</v>
       </c>
       <c r="E6">
-        <v>-1144.216</v>
+        <v>-1109.545</v>
       </c>
       <c r="F6">
-        <v>138.684</v>
+        <v>173.355</v>
       </c>
       <c r="G6">
         <v>47.1</v>
@@ -1785,28 +1785,28 @@
         <v>254.775</v>
       </c>
       <c r="M6">
-        <v>6.9758052</v>
+        <v>8.719756500000001</v>
       </c>
       <c r="N6">
-        <v>247.7991948</v>
+        <v>246.0552435</v>
       </c>
       <c r="O6">
-        <v>69.383774544</v>
+        <v>68.89546818000001</v>
       </c>
       <c r="P6">
-        <v>178.415420256</v>
+        <v>177.15977532</v>
       </c>
       <c r="Q6">
-        <v>319.015420256</v>
+        <v>317.75977532</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06561076188774931</v>
+        <v>0.06576260727779337</v>
       </c>
       <c r="T6">
-        <v>0.4575233692320855</v>
+        <v>0.461030191173057</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.522665512506</v>
+        <v>29.2181324100048</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06428527691390371</v>
+        <v>0.06413558241556806</v>
       </c>
       <c r="C7">
-        <v>2708.106450330236</v>
+        <v>2696.575610582186</v>
       </c>
       <c r="D7">
-        <v>2834.361450330236</v>
+        <v>2857.501610582186</v>
       </c>
       <c r="E7">
-        <v>-1109.545</v>
+        <v>-1074.874</v>
       </c>
       <c r="F7">
-        <v>173.355</v>
+        <v>208.026</v>
       </c>
       <c r="G7">
         <v>47.1</v>
@@ -1867,28 +1867,28 @@
         <v>254.775</v>
       </c>
       <c r="M7">
-        <v>8.719756500000001</v>
+        <v>10.4637078</v>
       </c>
       <c r="N7">
-        <v>246.0552435</v>
+        <v>244.3112922</v>
       </c>
       <c r="O7">
-        <v>68.89546818000001</v>
+        <v>68.407161816</v>
       </c>
       <c r="P7">
-        <v>177.15977532</v>
+        <v>175.904130384</v>
       </c>
       <c r="Q7">
-        <v>317.75977532</v>
+        <v>316.504130384</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06576260727779337</v>
+        <v>0.06591768342081709</v>
       </c>
       <c r="T7">
-        <v>0.461030191173057</v>
+        <v>0.4646116263468152</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.2181324100048</v>
+        <v>24.348443675004</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06413558241556806</v>
+        <v>0.06398588791723245</v>
       </c>
       <c r="C8">
-        <v>2696.575610582186</v>
+        <v>2685.425720578909</v>
       </c>
       <c r="D8">
-        <v>2857.501610582186</v>
+        <v>2881.02272057891</v>
       </c>
       <c r="E8">
-        <v>-1074.874</v>
+        <v>-1040.203</v>
       </c>
       <c r="F8">
-        <v>208.026</v>
+        <v>242.697</v>
       </c>
       <c r="G8">
         <v>47.1</v>
@@ -1949,28 +1949,28 @@
         <v>254.775</v>
       </c>
       <c r="M8">
-        <v>10.4637078</v>
+        <v>12.2076591</v>
       </c>
       <c r="N8">
-        <v>244.3112922</v>
+        <v>242.5673409</v>
       </c>
       <c r="O8">
-        <v>68.407161816</v>
+        <v>67.918855452</v>
       </c>
       <c r="P8">
-        <v>175.904130384</v>
+        <v>174.648485448</v>
       </c>
       <c r="Q8">
-        <v>316.504130384</v>
+        <v>315.248485448</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06591768342081709</v>
+        <v>0.06607609453465854</v>
       </c>
       <c r="T8">
-        <v>0.4646116263468152</v>
+        <v>0.468270081631837</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.348443675004</v>
+        <v>20.87009457857486</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06398588791723243</v>
+        <v>0.06383619341889682</v>
       </c>
       <c r="C9">
-        <v>2685.425720578912</v>
+        <v>2674.666265594764</v>
       </c>
       <c r="D9">
-        <v>2881.022720578912</v>
+        <v>2904.934265594764</v>
       </c>
       <c r="E9">
-        <v>-1040.203</v>
+        <v>-1005.532</v>
       </c>
       <c r="F9">
-        <v>242.697</v>
+        <v>277.368</v>
       </c>
       <c r="G9">
         <v>47.1</v>
@@ -2031,28 +2031,28 @@
         <v>254.775</v>
       </c>
       <c r="M9">
-        <v>12.2076591</v>
+        <v>13.9516104</v>
       </c>
       <c r="N9">
-        <v>242.5673409</v>
+        <v>240.8233896</v>
       </c>
       <c r="O9">
-        <v>67.918855452</v>
+        <v>67.43054908800001</v>
       </c>
       <c r="P9">
-        <v>174.648485448</v>
+        <v>173.392840512</v>
       </c>
       <c r="Q9">
-        <v>315.248485448</v>
+        <v>313.992840512</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06607609453465854</v>
+        <v>0.06623794936836611</v>
       </c>
       <c r="T9">
-        <v>0.468270081631837</v>
+        <v>0.4720080685534896</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.87009457857486</v>
+        <v>18.261332756253</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06383619341889682</v>
+        <v>0.06368649892056119</v>
       </c>
       <c r="C10">
-        <v>2674.666265594764</v>
+        <v>2664.307048438209</v>
       </c>
       <c r="D10">
-        <v>2904.934265594764</v>
+        <v>2929.246048438209</v>
       </c>
       <c r="E10">
-        <v>-1005.532</v>
+        <v>-970.8610000000001</v>
       </c>
       <c r="F10">
-        <v>277.368</v>
+        <v>312.039</v>
       </c>
       <c r="G10">
         <v>47.1</v>
@@ -2113,28 +2113,28 @@
         <v>254.775</v>
       </c>
       <c r="M10">
-        <v>13.9516104</v>
+        <v>15.6955617</v>
       </c>
       <c r="N10">
-        <v>240.8233896</v>
+        <v>239.0794383</v>
       </c>
       <c r="O10">
-        <v>67.43054908800001</v>
+        <v>66.94224272400001</v>
       </c>
       <c r="P10">
-        <v>173.392840512</v>
+        <v>172.137195576</v>
       </c>
       <c r="Q10">
-        <v>313.992840512</v>
+        <v>312.737195576</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.06623794936836611</v>
+        <v>0.06640336145116614</v>
       </c>
       <c r="T10">
-        <v>0.4720080685534896</v>
+        <v>0.47582820903386</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.261332756253</v>
+        <v>16.232295783336</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06368649892056119</v>
+        <v>0.06353680442222555</v>
       </c>
       <c r="C11">
-        <v>2664.307048438209</v>
+        <v>2654.358202851387</v>
       </c>
       <c r="D11">
-        <v>2929.246048438209</v>
+        <v>2953.968202851388</v>
       </c>
       <c r="E11">
-        <v>-970.8610000000001</v>
+        <v>-936.1900000000001</v>
       </c>
       <c r="F11">
-        <v>312.039</v>
+        <v>346.71</v>
       </c>
       <c r="G11">
         <v>47.1</v>
@@ -2195,28 +2195,28 @@
         <v>254.775</v>
       </c>
       <c r="M11">
-        <v>15.6955617</v>
+        <v>17.439513</v>
       </c>
       <c r="N11">
-        <v>239.0794383</v>
+        <v>237.335487</v>
       </c>
       <c r="O11">
-        <v>66.94224272400001</v>
+        <v>66.45393636</v>
       </c>
       <c r="P11">
-        <v>172.137195576</v>
+        <v>170.88155064</v>
       </c>
       <c r="Q11">
-        <v>312.737195576</v>
+        <v>311.48155064</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.06640336145116614</v>
+        <v>0.06657244935802839</v>
       </c>
       <c r="T11">
-        <v>0.47582820903386</v>
+        <v>0.4797332415249052</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.232295783336</v>
+        <v>14.6090662050024</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06353680442222555</v>
+        <v>0.06338710992388992</v>
       </c>
       <c r="C12">
-        <v>2654.358202851387</v>
+        <v>2644.830207594002</v>
       </c>
       <c r="D12">
-        <v>2953.968202851388</v>
+        <v>2979.111207594002</v>
       </c>
       <c r="E12">
-        <v>-936.1900000000001</v>
+        <v>-901.5190000000001</v>
       </c>
       <c r="F12">
-        <v>346.71</v>
+        <v>381.381</v>
       </c>
       <c r="G12">
         <v>47.1</v>
@@ -2277,28 +2277,28 @@
         <v>254.775</v>
       </c>
       <c r="M12">
-        <v>17.439513</v>
+        <v>19.1834643</v>
       </c>
       <c r="N12">
-        <v>237.335487</v>
+        <v>235.5915357</v>
       </c>
       <c r="O12">
-        <v>66.45393636</v>
+        <v>65.965629996</v>
       </c>
       <c r="P12">
-        <v>170.88155064</v>
+        <v>169.625905704</v>
       </c>
       <c r="Q12">
-        <v>311.48155064</v>
+        <v>310.225905704</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.06657244935802839</v>
+        <v>0.06674533699313474</v>
       </c>
       <c r="T12">
-        <v>0.4797332415249052</v>
+        <v>0.483726027555075</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.6090662050024</v>
+        <v>13.28096927727491</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06338710992388992</v>
+        <v>0.0633670154255543</v>
       </c>
       <c r="C13">
-        <v>2644.830207594002</v>
+        <v>2613.566943270919</v>
       </c>
       <c r="D13">
-        <v>2979.111207594002</v>
+        <v>2982.518943270919</v>
       </c>
       <c r="E13">
-        <v>-901.5190000000001</v>
+        <v>-866.8480000000002</v>
       </c>
       <c r="F13">
-        <v>381.381</v>
+        <v>416.052</v>
       </c>
       <c r="G13">
         <v>47.1</v>
@@ -2359,45 +2359,45 @@
         <v>254.775</v>
       </c>
       <c r="M13">
-        <v>19.1834643</v>
+        <v>21.5514936</v>
       </c>
       <c r="N13">
-        <v>235.5915357</v>
+        <v>233.2235064</v>
       </c>
       <c r="O13">
-        <v>65.965629996</v>
+        <v>65.30258179200001</v>
       </c>
       <c r="P13">
-        <v>169.625905704</v>
+        <v>167.920924608</v>
       </c>
       <c r="Q13">
-        <v>310.225905704</v>
+        <v>308.520924608</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.06674533699313474</v>
+        <v>0.06692215389267533</v>
       </c>
       <c r="T13">
-        <v>0.483726027555075</v>
+        <v>0.4878095587222941</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.28</v>
       </c>
       <c r="W13">
-        <v>0.036216</v>
+        <v>0.037296</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.28096927727491</v>
+        <v>11.82168645610716</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0633670154255543</v>
+        <v>0.06322812092721866</v>
       </c>
       <c r="C14">
-        <v>2613.566943270919</v>
+        <v>2602.665314285277</v>
       </c>
       <c r="D14">
-        <v>2982.518943270919</v>
+        <v>3006.288314285277</v>
       </c>
       <c r="E14">
-        <v>-866.8480000000002</v>
+        <v>-832.1770000000001</v>
       </c>
       <c r="F14">
-        <v>416.052</v>
+        <v>450.723</v>
       </c>
       <c r="G14">
         <v>47.1</v>
@@ -2441,28 +2441,28 @@
         <v>254.775</v>
       </c>
       <c r="M14">
-        <v>21.5514936</v>
+        <v>23.3474514</v>
       </c>
       <c r="N14">
-        <v>233.2235064</v>
+        <v>231.4275486</v>
       </c>
       <c r="O14">
-        <v>65.30258179200001</v>
+        <v>64.799713608</v>
       </c>
       <c r="P14">
-        <v>167.920924608</v>
+        <v>166.627834992</v>
       </c>
       <c r="Q14">
-        <v>308.520924608</v>
+        <v>307.227834992</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.06692215389267533</v>
+        <v>0.0671030355485272</v>
       </c>
       <c r="T14">
-        <v>0.4878095587222941</v>
+        <v>0.4919869641692194</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.82168645610716</v>
+        <v>10.91232595948353</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06322812092721866</v>
+        <v>0.06308922642888302</v>
       </c>
       <c r="C15">
-        <v>2602.665314285277</v>
+        <v>2592.14559190215</v>
       </c>
       <c r="D15">
-        <v>3006.288314285277</v>
+        <v>3030.43959190215</v>
       </c>
       <c r="E15">
-        <v>-832.1770000000001</v>
+        <v>-797.5060000000001</v>
       </c>
       <c r="F15">
-        <v>450.723</v>
+        <v>485.394</v>
       </c>
       <c r="G15">
         <v>47.1</v>
@@ -2523,28 +2523,28 @@
         <v>254.775</v>
       </c>
       <c r="M15">
-        <v>23.3474514</v>
+        <v>25.1434092</v>
       </c>
       <c r="N15">
-        <v>231.4275486</v>
+        <v>229.6315908</v>
       </c>
       <c r="O15">
-        <v>64.799713608</v>
+        <v>64.29684542400001</v>
       </c>
       <c r="P15">
-        <v>166.627834992</v>
+        <v>165.334745376</v>
       </c>
       <c r="Q15">
-        <v>307.227834992</v>
+        <v>305.934745376</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0671030355485272</v>
+        <v>0.06728812375451515</v>
       </c>
       <c r="T15">
-        <v>0.4919869641692194</v>
+        <v>0.4962615185800268</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.91232595948353</v>
+        <v>10.1328741052347</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06308922642888302</v>
+        <v>0.06313393193054741</v>
       </c>
       <c r="C16">
-        <v>2592.14559190215</v>
+        <v>2549.658862455282</v>
       </c>
       <c r="D16">
-        <v>3030.43959190215</v>
+        <v>3022.623862455282</v>
       </c>
       <c r="E16">
-        <v>-797.5060000000001</v>
+        <v>-762.835</v>
       </c>
       <c r="F16">
-        <v>485.394</v>
+        <v>520.0650000000001</v>
       </c>
       <c r="G16">
         <v>47.1</v>
@@ -2605,45 +2605,45 @@
         <v>254.775</v>
       </c>
       <c r="M16">
-        <v>25.1434092</v>
+        <v>27.8234775</v>
       </c>
       <c r="N16">
-        <v>229.6315908</v>
+        <v>226.9515225</v>
       </c>
       <c r="O16">
-        <v>64.29684542400001</v>
+        <v>63.54642630000001</v>
       </c>
       <c r="P16">
-        <v>165.334745376</v>
+        <v>163.4050962</v>
       </c>
       <c r="Q16">
-        <v>305.934745376</v>
+        <v>304.0050962</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.06728812375451515</v>
+        <v>0.0674775669771146</v>
       </c>
       <c r="T16">
-        <v>0.4962615185800268</v>
+        <v>0.5006366507416766</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.28</v>
       </c>
       <c r="W16">
-        <v>0.037296</v>
+        <v>0.03852</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.1328741052347</v>
+        <v>9.15683526618842</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06313393193054741</v>
+        <v>0.06300727743221177</v>
       </c>
       <c r="C17">
-        <v>2549.658862455282</v>
+        <v>2537.235943853677</v>
       </c>
       <c r="D17">
-        <v>3022.623862455282</v>
+        <v>3044.871943853677</v>
       </c>
       <c r="E17">
-        <v>-762.8350000000002</v>
+        <v>-728.1640000000001</v>
       </c>
       <c r="F17">
-        <v>520.0649999999999</v>
+        <v>554.736</v>
       </c>
       <c r="G17">
         <v>47.1</v>
@@ -2687,28 +2687,28 @@
         <v>254.775</v>
       </c>
       <c r="M17">
-        <v>27.8234775</v>
+        <v>29.678376</v>
       </c>
       <c r="N17">
-        <v>226.9515225</v>
+        <v>225.096624</v>
       </c>
       <c r="O17">
-        <v>63.54642630000001</v>
+        <v>63.02705472000001</v>
       </c>
       <c r="P17">
-        <v>163.4050962</v>
+        <v>162.06956928</v>
       </c>
       <c r="Q17">
-        <v>304.0050962</v>
+        <v>302.66956928</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0674775669771146</v>
+        <v>0.06767152075263307</v>
       </c>
       <c r="T17">
-        <v>0.5006366507416766</v>
+        <v>0.5051159527166992</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.156835266188422</v>
+        <v>8.584533062051644</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06300727743221177</v>
+        <v>0.06288062293387614</v>
       </c>
       <c r="C18">
-        <v>2537.235943853677</v>
+        <v>2525.142968673846</v>
       </c>
       <c r="D18">
-        <v>3044.871943853677</v>
+        <v>3067.449968673846</v>
       </c>
       <c r="E18">
-        <v>-728.1640000000001</v>
+        <v>-693.4930000000001</v>
       </c>
       <c r="F18">
-        <v>554.736</v>
+        <v>589.407</v>
       </c>
       <c r="G18">
         <v>47.1</v>
@@ -2769,28 +2769,28 @@
         <v>254.775</v>
       </c>
       <c r="M18">
-        <v>29.678376</v>
+        <v>31.5332745</v>
       </c>
       <c r="N18">
-        <v>225.096624</v>
+        <v>223.2417255</v>
       </c>
       <c r="O18">
-        <v>63.02705472000001</v>
+        <v>62.50768314</v>
       </c>
       <c r="P18">
-        <v>162.06956928</v>
+        <v>160.73404236</v>
       </c>
       <c r="Q18">
-        <v>302.66956928</v>
+        <v>301.33404236</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.06767152075263307</v>
+        <v>0.0678701481131038</v>
       </c>
       <c r="T18">
-        <v>0.5051159527166992</v>
+        <v>0.5097031896790715</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.584533062051644</v>
+        <v>8.079560528989781</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06288062293387614</v>
+        <v>0.06275396843554051</v>
       </c>
       <c r="C19">
-        <v>2525.142968673846</v>
+        <v>2513.387331435617</v>
       </c>
       <c r="D19">
-        <v>3067.449968673846</v>
+        <v>3090.365331435617</v>
       </c>
       <c r="E19">
-        <v>-693.4930000000001</v>
+        <v>-658.822</v>
       </c>
       <c r="F19">
-        <v>589.407</v>
+        <v>624.0780000000001</v>
       </c>
       <c r="G19">
         <v>47.1</v>
@@ -2851,28 +2851,28 @@
         <v>254.775</v>
       </c>
       <c r="M19">
-        <v>31.5332745</v>
+        <v>33.388173</v>
       </c>
       <c r="N19">
-        <v>223.2417255</v>
+        <v>221.386827</v>
       </c>
       <c r="O19">
-        <v>62.50768314</v>
+        <v>61.98831156000001</v>
       </c>
       <c r="P19">
-        <v>160.73404236</v>
+        <v>159.39851544</v>
       </c>
       <c r="Q19">
-        <v>301.33404236</v>
+        <v>299.99851544</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.0678701481131038</v>
+        <v>0.0680736200433421</v>
       </c>
       <c r="T19">
-        <v>0.5097031896790715</v>
+        <v>0.5144023104697945</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.079560528989781</v>
+        <v>7.630696055157016</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06275396843554053</v>
+        <v>0.06273675393720489</v>
       </c>
       <c r="C20">
-        <v>2513.387331435614</v>
+        <v>2481.857375407308</v>
       </c>
       <c r="D20">
-        <v>3090.365331435614</v>
+        <v>3093.506375407308</v>
       </c>
       <c r="E20">
-        <v>-658.8220000000001</v>
+        <v>-624.1510000000001</v>
       </c>
       <c r="F20">
-        <v>624.078</v>
+        <v>658.749</v>
       </c>
       <c r="G20">
         <v>47.1</v>
@@ -2933,45 +2933,45 @@
         <v>254.775</v>
       </c>
       <c r="M20">
-        <v>33.38817299999999</v>
+        <v>35.77007070000001</v>
       </c>
       <c r="N20">
-        <v>221.386827</v>
+        <v>219.0049293</v>
       </c>
       <c r="O20">
-        <v>61.98831156000001</v>
+        <v>61.32138020400001</v>
       </c>
       <c r="P20">
-        <v>159.39851544</v>
+        <v>157.683549096</v>
       </c>
       <c r="Q20">
-        <v>299.99851544</v>
+        <v>298.283549096</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0680736200433421</v>
+        <v>0.06828211597185789</v>
       </c>
       <c r="T20">
-        <v>0.5144023104697945</v>
+        <v>0.5192174589343624</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.28</v>
       </c>
       <c r="W20">
-        <v>0.03852</v>
+        <v>0.039096</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.630696055157018</v>
+        <v>7.12257468364467</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06273675393720489</v>
+        <v>0.06261585943886926</v>
       </c>
       <c r="C21">
-        <v>2481.857375407308</v>
+        <v>2469.426564956495</v>
       </c>
       <c r="D21">
-        <v>3093.506375407308</v>
+        <v>3115.746564956496</v>
       </c>
       <c r="E21">
-        <v>-624.1510000000001</v>
+        <v>-589.48</v>
       </c>
       <c r="F21">
-        <v>658.749</v>
+        <v>693.4200000000001</v>
       </c>
       <c r="G21">
         <v>47.1</v>
@@ -3015,28 +3015,28 @@
         <v>254.775</v>
       </c>
       <c r="M21">
-        <v>35.77007070000001</v>
+        <v>37.652706</v>
       </c>
       <c r="N21">
-        <v>219.0049293</v>
+        <v>217.122294</v>
       </c>
       <c r="O21">
-        <v>61.32138020400001</v>
+        <v>60.79424232000001</v>
       </c>
       <c r="P21">
-        <v>157.683549096</v>
+        <v>156.32805168</v>
       </c>
       <c r="Q21">
-        <v>298.283549096</v>
+        <v>296.92805168</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.06828211597185789</v>
+        <v>0.06849582429858657</v>
       </c>
       <c r="T21">
-        <v>0.5192174589343624</v>
+        <v>0.5241529861105445</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.12257468364467</v>
+        <v>6.766445949462437</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06261585943886926</v>
+        <v>0.06249496494053363</v>
       </c>
       <c r="C22">
-        <v>2469.426564956495</v>
+        <v>2457.317853601789</v>
       </c>
       <c r="D22">
-        <v>3115.746564956496</v>
+        <v>3138.308853601789</v>
       </c>
       <c r="E22">
-        <v>-589.48</v>
+        <v>-554.8090000000001</v>
       </c>
       <c r="F22">
-        <v>693.4200000000001</v>
+        <v>728.091</v>
       </c>
       <c r="G22">
         <v>47.1</v>
@@ -3097,28 +3097,28 @@
         <v>254.775</v>
       </c>
       <c r="M22">
-        <v>37.652706</v>
+        <v>39.5353413</v>
       </c>
       <c r="N22">
-        <v>217.122294</v>
+        <v>215.2396587</v>
       </c>
       <c r="O22">
-        <v>60.79424232000001</v>
+        <v>60.26710443600001</v>
       </c>
       <c r="P22">
-        <v>156.32805168</v>
+        <v>154.972554264</v>
       </c>
       <c r="Q22">
-        <v>296.92805168</v>
+        <v>295.572554264</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.06849582429858657</v>
+        <v>0.0687149429627008</v>
       </c>
       <c r="T22">
-        <v>0.5241529861105445</v>
+        <v>0.52921346334182</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.766445949462437</v>
+        <v>6.444234237583274</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06249496494053363</v>
+        <v>0.062374070442198</v>
       </c>
       <c r="C23">
-        <v>2457.317853601789</v>
+        <v>2445.538289703838</v>
       </c>
       <c r="D23">
-        <v>3138.308853601789</v>
+        <v>3161.200289703838</v>
       </c>
       <c r="E23">
-        <v>-554.8090000000001</v>
+        <v>-520.1380000000001</v>
       </c>
       <c r="F23">
-        <v>728.091</v>
+        <v>762.7619999999999</v>
       </c>
       <c r="G23">
         <v>47.1</v>
@@ -3179,28 +3179,28 @@
         <v>254.775</v>
       </c>
       <c r="M23">
-        <v>39.5353413</v>
+        <v>41.4179766</v>
       </c>
       <c r="N23">
-        <v>215.2396587</v>
+        <v>213.3570234</v>
       </c>
       <c r="O23">
-        <v>60.26710443600001</v>
+        <v>59.73996655200001</v>
       </c>
       <c r="P23">
-        <v>154.972554264</v>
+        <v>153.617056848</v>
       </c>
       <c r="Q23">
-        <v>295.572554264</v>
+        <v>294.217056848</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0687149429627008</v>
+        <v>0.06893968005410001</v>
       </c>
       <c r="T23">
-        <v>0.52921346334182</v>
+        <v>0.5344036963995383</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.444234237583274</v>
+        <v>6.151314499511307</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.062374070442198</v>
+        <v>0.06241877594386238</v>
       </c>
       <c r="C24">
-        <v>2445.538289703838</v>
+        <v>2402.363471775841</v>
       </c>
       <c r="D24">
-        <v>3161.200289703838</v>
+        <v>3152.696471775841</v>
       </c>
       <c r="E24">
-        <v>-520.1380000000001</v>
+        <v>-485.4670000000001</v>
       </c>
       <c r="F24">
-        <v>762.7619999999999</v>
+        <v>797.433</v>
       </c>
       <c r="G24">
         <v>47.1</v>
@@ -3261,45 +3261,45 @@
         <v>254.775</v>
       </c>
       <c r="M24">
-        <v>41.4179766</v>
+        <v>44.0980449</v>
       </c>
       <c r="N24">
-        <v>213.3570234</v>
+        <v>210.6769551</v>
       </c>
       <c r="O24">
-        <v>59.73996655200001</v>
+        <v>58.98954742800001</v>
       </c>
       <c r="P24">
-        <v>153.617056848</v>
+        <v>151.687407672</v>
       </c>
       <c r="Q24">
-        <v>294.217056848</v>
+        <v>292.287407672</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.06893968005410001</v>
+        <v>0.06917025447254854</v>
       </c>
       <c r="T24">
-        <v>0.5344036963995383</v>
+        <v>0.539728740705509</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.28</v>
       </c>
       <c r="W24">
-        <v>0.039096</v>
+        <v>0.039816</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.151314499511307</v>
+        <v>5.777467018724906</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06241877594386238</v>
+        <v>0.06230508144552675</v>
       </c>
       <c r="C25">
-        <v>2402.363471775841</v>
+        <v>2389.409677167772</v>
       </c>
       <c r="D25">
-        <v>3152.696471775841</v>
+        <v>3174.413677167772</v>
       </c>
       <c r="E25">
-        <v>-485.4670000000001</v>
+        <v>-450.796</v>
       </c>
       <c r="F25">
-        <v>797.433</v>
+        <v>832.104</v>
       </c>
       <c r="G25">
         <v>47.1</v>
@@ -3343,28 +3343,28 @@
         <v>254.775</v>
       </c>
       <c r="M25">
-        <v>44.0980449</v>
+        <v>46.0153512</v>
       </c>
       <c r="N25">
-        <v>210.6769551</v>
+        <v>208.7596488</v>
       </c>
       <c r="O25">
-        <v>58.98954742800001</v>
+        <v>58.45270166400001</v>
       </c>
       <c r="P25">
-        <v>151.687407672</v>
+        <v>150.306947136</v>
       </c>
       <c r="Q25">
-        <v>292.287407672</v>
+        <v>290.906947136</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.06917025447254854</v>
+        <v>0.06940689663885098</v>
       </c>
       <c r="T25">
-        <v>0.539728740705509</v>
+        <v>0.5451939177563738</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.777467018724906</v>
+        <v>5.536739226278033</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06230508144552675</v>
+        <v>0.06219138694719111</v>
       </c>
       <c r="C26">
-        <v>2389.409677167772</v>
+        <v>2376.757153804201</v>
       </c>
       <c r="D26">
-        <v>3174.413677167772</v>
+        <v>3196.432153804201</v>
       </c>
       <c r="E26">
-        <v>-450.7960000000002</v>
+        <v>-416.1250000000001</v>
       </c>
       <c r="F26">
-        <v>832.1039999999999</v>
+        <v>866.775</v>
       </c>
       <c r="G26">
         <v>47.1</v>
@@ -3425,28 +3425,28 @@
         <v>254.775</v>
       </c>
       <c r="M26">
-        <v>46.0153512</v>
+        <v>47.9326575</v>
       </c>
       <c r="N26">
-        <v>208.7596488</v>
+        <v>206.8423425</v>
       </c>
       <c r="O26">
-        <v>58.45270166400001</v>
+        <v>57.9158559</v>
       </c>
       <c r="P26">
-        <v>150.306947136</v>
+        <v>148.9264866</v>
       </c>
       <c r="Q26">
-        <v>290.906947136</v>
+        <v>289.5264866</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.06940689663885098</v>
+        <v>0.06964984926292149</v>
       </c>
       <c r="T26">
-        <v>0.5451939177563738</v>
+        <v>0.5508048328619282</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.536739226278034</v>
+        <v>5.315269657226913</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06219138694719111</v>
+        <v>0.06207769244885548</v>
       </c>
       <c r="C27">
-        <v>2376.757153804201</v>
+        <v>2364.412214536242</v>
       </c>
       <c r="D27">
-        <v>3196.432153804201</v>
+        <v>3218.758214536242</v>
       </c>
       <c r="E27">
-        <v>-416.1250000000001</v>
+        <v>-381.4540000000001</v>
       </c>
       <c r="F27">
-        <v>866.775</v>
+        <v>901.446</v>
       </c>
       <c r="G27">
         <v>47.1</v>
@@ -3507,28 +3507,28 @@
         <v>254.775</v>
       </c>
       <c r="M27">
-        <v>47.9326575</v>
+        <v>49.8499638</v>
       </c>
       <c r="N27">
-        <v>206.8423425</v>
+        <v>204.9250362</v>
       </c>
       <c r="O27">
-        <v>57.9158559</v>
+        <v>57.37901013600001</v>
       </c>
       <c r="P27">
-        <v>148.9264866</v>
+        <v>147.546026064</v>
       </c>
       <c r="Q27">
-        <v>289.5264866</v>
+        <v>288.146026064</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.06964984926292149</v>
+        <v>0.06989936817412903</v>
       </c>
       <c r="T27">
-        <v>0.5508048328619282</v>
+        <v>0.5565673943216869</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.315269657226913</v>
+        <v>5.110836208872031</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06207769244885548</v>
+        <v>0.06196399795051986</v>
       </c>
       <c r="C28">
-        <v>2364.412214536242</v>
+        <v>2352.381349828613</v>
       </c>
       <c r="D28">
-        <v>3218.758214536242</v>
+        <v>3241.398349828613</v>
       </c>
       <c r="E28">
-        <v>-381.4540000000001</v>
+        <v>-346.783</v>
       </c>
       <c r="F28">
-        <v>901.446</v>
+        <v>936.1170000000001</v>
       </c>
       <c r="G28">
         <v>47.1</v>
@@ -3589,28 +3589,28 @@
         <v>254.775</v>
       </c>
       <c r="M28">
-        <v>49.8499638</v>
+        <v>51.7672701</v>
       </c>
       <c r="N28">
-        <v>204.9250362</v>
+        <v>203.0077299</v>
       </c>
       <c r="O28">
-        <v>57.37901013600001</v>
+        <v>56.84216437200001</v>
       </c>
       <c r="P28">
-        <v>147.546026064</v>
+        <v>146.165565528</v>
       </c>
       <c r="Q28">
-        <v>288.146026064</v>
+        <v>286.765565528</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.06989936817412903</v>
+        <v>0.07015572321989022</v>
       </c>
       <c r="T28">
-        <v>0.5565673943216869</v>
+        <v>0.5624878341776032</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.110836208872031</v>
+        <v>4.921545978913808</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06196399795051986</v>
+        <v>0.06185030345218423</v>
       </c>
       <c r="C29">
-        <v>2352.381349828613</v>
+        <v>2340.671234050371</v>
       </c>
       <c r="D29">
-        <v>3241.398349828613</v>
+        <v>3264.359234050371</v>
       </c>
       <c r="E29">
-        <v>-346.783</v>
+        <v>-312.1120000000001</v>
       </c>
       <c r="F29">
-        <v>936.1170000000001</v>
+        <v>970.788</v>
       </c>
       <c r="G29">
         <v>47.1</v>
@@ -3671,28 +3671,28 @@
         <v>254.775</v>
       </c>
       <c r="M29">
-        <v>51.7672701</v>
+        <v>53.6845764</v>
       </c>
       <c r="N29">
-        <v>203.0077299</v>
+        <v>201.0904236</v>
       </c>
       <c r="O29">
-        <v>56.84216437200001</v>
+        <v>56.30531860800001</v>
       </c>
       <c r="P29">
-        <v>146.165565528</v>
+        <v>144.785104992</v>
       </c>
       <c r="Q29">
-        <v>286.765565528</v>
+        <v>285.385104992</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07015572321989022</v>
+        <v>0.07041919923914476</v>
       </c>
       <c r="T29">
-        <v>0.5624878341776032</v>
+        <v>0.568572730696184</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.921545978913808</v>
+        <v>4.745776479666886</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06185030345218423</v>
+        <v>0.0617366089538486</v>
       </c>
       <c r="C30">
-        <v>2340.671234050371</v>
+        <v>2329.288732034946</v>
       </c>
       <c r="D30">
-        <v>3264.359234050371</v>
+        <v>3287.647732034946</v>
       </c>
       <c r="E30">
-        <v>-312.1120000000001</v>
+        <v>-277.441</v>
       </c>
       <c r="F30">
-        <v>970.788</v>
+        <v>1005.459</v>
       </c>
       <c r="G30">
         <v>47.1</v>
@@ -3753,28 +3753,28 @@
         <v>254.775</v>
       </c>
       <c r="M30">
-        <v>53.6845764</v>
+        <v>55.6018827</v>
       </c>
       <c r="N30">
-        <v>201.0904236</v>
+        <v>199.1731173</v>
       </c>
       <c r="O30">
-        <v>56.30531860800001</v>
+        <v>55.76847284400001</v>
       </c>
       <c r="P30">
-        <v>144.785104992</v>
+        <v>143.404644456</v>
       </c>
       <c r="Q30">
-        <v>285.385104992</v>
+        <v>284.004644456</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07041919923914476</v>
+        <v>0.07069009711809662</v>
       </c>
       <c r="T30">
-        <v>0.568572730696184</v>
+        <v>0.5748290327504993</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.745776479666886</v>
+        <v>4.582129014850786</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0617366089538486</v>
+        <v>0.06216291445551296</v>
       </c>
       <c r="C31">
-        <v>2329.288732034946</v>
+        <v>2208.964145107548</v>
       </c>
       <c r="D31">
-        <v>3287.647732034946</v>
+        <v>3201.994145107547</v>
       </c>
       <c r="E31">
-        <v>-277.4410000000001</v>
+        <v>-242.7700000000002</v>
       </c>
       <c r="F31">
-        <v>1005.459</v>
+        <v>1040.13</v>
       </c>
       <c r="G31">
         <v>47.1</v>
@@ -3835,45 +3835,45 @@
         <v>254.775</v>
       </c>
       <c r="M31">
-        <v>55.6018827</v>
+        <v>60.119514</v>
       </c>
       <c r="N31">
-        <v>199.1731173</v>
+        <v>194.655486</v>
       </c>
       <c r="O31">
-        <v>55.76847284400001</v>
+        <v>54.50353608</v>
       </c>
       <c r="P31">
-        <v>143.404644456</v>
+        <v>140.15194992</v>
       </c>
       <c r="Q31">
-        <v>284.004644456</v>
+        <v>280.75194992</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07069009711809662</v>
+        <v>0.07096873493644709</v>
       </c>
       <c r="T31">
-        <v>0.5748290327504993</v>
+        <v>0.5812640862920809</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.28</v>
       </c>
       <c r="W31">
-        <v>0.039816</v>
+        <v>0.041616</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.582129014850787</v>
+        <v>4.237808708832876</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06216291445551296</v>
+        <v>0.06206721995717733</v>
       </c>
       <c r="C32">
-        <v>2208.964145107548</v>
+        <v>2193.12938290333</v>
       </c>
       <c r="D32">
-        <v>3201.994145107547</v>
+        <v>3220.83038290333</v>
       </c>
       <c r="E32">
-        <v>-242.7700000000002</v>
+        <v>-208.0990000000002</v>
       </c>
       <c r="F32">
-        <v>1040.13</v>
+        <v>1074.801</v>
       </c>
       <c r="G32">
         <v>47.1</v>
@@ -3917,28 +3917,28 @@
         <v>254.775</v>
       </c>
       <c r="M32">
-        <v>60.119514</v>
+        <v>62.1234978</v>
       </c>
       <c r="N32">
-        <v>194.655486</v>
+        <v>192.6515022</v>
       </c>
       <c r="O32">
-        <v>54.50353608</v>
+        <v>53.94242061600001</v>
       </c>
       <c r="P32">
-        <v>140.15194992</v>
+        <v>138.709081584</v>
       </c>
       <c r="Q32">
-        <v>280.75194992</v>
+        <v>279.309081584</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07096873493644709</v>
+        <v>0.07125544921330049</v>
       </c>
       <c r="T32">
-        <v>0.5812640862920809</v>
+        <v>0.5878856631247228</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.237808708832876</v>
+        <v>4.101105202096331</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06206721995717733</v>
+        <v>0.0627779254588417</v>
       </c>
       <c r="C33">
-        <v>2193.12938290333</v>
+        <v>2023.632612899429</v>
       </c>
       <c r="D33">
-        <v>3220.83038290333</v>
+        <v>3086.00461289943</v>
       </c>
       <c r="E33">
-        <v>-208.0990000000002</v>
+        <v>-173.4280000000001</v>
       </c>
       <c r="F33">
-        <v>1074.801</v>
+        <v>1109.472</v>
       </c>
       <c r="G33">
         <v>47.1</v>
@@ -3999,45 +3999,45 @@
         <v>254.775</v>
       </c>
       <c r="M33">
-        <v>62.1234978</v>
+        <v>68.01063360000001</v>
       </c>
       <c r="N33">
-        <v>192.6515022</v>
+        <v>186.7643664</v>
       </c>
       <c r="O33">
-        <v>53.94242061600001</v>
+        <v>52.294022592</v>
       </c>
       <c r="P33">
-        <v>138.709081584</v>
+        <v>134.470343808</v>
       </c>
       <c r="Q33">
-        <v>279.309081584</v>
+        <v>275.070343808</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07125544921330049</v>
+        <v>0.07155059626300252</v>
       </c>
       <c r="T33">
-        <v>0.5878856631247228</v>
+        <v>0.5947019922171483</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0.28</v>
       </c>
       <c r="W33">
-        <v>0.041616</v>
+        <v>0.044136</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.101105202096331</v>
+        <v>3.746105373733792</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0627779254588417</v>
+        <v>0.06270743096050607</v>
       </c>
       <c r="C34">
-        <v>2023.632612899429</v>
+        <v>2001.828520211128</v>
       </c>
       <c r="D34">
-        <v>3086.00461289943</v>
+        <v>3098.871520211128</v>
       </c>
       <c r="E34">
-        <v>-173.4280000000001</v>
+        <v>-138.7570000000001</v>
       </c>
       <c r="F34">
-        <v>1109.472</v>
+        <v>1144.143</v>
       </c>
       <c r="G34">
         <v>47.1</v>
@@ -4081,28 +4081,28 @@
         <v>254.775</v>
       </c>
       <c r="M34">
-        <v>68.01063360000001</v>
+        <v>70.1359659</v>
       </c>
       <c r="N34">
-        <v>186.7643664</v>
+        <v>184.6390341</v>
       </c>
       <c r="O34">
-        <v>52.294022592</v>
+        <v>51.698929548</v>
       </c>
       <c r="P34">
-        <v>134.470343808</v>
+        <v>132.940104552</v>
       </c>
       <c r="Q34">
-        <v>275.070343808</v>
+        <v>273.540104552</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07155059626300252</v>
+        <v>0.07185455367239714</v>
       </c>
       <c r="T34">
-        <v>0.5947019922171483</v>
+        <v>0.6017217938197954</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.746105373733792</v>
+        <v>3.632587029075192</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06270743096050607</v>
+        <v>0.06263693646217046</v>
       </c>
       <c r="C35">
-        <v>2001.828520211128</v>
+        <v>1980.132172322849</v>
       </c>
       <c r="D35">
-        <v>3098.871520211128</v>
+        <v>3111.846172322849</v>
       </c>
       <c r="E35">
-        <v>-138.7570000000001</v>
+        <v>-104.086</v>
       </c>
       <c r="F35">
-        <v>1144.143</v>
+        <v>1178.814</v>
       </c>
       <c r="G35">
         <v>47.1</v>
@@ -4163,28 +4163,28 @@
         <v>254.775</v>
       </c>
       <c r="M35">
-        <v>70.1359659</v>
+        <v>72.2612982</v>
       </c>
       <c r="N35">
-        <v>184.6390341</v>
+        <v>182.5137018</v>
       </c>
       <c r="O35">
-        <v>51.698929548</v>
+        <v>51.10383650400001</v>
       </c>
       <c r="P35">
-        <v>132.940104552</v>
+        <v>131.409865296</v>
       </c>
       <c r="Q35">
-        <v>273.540104552</v>
+        <v>272.009865296</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07185455367239714</v>
+        <v>0.07216772191237948</v>
       </c>
       <c r="T35">
-        <v>0.6017217938197954</v>
+        <v>0.6089543166831289</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.632587029075192</v>
+        <v>3.525746234102393</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06263693646217046</v>
+        <v>0.06327204196383482</v>
       </c>
       <c r="C36">
-        <v>1980.132172322849</v>
+        <v>1832.346138117559</v>
       </c>
       <c r="D36">
-        <v>3111.846172322849</v>
+        <v>2998.73113811756</v>
       </c>
       <c r="E36">
-        <v>-104.086</v>
+        <v>-69.41499999999996</v>
       </c>
       <c r="F36">
-        <v>1178.814</v>
+        <v>1213.485</v>
       </c>
       <c r="G36">
         <v>47.1</v>
@@ -4245,45 +4245,45 @@
         <v>254.775</v>
       </c>
       <c r="M36">
-        <v>72.2612982</v>
+        <v>77.78438850000002</v>
       </c>
       <c r="N36">
-        <v>182.5137018</v>
+        <v>176.9906115</v>
       </c>
       <c r="O36">
-        <v>51.10383650400001</v>
+        <v>49.55737122000001</v>
       </c>
       <c r="P36">
-        <v>131.409865296</v>
+        <v>127.43324028</v>
       </c>
       <c r="Q36">
-        <v>272.009865296</v>
+        <v>268.03324028</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07216772191237948</v>
+        <v>0.07249052609820741</v>
       </c>
       <c r="T36">
-        <v>0.6089543166831289</v>
+        <v>0.6164093787114879</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.28</v>
       </c>
       <c r="W36">
-        <v>0.044136</v>
+        <v>0.046152</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.525746234102393</v>
+        <v>3.275400178790374</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06327204196383482</v>
+        <v>0.0632217074654992</v>
       </c>
       <c r="C37">
-        <v>1832.346138117559</v>
+        <v>1806.339020677835</v>
       </c>
       <c r="D37">
-        <v>2998.73113811756</v>
+        <v>3007.395020677835</v>
       </c>
       <c r="E37">
-        <v>-69.41499999999996</v>
+        <v>-34.74399999999991</v>
       </c>
       <c r="F37">
-        <v>1213.485</v>
+        <v>1248.156</v>
       </c>
       <c r="G37">
         <v>47.1</v>
@@ -4327,28 +4327,28 @@
         <v>254.775</v>
       </c>
       <c r="M37">
-        <v>77.78438850000002</v>
+        <v>80.00679960000002</v>
       </c>
       <c r="N37">
-        <v>176.9906115</v>
+        <v>174.7682004</v>
       </c>
       <c r="O37">
-        <v>49.55737122000001</v>
+        <v>48.935096112</v>
       </c>
       <c r="P37">
-        <v>127.43324028</v>
+        <v>125.833104288</v>
       </c>
       <c r="Q37">
-        <v>268.03324028</v>
+        <v>266.433104288</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07249052609820741</v>
+        <v>0.07282341791484249</v>
       </c>
       <c r="T37">
-        <v>0.6164093787114879</v>
+        <v>0.6240974114282332</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.275400178790374</v>
+        <v>3.184416840490642</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0632217074654992</v>
+        <v>0.06317137296716357</v>
       </c>
       <c r="C38">
-        <v>1806.339020677835</v>
+        <v>1780.382111380338</v>
       </c>
       <c r="D38">
-        <v>3007.395020677835</v>
+        <v>3016.109111380338</v>
       </c>
       <c r="E38">
-        <v>-34.74400000000014</v>
+        <v>-0.07300000000009277</v>
       </c>
       <c r="F38">
-        <v>1248.156</v>
+        <v>1282.827</v>
       </c>
       <c r="G38">
         <v>47.1</v>
@@ -4409,28 +4409,28 @@
         <v>254.775</v>
       </c>
       <c r="M38">
-        <v>80.00679960000001</v>
+        <v>82.22921070000001</v>
       </c>
       <c r="N38">
-        <v>174.7682004</v>
+        <v>172.5457893</v>
       </c>
       <c r="O38">
-        <v>48.93509611200001</v>
+        <v>48.312821004</v>
       </c>
       <c r="P38">
-        <v>125.833104288</v>
+        <v>124.232968296</v>
       </c>
       <c r="Q38">
-        <v>266.433104288</v>
+        <v>264.832968296</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07282341791484249</v>
+        <v>0.07316687772565646</v>
       </c>
       <c r="T38">
-        <v>0.6240974114282332</v>
+        <v>0.6320295086756688</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.184416840490643</v>
+        <v>3.098351520477382</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06317137296716357</v>
+        <v>0.06312103846882794</v>
       </c>
       <c r="C39">
-        <v>1780.382111380338</v>
+        <v>1754.475847935832</v>
       </c>
       <c r="D39">
-        <v>3016.109111380338</v>
+        <v>3024.873847935832</v>
       </c>
       <c r="E39">
-        <v>-0.07300000000009277</v>
+        <v>34.59799999999996</v>
       </c>
       <c r="F39">
-        <v>1282.827</v>
+        <v>1317.498</v>
       </c>
       <c r="G39">
         <v>47.1</v>
@@ -4491,28 +4491,28 @@
         <v>254.775</v>
       </c>
       <c r="M39">
-        <v>82.22921070000001</v>
+        <v>84.45162180000001</v>
       </c>
       <c r="N39">
-        <v>172.5457893</v>
+        <v>170.3233782</v>
       </c>
       <c r="O39">
-        <v>48.312821004</v>
+        <v>47.690545896</v>
       </c>
       <c r="P39">
-        <v>124.232968296</v>
+        <v>122.632832304</v>
       </c>
       <c r="Q39">
-        <v>264.832968296</v>
+        <v>263.232832304</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07316687772565646</v>
+        <v>0.07352141688520634</v>
       </c>
       <c r="T39">
-        <v>0.6320295086756688</v>
+        <v>0.6402174800278604</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.098351520477382</v>
+        <v>3.016815954149029</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06312103846882794</v>
+        <v>0.06526094397049231</v>
       </c>
       <c r="C40">
-        <v>1754.475847935832</v>
+        <v>1387.192812319616</v>
       </c>
       <c r="D40">
-        <v>3024.873847935832</v>
+        <v>2692.261812319616</v>
       </c>
       <c r="E40">
-        <v>34.59799999999996</v>
+        <v>69.26900000000001</v>
       </c>
       <c r="F40">
-        <v>1317.498</v>
+        <v>1352.169</v>
       </c>
       <c r="G40">
         <v>47.1</v>
@@ -4573,45 +4573,45 @@
         <v>254.775</v>
       </c>
       <c r="M40">
-        <v>84.45162180000001</v>
+        <v>97.22095110000001</v>
       </c>
       <c r="N40">
-        <v>170.3233782</v>
+        <v>157.5540489</v>
       </c>
       <c r="O40">
-        <v>47.690545896</v>
+        <v>44.115133692</v>
       </c>
       <c r="P40">
-        <v>122.632832304</v>
+        <v>113.438915208</v>
       </c>
       <c r="Q40">
-        <v>263.232832304</v>
+        <v>254.038915208</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07352141688520634</v>
+        <v>0.07388758027949559</v>
       </c>
       <c r="T40">
-        <v>0.6402174800278604</v>
+        <v>0.648673909457173</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0.28</v>
       </c>
       <c r="W40">
-        <v>0.046152</v>
+        <v>0.051768</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.016815954149029</v>
+        <v>2.62057711961635</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06526094397049231</v>
+        <v>0.06526676947215668</v>
       </c>
       <c r="C41">
-        <v>1387.192812319616</v>
+        <v>1351.716143166807</v>
       </c>
       <c r="D41">
-        <v>2692.261812319616</v>
+        <v>2691.456143166807</v>
       </c>
       <c r="E41">
-        <v>69.26900000000001</v>
+        <v>103.9400000000001</v>
       </c>
       <c r="F41">
-        <v>1352.169</v>
+        <v>1386.84</v>
       </c>
       <c r="G41">
         <v>47.1</v>
@@ -4655,28 +4655,28 @@
         <v>254.775</v>
       </c>
       <c r="M41">
-        <v>97.22095110000001</v>
+        <v>99.71379600000002</v>
       </c>
       <c r="N41">
-        <v>157.5540489</v>
+        <v>155.061204</v>
       </c>
       <c r="O41">
-        <v>44.115133692</v>
+        <v>43.41713712</v>
       </c>
       <c r="P41">
-        <v>113.438915208</v>
+        <v>111.64406688</v>
       </c>
       <c r="Q41">
-        <v>254.038915208</v>
+        <v>252.24406688</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.07388758027949559</v>
+        <v>0.07426594912026113</v>
       </c>
       <c r="T41">
-        <v>0.648673909457173</v>
+        <v>0.6574122198674627</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.62057711961635</v>
+        <v>2.555062691625941</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06526676947215668</v>
+        <v>0.06642387497382105</v>
       </c>
       <c r="C42">
-        <v>1351.716143166807</v>
+        <v>1166.040605236868</v>
       </c>
       <c r="D42">
-        <v>2691.456143166807</v>
+        <v>2540.451605236868</v>
       </c>
       <c r="E42">
-        <v>103.9400000000001</v>
+        <v>138.6109999999999</v>
       </c>
       <c r="F42">
-        <v>1386.84</v>
+        <v>1421.511</v>
       </c>
       <c r="G42">
         <v>47.1</v>
@@ -4737,45 +4737,45 @@
         <v>254.775</v>
       </c>
       <c r="M42">
-        <v>99.71379600000002</v>
+        <v>107.7505338</v>
       </c>
       <c r="N42">
-        <v>155.061204</v>
+        <v>147.0244662</v>
       </c>
       <c r="O42">
-        <v>43.41713712</v>
+        <v>41.16685053600001</v>
       </c>
       <c r="P42">
-        <v>111.64406688</v>
+        <v>105.857615664</v>
       </c>
       <c r="Q42">
-        <v>252.24406688</v>
+        <v>246.457615664</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.07426594912026113</v>
+        <v>0.07465714402342551</v>
       </c>
       <c r="T42">
-        <v>0.6574122198674627</v>
+        <v>0.6664467441899656</v>
       </c>
       <c r="U42">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V42">
         <v>0.28</v>
       </c>
       <c r="W42">
-        <v>0.051768</v>
+        <v>0.054576</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.555062691625941</v>
+        <v>2.364489446269453</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06642387497382105</v>
+        <v>0.06645778047548541</v>
       </c>
       <c r="C43">
-        <v>1166.040605236868</v>
+        <v>1127.199975966588</v>
       </c>
       <c r="D43">
-        <v>2540.451605236868</v>
+        <v>2536.281975966589</v>
       </c>
       <c r="E43">
-        <v>138.6109999999999</v>
+        <v>173.2819999999999</v>
       </c>
       <c r="F43">
-        <v>1421.511</v>
+        <v>1456.182</v>
       </c>
       <c r="G43">
         <v>47.1</v>
@@ -4819,28 +4819,28 @@
         <v>254.775</v>
       </c>
       <c r="M43">
-        <v>107.7505338</v>
+        <v>110.3785956</v>
       </c>
       <c r="N43">
-        <v>147.0244662</v>
+        <v>144.3964044</v>
       </c>
       <c r="O43">
-        <v>41.16685053600001</v>
+        <v>40.43099323200001</v>
       </c>
       <c r="P43">
-        <v>105.857615664</v>
+        <v>103.965411168</v>
       </c>
       <c r="Q43">
-        <v>246.457615664</v>
+        <v>244.565411168</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.07465714402342551</v>
+        <v>0.07506182840600933</v>
       </c>
       <c r="T43">
-        <v>0.6664467441899656</v>
+        <v>0.6757928038339341</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.364489446269453</v>
+        <v>2.308192078501133</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06645778047548542</v>
+        <v>0.0664916859771498</v>
       </c>
       <c r="C44">
-        <v>1127.199975966587</v>
+        <v>1088.373011447677</v>
       </c>
       <c r="D44">
-        <v>2536.281975966587</v>
+        <v>2532.126011447677</v>
       </c>
       <c r="E44">
-        <v>173.2819999999999</v>
+        <v>207.9529999999997</v>
       </c>
       <c r="F44">
-        <v>1456.182</v>
+        <v>1490.853</v>
       </c>
       <c r="G44">
         <v>47.1</v>
@@ -4901,28 +4901,28 @@
         <v>254.775</v>
       </c>
       <c r="M44">
-        <v>110.3785956</v>
+        <v>113.0066574</v>
       </c>
       <c r="N44">
-        <v>144.3964044</v>
+        <v>141.7683426</v>
       </c>
       <c r="O44">
-        <v>40.43099323200001</v>
+        <v>39.69513592800001</v>
       </c>
       <c r="P44">
-        <v>103.965411168</v>
+        <v>102.073206672</v>
       </c>
       <c r="Q44">
-        <v>244.565411168</v>
+        <v>242.673206672</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.07506182840600933</v>
+        <v>0.07548071224061367</v>
       </c>
       <c r="T44">
-        <v>0.6757928038339341</v>
+        <v>0.6854667953952349</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.308192078501133</v>
+        <v>2.254513192954595</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0664916859771498</v>
+        <v>0.06652559147881416</v>
       </c>
       <c r="C45">
-        <v>1088.373011447677</v>
+        <v>1049.559644616637</v>
       </c>
       <c r="D45">
-        <v>2532.126011447677</v>
+        <v>2527.983644616637</v>
       </c>
       <c r="E45">
-        <v>207.9529999999997</v>
+        <v>242.6239999999998</v>
       </c>
       <c r="F45">
-        <v>1490.853</v>
+        <v>1525.524</v>
       </c>
       <c r="G45">
         <v>47.1</v>
@@ -4983,28 +4983,28 @@
         <v>254.775</v>
       </c>
       <c r="M45">
-        <v>113.0066574</v>
+        <v>115.6347192</v>
       </c>
       <c r="N45">
-        <v>141.7683426</v>
+        <v>139.1402808</v>
       </c>
       <c r="O45">
-        <v>39.69513592800001</v>
+        <v>38.95927862400001</v>
       </c>
       <c r="P45">
-        <v>102.073206672</v>
+        <v>100.181002176</v>
       </c>
       <c r="Q45">
-        <v>242.673206672</v>
+        <v>240.781002176</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.07548071224061367</v>
+        <v>0.07591455621216815</v>
       </c>
       <c r="T45">
-        <v>0.6854667953952349</v>
+        <v>0.6954862866551537</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.254513192954595</v>
+        <v>2.203274256751081</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06652559147881416</v>
+        <v>0.06655949698047853</v>
       </c>
       <c r="C46">
-        <v>1049.559644616637</v>
+        <v>1010.759808848091</v>
       </c>
       <c r="D46">
-        <v>2527.983644616637</v>
+        <v>2523.854808848091</v>
       </c>
       <c r="E46">
-        <v>242.6239999999998</v>
+        <v>277.2949999999998</v>
       </c>
       <c r="F46">
-        <v>1525.524</v>
+        <v>1560.195</v>
       </c>
       <c r="G46">
         <v>47.1</v>
@@ -5065,28 +5065,28 @@
         <v>254.775</v>
       </c>
       <c r="M46">
-        <v>115.6347192</v>
+        <v>118.262781</v>
       </c>
       <c r="N46">
-        <v>139.1402808</v>
+        <v>136.512219</v>
       </c>
       <c r="O46">
-        <v>38.95927862400001</v>
+        <v>38.22342132000001</v>
       </c>
       <c r="P46">
-        <v>100.181002176</v>
+        <v>98.28879768000002</v>
       </c>
       <c r="Q46">
-        <v>240.781002176</v>
+        <v>238.88879768</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.07591455621216815</v>
+        <v>0.07636417632814278</v>
       </c>
       <c r="T46">
-        <v>0.6954862866551537</v>
+        <v>0.7058701230517964</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.203274256751081</v>
+        <v>2.154312606601057</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06655949698047853</v>
+        <v>0.0665934024821429</v>
       </c>
       <c r="C47">
-        <v>1010.759808848091</v>
+        <v>971.9734379512142</v>
       </c>
       <c r="D47">
-        <v>2523.854808848091</v>
+        <v>2519.739437951214</v>
       </c>
       <c r="E47">
-        <v>277.2949999999998</v>
+        <v>311.9659999999999</v>
       </c>
       <c r="F47">
-        <v>1560.195</v>
+        <v>1594.866</v>
       </c>
       <c r="G47">
         <v>47.1</v>
@@ -5147,28 +5147,28 @@
         <v>254.775</v>
       </c>
       <c r="M47">
-        <v>118.262781</v>
+        <v>120.8908428</v>
       </c>
       <c r="N47">
-        <v>136.512219</v>
+        <v>133.8841572</v>
       </c>
       <c r="O47">
-        <v>38.22342132000001</v>
+        <v>37.48756401600001</v>
       </c>
       <c r="P47">
-        <v>98.28879768000002</v>
+        <v>96.396593184</v>
       </c>
       <c r="Q47">
-        <v>238.88879768</v>
+        <v>236.996593184</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.07636417632814278</v>
+        <v>0.07683044904100537</v>
       </c>
       <c r="T47">
-        <v>0.7058701230517964</v>
+        <v>0.7166385459816484</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.154312606601057</v>
+        <v>2.107479723848861</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0665934024821429</v>
+        <v>0.06662730798380728</v>
       </c>
       <c r="C48">
-        <v>971.9734379512142</v>
+        <v>933.2004661662061</v>
       </c>
       <c r="D48">
-        <v>2519.739437951214</v>
+        <v>2515.637466166206</v>
       </c>
       <c r="E48">
-        <v>311.9659999999999</v>
+        <v>346.6369999999999</v>
       </c>
       <c r="F48">
-        <v>1594.866</v>
+        <v>1629.537</v>
       </c>
       <c r="G48">
         <v>47.1</v>
@@ -5229,28 +5229,28 @@
         <v>254.775</v>
       </c>
       <c r="M48">
-        <v>120.8908428</v>
+        <v>123.5189046</v>
       </c>
       <c r="N48">
-        <v>133.8841572</v>
+        <v>131.2560954</v>
       </c>
       <c r="O48">
-        <v>37.48756401600001</v>
+        <v>36.751706712</v>
       </c>
       <c r="P48">
-        <v>96.396593184</v>
+        <v>94.50438868799999</v>
       </c>
       <c r="Q48">
-        <v>236.996593184</v>
+        <v>235.104388688</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.07683044904100537</v>
+        <v>0.07731431695057976</v>
       </c>
       <c r="T48">
-        <v>0.7166385459816484</v>
+        <v>0.727813324493759</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.107479723848861</v>
+        <v>2.062639729724416</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06662730798380728</v>
+        <v>0.06666121348547165</v>
       </c>
       <c r="C49">
-        <v>933.2004661662061</v>
+        <v>894.4408281607789</v>
       </c>
       <c r="D49">
-        <v>2515.637466166206</v>
+        <v>2511.548828160779</v>
       </c>
       <c r="E49">
-        <v>346.6369999999999</v>
+        <v>381.308</v>
       </c>
       <c r="F49">
-        <v>1629.537</v>
+        <v>1664.208</v>
       </c>
       <c r="G49">
         <v>47.1</v>
@@ -5311,28 +5311,28 @@
         <v>254.775</v>
       </c>
       <c r="M49">
-        <v>123.5189046</v>
+        <v>126.1469664</v>
       </c>
       <c r="N49">
-        <v>131.2560954</v>
+        <v>128.6280336</v>
       </c>
       <c r="O49">
-        <v>36.751706712</v>
+        <v>36.015849408</v>
       </c>
       <c r="P49">
-        <v>94.50438868799999</v>
+        <v>92.61218419199997</v>
       </c>
       <c r="Q49">
-        <v>235.104388688</v>
+        <v>233.212184192</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.07731431695057976</v>
+        <v>0.07781679516436854</v>
       </c>
       <c r="T49">
-        <v>0.727813324493759</v>
+        <v>0.7394179021794123</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.062639729724416</v>
+        <v>2.019668068688491</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06666121348547165</v>
+        <v>0.07170487898713601</v>
       </c>
       <c r="C50">
-        <v>894.4408281607791</v>
+        <v>370.7726710371908</v>
       </c>
       <c r="D50">
-        <v>2511.548828160779</v>
+        <v>2022.551671037191</v>
       </c>
       <c r="E50">
-        <v>381.3079999999998</v>
+        <v>415.9789999999998</v>
       </c>
       <c r="F50">
-        <v>1664.208</v>
+        <v>1698.879</v>
       </c>
       <c r="G50">
         <v>47.1</v>
@@ -5393,45 +5393,45 @@
         <v>254.775</v>
       </c>
       <c r="M50">
-        <v>126.1469664</v>
+        <v>152.89911</v>
       </c>
       <c r="N50">
-        <v>128.6280336</v>
+        <v>101.87589</v>
       </c>
       <c r="O50">
-        <v>36.01584940800001</v>
+        <v>28.52524920000001</v>
       </c>
       <c r="P50">
-        <v>92.612184192</v>
+        <v>73.35064080000001</v>
       </c>
       <c r="Q50">
-        <v>233.212184192</v>
+        <v>213.9506408</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.07781679516436854</v>
+        <v>0.07833897840614903</v>
       </c>
       <c r="T50">
-        <v>0.7394179021794122</v>
+        <v>0.7514775613429342</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V50">
         <v>0.28</v>
       </c>
       <c r="W50">
-        <v>0.054576</v>
+        <v>0.0648</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.019668068688492</v>
+        <v>1.666294852860818</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07170487898713601</v>
+        <v>0.07184102448880039</v>
       </c>
       <c r="C51">
-        <v>370.7726710371908</v>
+        <v>325.5275359061432</v>
       </c>
       <c r="D51">
-        <v>2022.551671037191</v>
+        <v>2011.977535906143</v>
       </c>
       <c r="E51">
-        <v>415.9789999999998</v>
+        <v>450.6499999999999</v>
       </c>
       <c r="F51">
-        <v>1698.879</v>
+        <v>1733.55</v>
       </c>
       <c r="G51">
         <v>47.1</v>
@@ -5475,28 +5475,28 @@
         <v>254.775</v>
       </c>
       <c r="M51">
-        <v>152.89911</v>
+        <v>156.0195</v>
       </c>
       <c r="N51">
-        <v>101.87589</v>
+        <v>98.75550000000001</v>
       </c>
       <c r="O51">
-        <v>28.52524920000001</v>
+        <v>27.65154000000001</v>
       </c>
       <c r="P51">
-        <v>73.35064080000001</v>
+        <v>71.10396</v>
       </c>
       <c r="Q51">
-        <v>213.9506408</v>
+        <v>211.70396</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.07833897840614903</v>
+        <v>0.07888204897760077</v>
       </c>
       <c r="T51">
-        <v>0.7514775613429342</v>
+        <v>0.7640196068729972</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.666294852860818</v>
+        <v>1.632968955803602</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07184102448880039</v>
+        <v>0.07197716999046476</v>
       </c>
       <c r="C52">
-        <v>325.5275359061432</v>
+        <v>280.3923913457056</v>
       </c>
       <c r="D52">
-        <v>2011.977535906143</v>
+        <v>2001.513391345705</v>
       </c>
       <c r="E52">
-        <v>450.6499999999999</v>
+        <v>485.3209999999999</v>
       </c>
       <c r="F52">
-        <v>1733.55</v>
+        <v>1768.221</v>
       </c>
       <c r="G52">
         <v>47.1</v>
@@ -5557,28 +5557,28 @@
         <v>254.775</v>
       </c>
       <c r="M52">
-        <v>156.0195</v>
+        <v>159.13989</v>
       </c>
       <c r="N52">
-        <v>98.75550000000001</v>
+        <v>95.63511</v>
       </c>
       <c r="O52">
-        <v>27.65154000000001</v>
+        <v>26.7778308</v>
       </c>
       <c r="P52">
-        <v>71.10396</v>
+        <v>68.85727919999999</v>
       </c>
       <c r="Q52">
-        <v>211.70396</v>
+        <v>209.4572792</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.07888204897760077</v>
+        <v>0.07944728569482604</v>
       </c>
       <c r="T52">
-        <v>0.7640196068729972</v>
+        <v>0.777073572628777</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.632968955803602</v>
+        <v>1.600949956670197</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07197716999046476</v>
+        <v>0.07211331549212913</v>
       </c>
       <c r="C53">
-        <v>280.3923913457056</v>
+        <v>235.3655300771313</v>
       </c>
       <c r="D53">
-        <v>2001.513391345705</v>
+        <v>1991.157530077131</v>
       </c>
       <c r="E53">
-        <v>485.3209999999999</v>
+        <v>519.992</v>
       </c>
       <c r="F53">
-        <v>1768.221</v>
+        <v>1802.892</v>
       </c>
       <c r="G53">
         <v>47.1</v>
@@ -5639,28 +5639,28 @@
         <v>254.775</v>
       </c>
       <c r="M53">
-        <v>159.13989</v>
+        <v>162.26028</v>
       </c>
       <c r="N53">
-        <v>95.63511</v>
+        <v>92.51472000000001</v>
       </c>
       <c r="O53">
-        <v>26.7778308</v>
+        <v>25.90412160000001</v>
       </c>
       <c r="P53">
-        <v>68.85727919999999</v>
+        <v>66.6105984</v>
       </c>
       <c r="Q53">
-        <v>209.4572792</v>
+        <v>207.2105984</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.07944728569482604</v>
+        <v>0.08003607394193568</v>
       </c>
       <c r="T53">
-        <v>0.777073572628777</v>
+        <v>0.7906714536243808</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.600949956670197</v>
+        <v>1.570162457503463</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07211331549212913</v>
+        <v>0.07224946099379351</v>
       </c>
       <c r="C54">
-        <v>235.3655300771313</v>
+        <v>190.4452799737448</v>
       </c>
       <c r="D54">
-        <v>1991.157530077131</v>
+        <v>1980.908279973745</v>
       </c>
       <c r="E54">
-        <v>519.992</v>
+        <v>554.663</v>
       </c>
       <c r="F54">
-        <v>1802.892</v>
+        <v>1837.563</v>
       </c>
       <c r="G54">
         <v>47.1</v>
@@ -5721,28 +5721,28 @@
         <v>254.775</v>
       </c>
       <c r="M54">
-        <v>162.26028</v>
+        <v>165.38067</v>
       </c>
       <c r="N54">
-        <v>92.51472000000001</v>
+        <v>89.39433</v>
       </c>
       <c r="O54">
-        <v>25.90412160000001</v>
+        <v>25.0304124</v>
       </c>
       <c r="P54">
-        <v>66.6105984</v>
+        <v>64.36391759999999</v>
       </c>
       <c r="Q54">
-        <v>207.2105984</v>
+        <v>204.9639176</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08003607394193568</v>
+        <v>0.08064991700807128</v>
       </c>
       <c r="T54">
-        <v>0.7906714536243808</v>
+        <v>0.8048479678538403</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.570162457503463</v>
+        <v>1.540536750758115</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07224946099379351</v>
+        <v>0.07238560649545786</v>
       </c>
       <c r="C55">
-        <v>190.4452799737448</v>
+        <v>145.6300031608696</v>
       </c>
       <c r="D55">
-        <v>1980.908279973745</v>
+        <v>1970.76400316087</v>
       </c>
       <c r="E55">
-        <v>554.663</v>
+        <v>589.3340000000001</v>
       </c>
       <c r="F55">
-        <v>1837.563</v>
+        <v>1872.234</v>
       </c>
       <c r="G55">
         <v>47.1</v>
@@ -5803,28 +5803,28 @@
         <v>254.775</v>
       </c>
       <c r="M55">
-        <v>165.38067</v>
+        <v>168.50106</v>
       </c>
       <c r="N55">
-        <v>89.39433</v>
+        <v>86.27394000000001</v>
       </c>
       <c r="O55">
-        <v>25.0304124</v>
+        <v>24.15670320000001</v>
       </c>
       <c r="P55">
-        <v>64.36391759999999</v>
+        <v>62.1172368</v>
       </c>
       <c r="Q55">
-        <v>204.9639176</v>
+        <v>202.7172368</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.08064991700807128</v>
+        <v>0.08129044890316928</v>
       </c>
       <c r="T55">
-        <v>0.8048479678538403</v>
+        <v>0.8196408522671891</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.540536750758115</v>
+        <v>1.512008292410742</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07238560649545786</v>
+        <v>0.09731254861691108</v>
       </c>
       <c r="C56">
-        <v>145.6300031608696</v>
+        <v>-842.6944572254245</v>
       </c>
       <c r="D56">
-        <v>1970.76400316087</v>
+        <v>1017.110542774576</v>
       </c>
       <c r="E56">
-        <v>589.3340000000001</v>
+        <v>624.0050000000001</v>
       </c>
       <c r="F56">
-        <v>1872.234</v>
+        <v>1906.905</v>
       </c>
       <c r="G56">
         <v>47.1</v>
@@ -5885,45 +5885,45 @@
         <v>254.775</v>
       </c>
       <c r="M56">
-        <v>168.50106</v>
+        <v>279.933654</v>
       </c>
       <c r="N56">
-        <v>86.27394000000001</v>
+        <v>-25.15865400000004</v>
       </c>
       <c r="O56">
-        <v>24.15670320000001</v>
+        <v>-7.044423120000012</v>
       </c>
       <c r="P56">
-        <v>62.1172368</v>
+        <v>-18.11423088000003</v>
       </c>
       <c r="Q56">
-        <v>202.7172368</v>
+        <v>122.48576912</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.08129044890316928</v>
+        <v>0.08255101657785875</v>
       </c>
       <c r="T56">
-        <v>0.8196408522671891</v>
+        <v>0.8487532696965071</v>
       </c>
       <c r="U56">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.28</v>
+        <v>0.2548353832440596</v>
       </c>
       <c r="W56">
-        <v>0.0648</v>
+        <v>0.1093901657397721</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.512008292410742</v>
+        <v>0.9101263687287844</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09731254861691108</v>
+        <v>0.09832254861691106</v>
       </c>
       <c r="C57">
-        <v>-842.6944572254245</v>
+        <v>-896.9243262303366</v>
       </c>
       <c r="D57">
-        <v>1017.110542774576</v>
+        <v>997.5516737696635</v>
       </c>
       <c r="E57">
-        <v>624.0050000000001</v>
+        <v>658.6759999999999</v>
       </c>
       <c r="F57">
-        <v>1906.905</v>
+        <v>1941.576</v>
       </c>
       <c r="G57">
         <v>47.1</v>
@@ -5967,37 +5967,37 @@
         <v>254.775</v>
       </c>
       <c r="M57">
-        <v>279.933654</v>
+        <v>285.0233568</v>
       </c>
       <c r="N57">
-        <v>-25.15865400000004</v>
+        <v>-30.24835680000004</v>
       </c>
       <c r="O57">
-        <v>-7.044423120000012</v>
+        <v>-8.469539904000012</v>
       </c>
       <c r="P57">
-        <v>-18.11423088000003</v>
+        <v>-21.77881689600003</v>
       </c>
       <c r="Q57">
-        <v>122.48576912</v>
+        <v>118.821183104</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.08255101657785875</v>
+        <v>0.08338626695462825</v>
       </c>
       <c r="T57">
-        <v>0.8487532696965071</v>
+        <v>0.868043116735064</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2548353832440596</v>
+        <v>0.2502847514004157</v>
       </c>
       <c r="W57">
-        <v>0.1093901657397721</v>
+        <v>0.110058198494419</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9101263687287844</v>
+        <v>0.8938741121443419</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09832254861691106</v>
+        <v>0.09933254861691107</v>
       </c>
       <c r="C58">
-        <v>-896.9243262303366</v>
+        <v>-950.4161598453663</v>
       </c>
       <c r="D58">
-        <v>997.5516737696635</v>
+        <v>978.7308401546338</v>
       </c>
       <c r="E58">
-        <v>658.6759999999999</v>
+        <v>693.347</v>
       </c>
       <c r="F58">
-        <v>1941.576</v>
+        <v>1976.247</v>
       </c>
       <c r="G58">
         <v>47.1</v>
@@ -6049,37 +6049,37 @@
         <v>254.775</v>
       </c>
       <c r="M58">
-        <v>285.0233568</v>
+        <v>290.1130596</v>
       </c>
       <c r="N58">
-        <v>-30.24835680000004</v>
+        <v>-35.33805960000004</v>
       </c>
       <c r="O58">
-        <v>-8.469539904000012</v>
+        <v>-9.894656688000012</v>
       </c>
       <c r="P58">
-        <v>-21.77881689600003</v>
+        <v>-25.44340291200002</v>
       </c>
       <c r="Q58">
-        <v>118.821183104</v>
+        <v>115.156597088</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.08338626695462825</v>
+        <v>0.08426036618613125</v>
       </c>
       <c r="T58">
-        <v>0.868043116735064</v>
+        <v>0.8882301659614609</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2502847514004157</v>
+        <v>0.2458937908495313</v>
       </c>
       <c r="W58">
-        <v>0.110058198494419</v>
+        <v>0.1107027915032888</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8938741121443419</v>
+        <v>0.8781921101768972</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09933254861691107</v>
+        <v>0.1003425486169111</v>
       </c>
       <c r="C59">
-        <v>-950.4161598453663</v>
+        <v>-1003.210958120713</v>
       </c>
       <c r="D59">
-        <v>978.7308401546338</v>
+        <v>960.6070418792874</v>
       </c>
       <c r="E59">
-        <v>693.347</v>
+        <v>728.018</v>
       </c>
       <c r="F59">
-        <v>1976.247</v>
+        <v>2010.918</v>
       </c>
       <c r="G59">
         <v>47.1</v>
@@ -6131,37 +6131,37 @@
         <v>254.775</v>
       </c>
       <c r="M59">
-        <v>290.1130596</v>
+        <v>295.2027624</v>
       </c>
       <c r="N59">
-        <v>-35.33805960000004</v>
+        <v>-40.42776240000003</v>
       </c>
       <c r="O59">
-        <v>-9.894656688000012</v>
+        <v>-11.31977347200001</v>
       </c>
       <c r="P59">
-        <v>-25.44340291200002</v>
+        <v>-29.10798892800003</v>
       </c>
       <c r="Q59">
-        <v>115.156597088</v>
+        <v>111.492011072</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.08426036618613125</v>
+        <v>0.08517608919056294</v>
       </c>
       <c r="T59">
-        <v>0.8882301659614609</v>
+        <v>0.9093785032462576</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.2458937908495313</v>
+        <v>0.2416542427314359</v>
       </c>
       <c r="W59">
-        <v>0.1107027915032888</v>
+        <v>0.1113251571670252</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8781921101768972</v>
+        <v>0.8630508668979853</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1003425486169111</v>
+        <v>0.1013525486169111</v>
       </c>
       <c r="C60">
-        <v>-1003.210958120712</v>
+        <v>-1055.346739421543</v>
       </c>
       <c r="D60">
-        <v>960.6070418792874</v>
+        <v>943.142260578457</v>
       </c>
       <c r="E60">
-        <v>728.0179999999998</v>
+        <v>762.6889999999999</v>
       </c>
       <c r="F60">
-        <v>2010.918</v>
+        <v>2045.589</v>
       </c>
       <c r="G60">
         <v>47.1</v>
@@ -6213,37 +6213,37 @@
         <v>254.775</v>
       </c>
       <c r="M60">
-        <v>295.2027624</v>
+        <v>300.2924652</v>
       </c>
       <c r="N60">
-        <v>-40.42776240000003</v>
+        <v>-45.51746520000003</v>
       </c>
       <c r="O60">
-        <v>-11.31977347200001</v>
+        <v>-12.74489025600001</v>
       </c>
       <c r="P60">
-        <v>-29.10798892800003</v>
+        <v>-32.77257494400002</v>
       </c>
       <c r="Q60">
-        <v>111.492011072</v>
+        <v>107.827425056</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.08517608919056294</v>
+        <v>0.08613648160984495</v>
       </c>
       <c r="T60">
-        <v>0.9093785032462574</v>
+        <v>0.9315584667400684</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.2416542427314359</v>
+        <v>0.2375584081088692</v>
       </c>
       <c r="W60">
-        <v>0.1113251571670252</v>
+        <v>0.111926425689618</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8630508668979853</v>
+        <v>0.8484228861031042</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1013525486169111</v>
+        <v>0.102362548616911</v>
       </c>
       <c r="C61">
-        <v>-1055.346739421543</v>
+        <v>-1106.858806637871</v>
       </c>
       <c r="D61">
-        <v>943.142260578457</v>
+        <v>926.3011933621291</v>
       </c>
       <c r="E61">
-        <v>762.6889999999999</v>
+        <v>797.3599999999997</v>
       </c>
       <c r="F61">
-        <v>2045.589</v>
+        <v>2080.26</v>
       </c>
       <c r="G61">
         <v>47.1</v>
@@ -6295,37 +6295,37 @@
         <v>254.775</v>
       </c>
       <c r="M61">
-        <v>300.2924652</v>
+        <v>305.382168</v>
       </c>
       <c r="N61">
-        <v>-45.51746520000003</v>
+        <v>-50.60716799999997</v>
       </c>
       <c r="O61">
-        <v>-12.74489025600001</v>
+        <v>-14.17000703999999</v>
       </c>
       <c r="P61">
-        <v>-32.77257494400002</v>
+        <v>-36.43716095999998</v>
       </c>
       <c r="Q61">
-        <v>107.827425056</v>
+        <v>104.16283904</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.08613648160984495</v>
+        <v>0.08714489365009108</v>
       </c>
       <c r="T61">
-        <v>0.9315584667400684</v>
+        <v>0.9548474284085701</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.2375584081088692</v>
+        <v>0.2335991013070548</v>
       </c>
       <c r="W61">
-        <v>0.111926425689618</v>
+        <v>0.1125076519281244</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8484228861031042</v>
+        <v>0.8342825046680526</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.102362548616911</v>
+        <v>0.1033725486169111</v>
       </c>
       <c r="C62">
-        <v>-1106.858806637871</v>
+        <v>-1157.779985373591</v>
       </c>
       <c r="D62">
-        <v>926.3011933621291</v>
+        <v>910.0510146264085</v>
       </c>
       <c r="E62">
-        <v>797.3599999999997</v>
+        <v>832.0309999999999</v>
       </c>
       <c r="F62">
-        <v>2080.26</v>
+        <v>2114.931</v>
       </c>
       <c r="G62">
         <v>47.1</v>
@@ -6377,37 +6377,37 @@
         <v>254.775</v>
       </c>
       <c r="M62">
-        <v>305.382168</v>
+        <v>310.4718708</v>
       </c>
       <c r="N62">
-        <v>-50.60716799999997</v>
+        <v>-55.69687080000003</v>
       </c>
       <c r="O62">
-        <v>-14.17000703999999</v>
+        <v>-15.59512382400001</v>
       </c>
       <c r="P62">
-        <v>-36.43716095999998</v>
+        <v>-40.10174697600002</v>
       </c>
       <c r="Q62">
-        <v>104.16283904</v>
+        <v>100.498253024</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.08714489365009108</v>
+        <v>0.08820501912829855</v>
       </c>
       <c r="T62">
-        <v>0.9548474284085701</v>
+        <v>0.9793306958036618</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.2335991013070548</v>
+        <v>0.2297696078430046</v>
       </c>
       <c r="W62">
-        <v>0.1125076519281244</v>
+        <v>0.1130698215686469</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8342825046680526</v>
+        <v>0.820605742296445</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1033725486169111</v>
+        <v>0.1043825486169111</v>
       </c>
       <c r="C63">
-        <v>-1157.779985373591</v>
+        <v>-1208.140837496333</v>
       </c>
       <c r="D63">
-        <v>910.0510146264085</v>
+        <v>894.3611625036666</v>
       </c>
       <c r="E63">
-        <v>832.0309999999999</v>
+        <v>866.7019999999998</v>
       </c>
       <c r="F63">
-        <v>2114.931</v>
+        <v>2149.602</v>
       </c>
       <c r="G63">
         <v>47.1</v>
@@ -6459,37 +6459,37 @@
         <v>254.775</v>
       </c>
       <c r="M63">
-        <v>310.4718708</v>
+        <v>315.5615736</v>
       </c>
       <c r="N63">
-        <v>-55.69687080000003</v>
+        <v>-60.78657360000003</v>
       </c>
       <c r="O63">
-        <v>-15.59512382400001</v>
+        <v>-17.02024060800001</v>
       </c>
       <c r="P63">
-        <v>-40.10174697600002</v>
+        <v>-43.76633299200002</v>
       </c>
       <c r="Q63">
-        <v>100.498253024</v>
+        <v>96.83366700799998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.08820501912829855</v>
+        <v>0.0893209406843064</v>
       </c>
       <c r="T63">
-        <v>0.9793306958036618</v>
+        <v>1.005102556219547</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.2297696078430046</v>
+        <v>0.226063646426182</v>
       </c>
       <c r="W63">
-        <v>0.1130698215686469</v>
+        <v>0.1136138567046365</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.820605742296445</v>
+        <v>0.8073701658077928</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1043825486169111</v>
+        <v>0.1401375125863306</v>
       </c>
       <c r="C64">
-        <v>-1208.140837496333</v>
+        <v>-1581.784641254574</v>
       </c>
       <c r="D64">
-        <v>894.3611625036666</v>
+        <v>555.3883587454258</v>
       </c>
       <c r="E64">
-        <v>866.7019999999998</v>
+        <v>901.373</v>
       </c>
       <c r="F64">
-        <v>2149.602</v>
+        <v>2184.273</v>
       </c>
       <c r="G64">
         <v>47.1</v>
@@ -6541,45 +6541,45 @@
         <v>254.775</v>
       </c>
       <c r="M64">
-        <v>315.5615736</v>
+        <v>438.6020184</v>
       </c>
       <c r="N64">
-        <v>-60.78657360000003</v>
+        <v>-183.8270184</v>
       </c>
       <c r="O64">
-        <v>-17.02024060800001</v>
+        <v>-51.47156515200001</v>
       </c>
       <c r="P64">
-        <v>-43.76633299200002</v>
+        <v>-132.355453248</v>
       </c>
       <c r="Q64">
-        <v>96.83366700799998</v>
+        <v>8.244546751999991</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.0893209406843064</v>
+        <v>0.09245654440393518</v>
       </c>
       <c r="T64">
-        <v>1.005102556219547</v>
+        <v>1.077518346511205</v>
       </c>
       <c r="U64">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.226063646426182</v>
+        <v>0.1626463103390041</v>
       </c>
       <c r="W64">
-        <v>0.1136138567046365</v>
+        <v>0.168140620883928</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.8073701658077928</v>
+        <v>0.5808796797821576</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1401375125863306</v>
+        <v>0.1416875125863306</v>
       </c>
       <c r="C65">
-        <v>-1581.784641254574</v>
+        <v>-1625.433368727485</v>
       </c>
       <c r="D65">
-        <v>555.3883587454258</v>
+        <v>546.4106312725146</v>
       </c>
       <c r="E65">
-        <v>901.373</v>
+        <v>936.0439999999999</v>
       </c>
       <c r="F65">
-        <v>2184.273</v>
+        <v>2218.944</v>
       </c>
       <c r="G65">
         <v>47.1</v>
@@ -6623,37 +6623,37 @@
         <v>254.775</v>
       </c>
       <c r="M65">
-        <v>438.6020184</v>
+        <v>445.5639552</v>
       </c>
       <c r="N65">
-        <v>-183.8270184</v>
+        <v>-190.7889552</v>
       </c>
       <c r="O65">
-        <v>-51.47156515200001</v>
+        <v>-53.42090745600001</v>
       </c>
       <c r="P65">
-        <v>-132.355453248</v>
+        <v>-137.368047744</v>
       </c>
       <c r="Q65">
-        <v>8.244546751999991</v>
+        <v>3.231952256</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.09245654440393518</v>
+        <v>0.09375255952626671</v>
       </c>
       <c r="T65">
-        <v>1.077518346511205</v>
+        <v>1.107449411692072</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1626463103390041</v>
+        <v>0.1601049617399572</v>
       </c>
       <c r="W65">
-        <v>0.168140620883928</v>
+        <v>0.1686509236826166</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5808796797821576</v>
+        <v>0.5718034347855614</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1416875125863306</v>
+        <v>0.1432375125863307</v>
       </c>
       <c r="C66">
-        <v>-1625.433368727485</v>
+        <v>-1668.796467447904</v>
       </c>
       <c r="D66">
-        <v>546.4106312725146</v>
+        <v>537.7185325520959</v>
       </c>
       <c r="E66">
-        <v>936.0439999999999</v>
+        <v>970.7150000000001</v>
       </c>
       <c r="F66">
-        <v>2218.944</v>
+        <v>2253.615</v>
       </c>
       <c r="G66">
         <v>47.1</v>
@@ -6705,37 +6705,37 @@
         <v>254.775</v>
       </c>
       <c r="M66">
-        <v>445.5639552</v>
+        <v>452.5258920000001</v>
       </c>
       <c r="N66">
-        <v>-190.7889552</v>
+        <v>-197.7508920000001</v>
       </c>
       <c r="O66">
-        <v>-53.42090745600001</v>
+        <v>-55.37024976000002</v>
       </c>
       <c r="P66">
-        <v>-137.368047744</v>
+        <v>-142.38064224</v>
       </c>
       <c r="Q66">
-        <v>3.231952256</v>
+        <v>-1.780642240000049</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.09375255952626671</v>
+        <v>0.09512263265558862</v>
       </c>
       <c r="T66">
-        <v>1.107449411692072</v>
+        <v>1.139090823454703</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1601049617399572</v>
+        <v>0.1576418084824194</v>
       </c>
       <c r="W66">
-        <v>0.1686509236826166</v>
+        <v>0.1691455248567302</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5718034347855614</v>
+        <v>0.5630064588657835</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1432375125863307</v>
+        <v>0.1447875125863307</v>
       </c>
       <c r="C67">
-        <v>-1668.796467447904</v>
+        <v>-1711.887355004214</v>
       </c>
       <c r="D67">
-        <v>537.7185325520959</v>
+        <v>529.2986449957856</v>
       </c>
       <c r="E67">
-        <v>970.7150000000001</v>
+        <v>1005.386</v>
       </c>
       <c r="F67">
-        <v>2253.615</v>
+        <v>2288.286</v>
       </c>
       <c r="G67">
         <v>47.1</v>
@@ -6787,37 +6787,37 @@
         <v>254.775</v>
       </c>
       <c r="M67">
-        <v>452.5258920000001</v>
+        <v>459.4878288</v>
       </c>
       <c r="N67">
-        <v>-197.7508920000001</v>
+        <v>-204.7128288</v>
       </c>
       <c r="O67">
-        <v>-55.37024976000002</v>
+        <v>-57.31959206400002</v>
       </c>
       <c r="P67">
-        <v>-142.38064224</v>
+        <v>-147.393236736</v>
       </c>
       <c r="Q67">
-        <v>-1.780642240000049</v>
+        <v>-6.793236736000011</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.09512263265558862</v>
+        <v>0.09657329832192946</v>
       </c>
       <c r="T67">
-        <v>1.139090823454703</v>
+        <v>1.172593494732782</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1576418084824194</v>
+        <v>0.1552532962326858</v>
       </c>
       <c r="W67">
-        <v>0.1691455248567302</v>
+        <v>0.1696251381164767</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5630064588657835</v>
+        <v>0.5544760579738777</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1447875125863307</v>
+        <v>0.1463375125863307</v>
       </c>
       <c r="C68">
-        <v>-1711.887355004214</v>
+        <v>-1754.71862154193</v>
       </c>
       <c r="D68">
-        <v>529.2986449957856</v>
+        <v>521.1383784580696</v>
       </c>
       <c r="E68">
-        <v>1005.386</v>
+        <v>1040.057</v>
       </c>
       <c r="F68">
-        <v>2288.286</v>
+        <v>2322.957</v>
       </c>
       <c r="G68">
         <v>47.1</v>
@@ -6869,37 +6869,37 @@
         <v>254.775</v>
       </c>
       <c r="M68">
-        <v>459.4878288</v>
+        <v>466.4497656</v>
       </c>
       <c r="N68">
-        <v>-204.7128288</v>
+        <v>-211.6747656</v>
       </c>
       <c r="O68">
-        <v>-57.31959206400002</v>
+        <v>-59.268934368</v>
       </c>
       <c r="P68">
-        <v>-147.393236736</v>
+        <v>-152.405831232</v>
       </c>
       <c r="Q68">
-        <v>-6.793236736000011</v>
+        <v>-11.80583123199997</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.09657329832192946</v>
+        <v>0.09811188311956369</v>
       </c>
       <c r="T68">
-        <v>1.172593494732782</v>
+        <v>1.208126630936806</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1552532962326858</v>
+        <v>0.1529360828560785</v>
       </c>
       <c r="W68">
-        <v>0.1696251381164767</v>
+        <v>0.1700904345624994</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5544760579738777</v>
+        <v>0.5462002959145662</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1463375125863307</v>
+        <v>0.1478875125863306</v>
       </c>
       <c r="C69">
-        <v>-1754.71862154193</v>
+        <v>-1797.302092579237</v>
       </c>
       <c r="D69">
-        <v>521.1383784580696</v>
+        <v>513.225907420763</v>
       </c>
       <c r="E69">
-        <v>1040.057</v>
+        <v>1074.728</v>
       </c>
       <c r="F69">
-        <v>2322.957</v>
+        <v>2357.628</v>
       </c>
       <c r="G69">
         <v>47.1</v>
@@ -6951,37 +6951,37 @@
         <v>254.775</v>
       </c>
       <c r="M69">
-        <v>466.4497656</v>
+        <v>473.4117024</v>
       </c>
       <c r="N69">
-        <v>-211.6747656</v>
+        <v>-218.6367024</v>
       </c>
       <c r="O69">
-        <v>-59.268934368</v>
+        <v>-61.21827667200001</v>
       </c>
       <c r="P69">
-        <v>-152.405831232</v>
+        <v>-157.418425728</v>
       </c>
       <c r="Q69">
-        <v>-11.80583123199997</v>
+        <v>-16.81842572800002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.09811188311956369</v>
+        <v>0.09974662946705007</v>
       </c>
       <c r="T69">
-        <v>1.208126630936806</v>
+        <v>1.245880588153581</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1529360828560785</v>
+        <v>0.1506870228140774</v>
       </c>
       <c r="W69">
-        <v>0.1700904345624994</v>
+        <v>0.1705420458189333</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5462002959145662</v>
+        <v>0.5381679386217049</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1478875125863306</v>
+        <v>0.1494375125863306</v>
       </c>
       <c r="C70">
-        <v>-1797.302092579237</v>
+        <v>-1839.648886185722</v>
       </c>
       <c r="D70">
-        <v>513.225907420763</v>
+        <v>505.5501138142779</v>
       </c>
       <c r="E70">
-        <v>1074.728</v>
+        <v>1109.399</v>
       </c>
       <c r="F70">
-        <v>2357.628</v>
+        <v>2392.299</v>
       </c>
       <c r="G70">
         <v>47.1</v>
@@ -7033,37 +7033,37 @@
         <v>254.775</v>
       </c>
       <c r="M70">
-        <v>473.4117024</v>
+        <v>480.3736392</v>
       </c>
       <c r="N70">
-        <v>-218.6367024</v>
+        <v>-225.5986392</v>
       </c>
       <c r="O70">
-        <v>-61.21827667200001</v>
+        <v>-63.16761897600001</v>
       </c>
       <c r="P70">
-        <v>-157.418425728</v>
+        <v>-162.431020224</v>
       </c>
       <c r="Q70">
-        <v>-16.81842572800002</v>
+        <v>-21.83102022400001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.09974662946705007</v>
+        <v>0.1014868433208259</v>
       </c>
       <c r="T70">
-        <v>1.245880588153581</v>
+        <v>1.286070284545632</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1506870228140774</v>
+        <v>0.1485031529182212</v>
       </c>
       <c r="W70">
-        <v>0.1705420458189333</v>
+        <v>0.1709805668940212</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5381679386217049</v>
+        <v>0.5303684032793613</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1494375125863306</v>
+        <v>0.1509875125863306</v>
       </c>
       <c r="C71">
-        <v>-1839.648886185722</v>
+        <v>-1881.76946510574</v>
       </c>
       <c r="D71">
-        <v>505.5501138142779</v>
+        <v>498.1005348942609</v>
       </c>
       <c r="E71">
-        <v>1109.399</v>
+        <v>1144.07</v>
       </c>
       <c r="F71">
-        <v>2392.299</v>
+        <v>2426.97</v>
       </c>
       <c r="G71">
         <v>47.1</v>
@@ -7115,37 +7115,37 @@
         <v>254.775</v>
       </c>
       <c r="M71">
-        <v>480.3736392</v>
+        <v>487.3355760000001</v>
       </c>
       <c r="N71">
-        <v>-225.5986392</v>
+        <v>-232.5605760000001</v>
       </c>
       <c r="O71">
-        <v>-63.16761897600001</v>
+        <v>-65.11696128000003</v>
       </c>
       <c r="P71">
-        <v>-162.431020224</v>
+        <v>-167.44361472</v>
       </c>
       <c r="Q71">
-        <v>-21.83102022400001</v>
+        <v>-26.84361472000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1014868433208259</v>
+        <v>0.1033430714315201</v>
       </c>
       <c r="T71">
-        <v>1.286070284545632</v>
+        <v>1.328939294030487</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.1485031529182212</v>
+        <v>0.1463816793051037</v>
       </c>
       <c r="W71">
-        <v>0.1709805668940212</v>
+        <v>0.1714065587955352</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5303684032793613</v>
+        <v>0.5227917118039418</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1509875125863306</v>
+        <v>0.1525375125863306</v>
       </c>
       <c r="C72">
-        <v>-1881.76946510574</v>
+        <v>-1923.673684340276</v>
       </c>
       <c r="D72">
-        <v>498.1005348942609</v>
+        <v>490.8673156597239</v>
       </c>
       <c r="E72">
-        <v>1144.07</v>
+        <v>1178.741</v>
       </c>
       <c r="F72">
-        <v>2426.97</v>
+        <v>2461.641</v>
       </c>
       <c r="G72">
         <v>47.1</v>
@@ -7197,37 +7197,37 @@
         <v>254.775</v>
       </c>
       <c r="M72">
-        <v>487.3355760000001</v>
+        <v>494.2975128</v>
       </c>
       <c r="N72">
-        <v>-232.5605760000001</v>
+        <v>-239.5225128</v>
       </c>
       <c r="O72">
-        <v>-65.11696128000003</v>
+        <v>-67.06630358400002</v>
       </c>
       <c r="P72">
-        <v>-167.44361472</v>
+        <v>-172.456209216</v>
       </c>
       <c r="Q72">
-        <v>-26.84361472000003</v>
+        <v>-31.85620921600002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1033430714315201</v>
+        <v>0.1053273152739863</v>
       </c>
       <c r="T72">
-        <v>1.328939294030487</v>
+        <v>1.37476478692809</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.1463816793051037</v>
+        <v>0.1443199655120741</v>
       </c>
       <c r="W72">
-        <v>0.1714065587955352</v>
+        <v>0.1718205509251755</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5227917118039418</v>
+        <v>0.5154284482574074</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1525375125863306</v>
+        <v>0.1540875125863307</v>
       </c>
       <c r="C73">
-        <v>-1923.673684340276</v>
+        <v>-1965.37083464238</v>
       </c>
       <c r="D73">
-        <v>490.8673156597239</v>
+        <v>483.8411653576194</v>
       </c>
       <c r="E73">
-        <v>1178.741</v>
+        <v>1213.412</v>
       </c>
       <c r="F73">
-        <v>2461.641</v>
+        <v>2496.312</v>
       </c>
       <c r="G73">
         <v>47.1</v>
@@ -7279,37 +7279,37 @@
         <v>254.775</v>
       </c>
       <c r="M73">
-        <v>494.2975127999999</v>
+        <v>501.2594496</v>
       </c>
       <c r="N73">
-        <v>-239.5225127999999</v>
+        <v>-246.4844496</v>
       </c>
       <c r="O73">
-        <v>-67.06630358399998</v>
+        <v>-69.01564588799999</v>
       </c>
       <c r="P73">
-        <v>-172.4562092159999</v>
+        <v>-177.468803712</v>
       </c>
       <c r="Q73">
-        <v>-31.85620921599994</v>
+        <v>-36.86880371199999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1053273152739863</v>
+        <v>0.1074532908194858</v>
       </c>
       <c r="T73">
-        <v>1.374764786928089</v>
+        <v>1.423863529318378</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1443199655120741</v>
+        <v>0.1423155215466286</v>
       </c>
       <c r="W73">
-        <v>0.1718205509251755</v>
+        <v>0.172223043273437</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5154284482574075</v>
+        <v>0.508269719809388</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1540875125863307</v>
+        <v>0.1556375125863306</v>
       </c>
       <c r="C74">
-        <v>-1965.37083464238</v>
+        <v>-2006.869682329798</v>
       </c>
       <c r="D74">
-        <v>483.8411653576194</v>
+        <v>477.0133176702016</v>
       </c>
       <c r="E74">
-        <v>1213.412</v>
+        <v>1248.083</v>
       </c>
       <c r="F74">
-        <v>2496.312</v>
+        <v>2530.983</v>
       </c>
       <c r="G74">
         <v>47.1</v>
@@ -7361,37 +7361,37 @@
         <v>254.775</v>
       </c>
       <c r="M74">
-        <v>501.2594496</v>
+        <v>508.2213864</v>
       </c>
       <c r="N74">
-        <v>-246.4844496</v>
+        <v>-253.4463864</v>
       </c>
       <c r="O74">
-        <v>-69.01564588799999</v>
+        <v>-70.96498819199999</v>
       </c>
       <c r="P74">
-        <v>-177.468803712</v>
+        <v>-182.481398208</v>
       </c>
       <c r="Q74">
-        <v>-36.86880371199999</v>
+        <v>-41.88139820799998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1074532908194858</v>
+        <v>0.1097367460350223</v>
       </c>
       <c r="T74">
-        <v>1.423863529318378</v>
+        <v>1.476599215589429</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1423155215466286</v>
+        <v>0.1403659938542091</v>
       </c>
       <c r="W74">
-        <v>0.172223043273437</v>
+        <v>0.1726145084340748</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.508269719809388</v>
+        <v>0.5013071209078894</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1556375125863306</v>
+        <v>0.1833800443045851</v>
       </c>
       <c r="C75">
-        <v>-2006.869682329798</v>
+        <v>-2137.728738979918</v>
       </c>
       <c r="D75">
-        <v>477.0133176702016</v>
+        <v>380.8252610200823</v>
       </c>
       <c r="E75">
-        <v>1248.083</v>
+        <v>1282.754</v>
       </c>
       <c r="F75">
-        <v>2530.983</v>
+        <v>2565.654</v>
       </c>
       <c r="G75">
         <v>47.1</v>
@@ -7443,45 +7443,45 @@
         <v>254.775</v>
       </c>
       <c r="M75">
-        <v>508.2213864</v>
+        <v>604.9812132000001</v>
       </c>
       <c r="N75">
-        <v>-253.4463864</v>
+        <v>-350.2062132000001</v>
       </c>
       <c r="O75">
-        <v>-70.96498819199999</v>
+        <v>-98.05773969600004</v>
       </c>
       <c r="P75">
-        <v>-182.481398208</v>
+        <v>-252.148473504</v>
       </c>
       <c r="Q75">
-        <v>-41.88139820799998</v>
+        <v>-111.548473504</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1097367460350223</v>
+        <v>0.1133209736450403</v>
       </c>
       <c r="T75">
-        <v>1.476599215589429</v>
+        <v>1.559375834758437</v>
       </c>
       <c r="U75">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1403659938542091</v>
+        <v>0.1179160582899238</v>
       </c>
       <c r="W75">
-        <v>0.1726145084340748</v>
+        <v>0.207995393455236</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.5013071209078894</v>
+        <v>0.4211287796068706</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1833800443045851</v>
+        <v>0.1852800443045851</v>
       </c>
       <c r="C76">
-        <v>-2137.728738979918</v>
+        <v>-2177.587348430041</v>
       </c>
       <c r="D76">
-        <v>380.8252610200823</v>
+        <v>375.6376515699585</v>
       </c>
       <c r="E76">
-        <v>1282.754</v>
+        <v>1317.425</v>
       </c>
       <c r="F76">
-        <v>2565.654</v>
+        <v>2600.325</v>
       </c>
       <c r="G76">
         <v>47.1</v>
@@ -7525,37 +7525,37 @@
         <v>254.775</v>
       </c>
       <c r="M76">
-        <v>604.9812132000001</v>
+        <v>613.1566349999999</v>
       </c>
       <c r="N76">
-        <v>-350.2062132000001</v>
+        <v>-358.381635</v>
       </c>
       <c r="O76">
-        <v>-98.05773969600004</v>
+        <v>-100.3468578</v>
       </c>
       <c r="P76">
-        <v>-252.148473504</v>
+        <v>-258.0347772</v>
       </c>
       <c r="Q76">
-        <v>-111.548473504</v>
+        <v>-117.4347772</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1133209736450403</v>
+        <v>0.1160218125908419</v>
       </c>
       <c r="T76">
-        <v>1.559375834758437</v>
+        <v>1.621750868148775</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1179160582899238</v>
+        <v>0.1163438441793915</v>
       </c>
       <c r="W76">
-        <v>0.207995393455236</v>
+        <v>0.2083661215424995</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4211287796068706</v>
+        <v>0.4155137292121124</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1852800443045851</v>
+        <v>0.1871800443045851</v>
       </c>
       <c r="C77">
-        <v>-2177.587348430041</v>
+        <v>-2217.306525784162</v>
       </c>
       <c r="D77">
-        <v>375.6376515699585</v>
+        <v>370.5894742158381</v>
       </c>
       <c r="E77">
-        <v>1317.425</v>
+        <v>1352.096</v>
       </c>
       <c r="F77">
-        <v>2600.325</v>
+        <v>2634.996</v>
       </c>
       <c r="G77">
         <v>47.1</v>
@@ -7607,37 +7607,37 @@
         <v>254.775</v>
       </c>
       <c r="M77">
-        <v>613.1566349999999</v>
+        <v>621.3320568</v>
       </c>
       <c r="N77">
-        <v>-358.381635</v>
+        <v>-366.5570568000001</v>
       </c>
       <c r="O77">
-        <v>-100.3468578</v>
+        <v>-102.635975904</v>
       </c>
       <c r="P77">
-        <v>-258.0347772</v>
+        <v>-263.921080896</v>
       </c>
       <c r="Q77">
-        <v>-117.4347772</v>
+        <v>-123.321080896</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1160218125908419</v>
+        <v>0.1189477214487937</v>
       </c>
       <c r="T77">
-        <v>1.621750868148775</v>
+        <v>1.689323820988307</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.1163438441793915</v>
+        <v>0.1148130041243995</v>
       </c>
       <c r="W77">
-        <v>0.2083661215424995</v>
+        <v>0.2087270936274666</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4155137292121124</v>
+        <v>0.4100464433014266</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1871800443045851</v>
+        <v>0.1890800443045851</v>
       </c>
       <c r="C78">
-        <v>-2217.306525784162</v>
+        <v>-2256.891817962306</v>
       </c>
       <c r="D78">
-        <v>370.5894742158381</v>
+        <v>365.6751820376944</v>
       </c>
       <c r="E78">
-        <v>1352.096</v>
+        <v>1386.767</v>
       </c>
       <c r="F78">
-        <v>2634.996</v>
+        <v>2669.667</v>
       </c>
       <c r="G78">
         <v>47.1</v>
@@ -7689,37 +7689,37 @@
         <v>254.775</v>
       </c>
       <c r="M78">
-        <v>621.3320568</v>
+        <v>629.5074786</v>
       </c>
       <c r="N78">
-        <v>-366.5570568000001</v>
+        <v>-374.7324786</v>
       </c>
       <c r="O78">
-        <v>-102.635975904</v>
+        <v>-104.925094008</v>
       </c>
       <c r="P78">
-        <v>-263.921080896</v>
+        <v>-269.807384592</v>
       </c>
       <c r="Q78">
-        <v>-123.321080896</v>
+        <v>-129.207384592</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1189477214487937</v>
+        <v>0.1221280571639586</v>
       </c>
       <c r="T78">
-        <v>1.689323820988307</v>
+        <v>1.762772682770408</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1148130041243995</v>
+        <v>0.1133219261487579</v>
       </c>
       <c r="W78">
-        <v>0.2087270936274666</v>
+        <v>0.2090786898141229</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4100464433014266</v>
+        <v>0.4047211648169925</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1890800443045851</v>
+        <v>0.1909800443045851</v>
       </c>
       <c r="C79">
-        <v>-2256.891817962306</v>
+        <v>-2296.348481509935</v>
       </c>
       <c r="D79">
-        <v>365.6751820376944</v>
+        <v>360.8895184900655</v>
       </c>
       <c r="E79">
-        <v>1386.767</v>
+        <v>1421.438</v>
       </c>
       <c r="F79">
-        <v>2669.667</v>
+        <v>2704.338</v>
       </c>
       <c r="G79">
         <v>47.1</v>
@@ -7771,37 +7771,37 @@
         <v>254.775</v>
       </c>
       <c r="M79">
-        <v>629.5074786</v>
+        <v>637.6829004000001</v>
       </c>
       <c r="N79">
-        <v>-374.7324786</v>
+        <v>-382.9079004000001</v>
       </c>
       <c r="O79">
-        <v>-104.925094008</v>
+        <v>-107.214212112</v>
       </c>
       <c r="P79">
-        <v>-269.807384592</v>
+        <v>-275.6936882880001</v>
       </c>
       <c r="Q79">
-        <v>-129.207384592</v>
+        <v>-135.0936882880001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1221280571639586</v>
+        <v>0.1255975143077749</v>
       </c>
       <c r="T79">
-        <v>1.762772682770408</v>
+        <v>1.842898713805426</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1133219261487579</v>
+        <v>0.1118690809417225</v>
       </c>
       <c r="W79">
-        <v>0.2090786898141229</v>
+        <v>0.2094212707139418</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4047211648169925</v>
+        <v>0.3995324319347233</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1909800443045851</v>
+        <v>0.1928800443045851</v>
       </c>
       <c r="C80">
-        <v>-2296.348481509935</v>
+        <v>-2335.681501353436</v>
       </c>
       <c r="D80">
-        <v>360.8895184900655</v>
+        <v>356.2274986465637</v>
       </c>
       <c r="E80">
-        <v>1421.438</v>
+        <v>1456.109</v>
       </c>
       <c r="F80">
-        <v>2704.338</v>
+        <v>2739.009</v>
       </c>
       <c r="G80">
         <v>47.1</v>
@@ -7853,37 +7853,37 @@
         <v>254.775</v>
       </c>
       <c r="M80">
-        <v>637.6829004000001</v>
+        <v>645.8583222</v>
       </c>
       <c r="N80">
-        <v>-382.9079004000001</v>
+        <v>-391.0833222</v>
       </c>
       <c r="O80">
-        <v>-107.214212112</v>
+        <v>-109.503330216</v>
       </c>
       <c r="P80">
-        <v>-275.6936882880001</v>
+        <v>-281.579991984</v>
       </c>
       <c r="Q80">
-        <v>-135.0936882880001</v>
+        <v>-140.979991984</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1255975143077749</v>
+        <v>0.1293973959414785</v>
       </c>
       <c r="T80">
-        <v>1.842898713805426</v>
+        <v>1.930655795415209</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1118690809417225</v>
+        <v>0.1104530166260046</v>
       </c>
       <c r="W80">
-        <v>0.2094212707139418</v>
+        <v>0.2097551786795881</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3995324319347233</v>
+        <v>0.3944750593785876</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1928800443045851</v>
+        <v>0.1947800443045851</v>
       </c>
       <c r="C81">
-        <v>-2335.681501353436</v>
+        <v>-2374.895608120439</v>
       </c>
       <c r="D81">
-        <v>356.2274986465637</v>
+        <v>351.6843918795613</v>
       </c>
       <c r="E81">
-        <v>1456.109</v>
+        <v>1490.78</v>
       </c>
       <c r="F81">
-        <v>2739.009</v>
+        <v>2773.68</v>
       </c>
       <c r="G81">
         <v>47.1</v>
@@ -7935,37 +7935,37 @@
         <v>254.775</v>
       </c>
       <c r="M81">
-        <v>645.8583222</v>
+        <v>654.0337440000001</v>
       </c>
       <c r="N81">
-        <v>-391.0833222</v>
+        <v>-399.2587440000001</v>
       </c>
       <c r="O81">
-        <v>-109.503330216</v>
+        <v>-111.79244832</v>
       </c>
       <c r="P81">
-        <v>-281.579991984</v>
+        <v>-287.46629568</v>
       </c>
       <c r="Q81">
-        <v>-140.979991984</v>
+        <v>-146.86629568</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1293973959414785</v>
+        <v>0.1335772657385524</v>
       </c>
       <c r="T81">
-        <v>1.930655795415209</v>
+        <v>2.027188585185969</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1104530166260046</v>
+        <v>0.1090723539181795</v>
       </c>
       <c r="W81">
-        <v>0.2097551786795881</v>
+        <v>0.2100807389460933</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3944750593785876</v>
+        <v>0.3895441211363553</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1947800443045851</v>
+        <v>0.1966800443045851</v>
       </c>
       <c r="C82">
-        <v>-2374.895608120439</v>
+        <v>-2413.995294151457</v>
       </c>
       <c r="D82">
-        <v>351.6843918795613</v>
+        <v>347.2557058485428</v>
       </c>
       <c r="E82">
-        <v>1490.78</v>
+        <v>1525.451</v>
       </c>
       <c r="F82">
-        <v>2773.68</v>
+        <v>2808.351</v>
       </c>
       <c r="G82">
         <v>47.1</v>
@@ -8017,37 +8017,37 @@
         <v>254.775</v>
       </c>
       <c r="M82">
-        <v>654.0337440000001</v>
+        <v>662.2091658000001</v>
       </c>
       <c r="N82">
-        <v>-399.2587440000001</v>
+        <v>-407.4341658000001</v>
       </c>
       <c r="O82">
-        <v>-111.79244832</v>
+        <v>-114.081566424</v>
       </c>
       <c r="P82">
-        <v>-287.46629568</v>
+        <v>-293.3525993760001</v>
       </c>
       <c r="Q82">
-        <v>-146.86629568</v>
+        <v>-152.7525993760001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1335772657385524</v>
+        <v>0.1381971218300552</v>
       </c>
       <c r="T82">
-        <v>2.027188585185969</v>
+        <v>2.133882721248388</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1090723539181795</v>
+        <v>0.1077257816475847</v>
       </c>
       <c r="W82">
-        <v>0.2100807389460933</v>
+        <v>0.2103982606874995</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3895441211363553</v>
+        <v>0.3847349344556595</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1966800443045851</v>
+        <v>0.1985800443045851</v>
       </c>
       <c r="C83">
-        <v>-2413.995294151457</v>
+        <v>-2452.984828316802</v>
       </c>
       <c r="D83">
-        <v>347.2557058485428</v>
+        <v>342.9371716831979</v>
       </c>
       <c r="E83">
-        <v>1525.451</v>
+        <v>1560.122</v>
       </c>
       <c r="F83">
-        <v>2808.351</v>
+        <v>2843.022</v>
       </c>
       <c r="G83">
         <v>47.1</v>
@@ -8099,37 +8099,37 @@
         <v>254.775</v>
       </c>
       <c r="M83">
-        <v>662.2091658000001</v>
+        <v>670.3845876</v>
       </c>
       <c r="N83">
-        <v>-407.4341658000001</v>
+        <v>-415.6095876000001</v>
       </c>
       <c r="O83">
-        <v>-114.081566424</v>
+        <v>-116.370684528</v>
       </c>
       <c r="P83">
-        <v>-293.3525993760001</v>
+        <v>-299.238903072</v>
       </c>
       <c r="Q83">
-        <v>-152.7525993760001</v>
+        <v>-158.638903072</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1381971218300552</v>
+        <v>0.1433302952650583</v>
       </c>
       <c r="T83">
-        <v>2.133882721248388</v>
+        <v>2.252431761317744</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1077257816475847</v>
+        <v>0.1064120526031019</v>
       </c>
       <c r="W83">
-        <v>0.2103982606874995</v>
+        <v>0.2107080379961886</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3847349344556595</v>
+        <v>0.3800430450110783</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1985800443045851</v>
+        <v>0.2004800443045852</v>
       </c>
       <c r="C84">
-        <v>-2452.984828316802</v>
+        <v>-2491.86826974147</v>
       </c>
       <c r="D84">
-        <v>342.9371716831979</v>
+        <v>338.7247302585301</v>
       </c>
       <c r="E84">
-        <v>1560.122</v>
+        <v>1594.793</v>
       </c>
       <c r="F84">
-        <v>2843.022</v>
+        <v>2877.693</v>
       </c>
       <c r="G84">
         <v>47.1</v>
@@ -8181,37 +8181,37 @@
         <v>254.775</v>
       </c>
       <c r="M84">
-        <v>670.3845876</v>
+        <v>678.5600094000001</v>
       </c>
       <c r="N84">
-        <v>-415.6095876000001</v>
+        <v>-423.7850094000001</v>
       </c>
       <c r="O84">
-        <v>-116.370684528</v>
+        <v>-118.6598026320001</v>
       </c>
       <c r="P84">
-        <v>-299.238903072</v>
+        <v>-305.1252067680001</v>
       </c>
       <c r="Q84">
-        <v>-158.638903072</v>
+        <v>-164.5252067680001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1433302952650583</v>
+        <v>0.1490673714571205</v>
       </c>
       <c r="T84">
-        <v>2.252431761317744</v>
+        <v>2.384927747277611</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.1064120526031019</v>
+        <v>0.105129979680173</v>
       </c>
       <c r="W84">
-        <v>0.2107080379961886</v>
+        <v>0.2110103507914152</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3800430450110783</v>
+        <v>0.3754642131434749</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2004800443045852</v>
+        <v>0.2023800443045851</v>
       </c>
       <c r="C85">
-        <v>-2491.86826974147</v>
+        <v>-2530.649480530779</v>
       </c>
       <c r="D85">
-        <v>338.7247302585301</v>
+        <v>334.6145194692211</v>
       </c>
       <c r="E85">
-        <v>1594.793</v>
+        <v>1629.464</v>
       </c>
       <c r="F85">
-        <v>2877.693</v>
+        <v>2912.364</v>
       </c>
       <c r="G85">
         <v>47.1</v>
@@ -8263,37 +8263,37 @@
         <v>254.775</v>
       </c>
       <c r="M85">
-        <v>678.5600094000001</v>
+        <v>686.7354312</v>
       </c>
       <c r="N85">
-        <v>-423.7850094000001</v>
+        <v>-431.9604312</v>
       </c>
       <c r="O85">
-        <v>-118.6598026320001</v>
+        <v>-120.948920736</v>
       </c>
       <c r="P85">
-        <v>-305.1252067680001</v>
+        <v>-311.011510464</v>
       </c>
       <c r="Q85">
-        <v>-164.5252067680001</v>
+        <v>-170.411510464</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1490673714571205</v>
+        <v>0.1555215821731906</v>
       </c>
       <c r="T85">
-        <v>2.384927747277611</v>
+        <v>2.533985731482463</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.105129979680173</v>
+        <v>0.1038784323030281</v>
       </c>
       <c r="W85">
-        <v>0.2110103507914152</v>
+        <v>0.211305465662946</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3754642131434749</v>
+        <v>0.3709944010822431</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2023800443045851</v>
+        <v>0.2042800443045851</v>
       </c>
       <c r="C86">
-        <v>-2530.649480530779</v>
+        <v>-2569.332137580607</v>
       </c>
       <c r="D86">
-        <v>334.6145194692211</v>
+        <v>330.6028624193932</v>
       </c>
       <c r="E86">
-        <v>1629.464</v>
+        <v>1664.135</v>
       </c>
       <c r="F86">
-        <v>2912.364</v>
+        <v>2947.035</v>
       </c>
       <c r="G86">
         <v>47.1</v>
@@ -8345,37 +8345,37 @@
         <v>254.775</v>
       </c>
       <c r="M86">
-        <v>686.7354312</v>
+        <v>694.910853</v>
       </c>
       <c r="N86">
-        <v>-431.9604312</v>
+        <v>-440.135853</v>
       </c>
       <c r="O86">
-        <v>-120.948920736</v>
+        <v>-123.23803884</v>
       </c>
       <c r="P86">
-        <v>-311.011510464</v>
+        <v>-316.89781416</v>
       </c>
       <c r="Q86">
-        <v>-170.411510464</v>
+        <v>-176.29781416</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1555215821731905</v>
+        <v>0.1628363543180699</v>
       </c>
       <c r="T86">
-        <v>2.53398573148246</v>
+        <v>2.702918113581291</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1038784323030281</v>
+        <v>0.1026563330994631</v>
       </c>
       <c r="W86">
-        <v>0.211305465662946</v>
+        <v>0.2115936366551466</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3709944010822431</v>
+        <v>0.3666297610695108</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2042800443045851</v>
+        <v>0.2061800443045851</v>
       </c>
       <c r="C87">
-        <v>-2569.332137580607</v>
+        <v>-2607.919743548141</v>
       </c>
       <c r="D87">
-        <v>330.6028624193932</v>
+        <v>326.6862564518585</v>
       </c>
       <c r="E87">
-        <v>1664.135</v>
+        <v>1698.806</v>
       </c>
       <c r="F87">
-        <v>2947.035</v>
+        <v>2981.706</v>
       </c>
       <c r="G87">
         <v>47.1</v>
@@ -8427,37 +8427,37 @@
         <v>254.775</v>
       </c>
       <c r="M87">
-        <v>694.910853</v>
+        <v>703.0862748</v>
       </c>
       <c r="N87">
-        <v>-440.135853</v>
+        <v>-448.3112748</v>
       </c>
       <c r="O87">
-        <v>-123.23803884</v>
+        <v>-125.527156944</v>
       </c>
       <c r="P87">
-        <v>-316.89781416</v>
+        <v>-322.784117856</v>
       </c>
       <c r="Q87">
-        <v>-176.29781416</v>
+        <v>-182.184117856</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1628363543180699</v>
+        <v>0.1711960939122177</v>
       </c>
       <c r="T87">
-        <v>2.702918113581291</v>
+        <v>2.895983693122812</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1026563330994631</v>
+        <v>0.1014626548076088</v>
       </c>
       <c r="W87">
-        <v>0.2115936366551466</v>
+        <v>0.2118751059963658</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3666297610695108</v>
+        <v>0.3623666243128887</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2061800443045851</v>
+        <v>0.2080800443045851</v>
       </c>
       <c r="C88">
-        <v>-2607.919743548141</v>
+        <v>-2646.415637051951</v>
       </c>
       <c r="D88">
-        <v>326.6862564518585</v>
+        <v>322.8613629480488</v>
       </c>
       <c r="E88">
-        <v>1698.806</v>
+        <v>1733.477</v>
       </c>
       <c r="F88">
-        <v>2981.706</v>
+        <v>3016.377</v>
       </c>
       <c r="G88">
         <v>47.1</v>
@@ -8509,37 +8509,37 @@
         <v>254.775</v>
       </c>
       <c r="M88">
-        <v>703.0862748</v>
+        <v>711.2616966000001</v>
       </c>
       <c r="N88">
-        <v>-448.3112748</v>
+        <v>-456.4866966000001</v>
       </c>
       <c r="O88">
-        <v>-125.527156944</v>
+        <v>-127.816275048</v>
       </c>
       <c r="P88">
-        <v>-322.784117856</v>
+        <v>-328.6704215520001</v>
       </c>
       <c r="Q88">
-        <v>-182.184117856</v>
+        <v>-188.0704215520001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1711960939122177</v>
+        <v>0.1808419472900807</v>
       </c>
       <c r="T88">
-        <v>2.895983693122812</v>
+        <v>3.118751669516875</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1014626548076088</v>
+        <v>0.1002964173960271</v>
       </c>
       <c r="W88">
-        <v>0.2118751059963658</v>
+        <v>0.2121501047780168</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3623666243128887</v>
+        <v>0.3582014907000968</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2080800443045851</v>
+        <v>0.2099800443045851</v>
       </c>
       <c r="C89">
-        <v>-2646.415637051951</v>
+        <v>-2684.823002163799</v>
       </c>
       <c r="D89">
-        <v>322.8613629480488</v>
+        <v>319.1249978362011</v>
       </c>
       <c r="E89">
-        <v>1733.477</v>
+        <v>1768.148</v>
       </c>
       <c r="F89">
-        <v>3016.377</v>
+        <v>3051.048</v>
       </c>
       <c r="G89">
         <v>47.1</v>
@@ -8591,37 +8591,37 @@
         <v>254.775</v>
       </c>
       <c r="M89">
-        <v>711.2616966000001</v>
+        <v>719.4371184</v>
       </c>
       <c r="N89">
-        <v>-456.4866966000001</v>
+        <v>-464.6621184000001</v>
       </c>
       <c r="O89">
-        <v>-127.816275048</v>
+        <v>-130.105393152</v>
       </c>
       <c r="P89">
-        <v>-328.6704215520001</v>
+        <v>-334.556725248</v>
       </c>
       <c r="Q89">
-        <v>-188.0704215520001</v>
+        <v>-193.956725248</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.1808419472900807</v>
+        <v>0.1920954428975874</v>
       </c>
       <c r="T89">
-        <v>3.118751669516875</v>
+        <v>3.378647641976615</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1002964173960271</v>
+        <v>0.09915668538016317</v>
       </c>
       <c r="W89">
-        <v>0.2121501047780168</v>
+        <v>0.2124188535873575</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3582014907000968</v>
+        <v>0.3541310192148684</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2099800443045851</v>
+        <v>0.2118800443045851</v>
       </c>
       <c r="C90">
-        <v>-2684.823002163799</v>
+        <v>-2723.144877248928</v>
       </c>
       <c r="D90">
-        <v>319.1249978362011</v>
+        <v>315.4741227510716</v>
       </c>
       <c r="E90">
-        <v>1768.148</v>
+        <v>1802.819</v>
       </c>
       <c r="F90">
-        <v>3051.048</v>
+        <v>3085.719</v>
       </c>
       <c r="G90">
         <v>47.1</v>
@@ -8673,37 +8673,37 @@
         <v>254.775</v>
       </c>
       <c r="M90">
-        <v>719.4371184</v>
+        <v>727.6125402</v>
       </c>
       <c r="N90">
-        <v>-464.6621184000001</v>
+        <v>-472.8375402</v>
       </c>
       <c r="O90">
-        <v>-130.105393152</v>
+        <v>-132.394511256</v>
       </c>
       <c r="P90">
-        <v>-334.556725248</v>
+        <v>-340.443028944</v>
       </c>
       <c r="Q90">
-        <v>-193.956725248</v>
+        <v>-199.8430289440001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.1920954428975874</v>
+        <v>0.2053950286155499</v>
       </c>
       <c r="T90">
-        <v>3.378647641976615</v>
+        <v>3.685797427610852</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.09915668538016317</v>
+        <v>0.09804256531971191</v>
       </c>
       <c r="W90">
-        <v>0.2124188535873575</v>
+        <v>0.2126815630976119</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3541310192148684</v>
+        <v>0.3501520189989711</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2118800443045851</v>
+        <v>0.2137800443045851</v>
       </c>
       <c r="C91">
-        <v>-2723.144877248928</v>
+        <v>-2761.384163206397</v>
       </c>
       <c r="D91">
-        <v>315.4741227510716</v>
+        <v>311.9058367936028</v>
       </c>
       <c r="E91">
-        <v>1802.819</v>
+        <v>1837.49</v>
       </c>
       <c r="F91">
-        <v>3085.719</v>
+        <v>3120.39</v>
       </c>
       <c r="G91">
         <v>47.1</v>
@@ -8755,37 +8755,37 @@
         <v>254.775</v>
       </c>
       <c r="M91">
-        <v>727.6125402</v>
+        <v>735.787962</v>
       </c>
       <c r="N91">
-        <v>-472.8375402</v>
+        <v>-481.012962</v>
       </c>
       <c r="O91">
-        <v>-132.394511256</v>
+        <v>-134.68362936</v>
       </c>
       <c r="P91">
-        <v>-340.443028944</v>
+        <v>-346.32933264</v>
       </c>
       <c r="Q91">
-        <v>-199.8430289440001</v>
+        <v>-205.72933264</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2053950286155499</v>
+        <v>0.2213545314771049</v>
       </c>
       <c r="T91">
-        <v>3.685797427610852</v>
+        <v>4.054377170371938</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.09804256531971191</v>
+        <v>0.09695320348282621</v>
       </c>
       <c r="W91">
-        <v>0.2126815630976119</v>
+        <v>0.2129384346187496</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3501520189989711</v>
+        <v>0.3462614410100936</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2137800443045851</v>
+        <v>0.2156800443045852</v>
       </c>
       <c r="C92">
-        <v>-2761.384163206397</v>
+        <v>-2799.543631156437</v>
       </c>
       <c r="D92">
-        <v>311.9058367936028</v>
+        <v>308.4173688435634</v>
       </c>
       <c r="E92">
-        <v>1837.49</v>
+        <v>1872.161</v>
       </c>
       <c r="F92">
-        <v>3120.39</v>
+        <v>3155.061</v>
       </c>
       <c r="G92">
         <v>47.1</v>
@@ -8837,37 +8837,37 @@
         <v>254.775</v>
       </c>
       <c r="M92">
-        <v>735.787962</v>
+        <v>743.9633838000001</v>
       </c>
       <c r="N92">
-        <v>-481.012962</v>
+        <v>-489.1883838000001</v>
       </c>
       <c r="O92">
-        <v>-134.68362936</v>
+        <v>-136.972747464</v>
       </c>
       <c r="P92">
-        <v>-346.32933264</v>
+        <v>-352.2156363360001</v>
       </c>
       <c r="Q92">
-        <v>-205.72933264</v>
+        <v>-211.6156363360001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2213545314771049</v>
+        <v>0.2408605905301166</v>
       </c>
       <c r="T92">
-        <v>4.054377170371938</v>
+        <v>4.504863522635487</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.09695320348282621</v>
+        <v>0.09588778366433362</v>
       </c>
       <c r="W92">
-        <v>0.2129384346187496</v>
+        <v>0.2131896606119502</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3462614410100936</v>
+        <v>0.3424563702297628</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2156800443045852</v>
+        <v>0.2175800443045851</v>
       </c>
       <c r="C93">
-        <v>-2799.543631156437</v>
+        <v>-2837.625929617646</v>
       </c>
       <c r="D93">
-        <v>308.4173688435634</v>
+        <v>305.0060703823536</v>
       </c>
       <c r="E93">
-        <v>1872.161</v>
+        <v>1906.832</v>
       </c>
       <c r="F93">
-        <v>3155.061</v>
+        <v>3189.732</v>
       </c>
       <c r="G93">
         <v>47.1</v>
@@ -8919,37 +8919,37 @@
         <v>254.775</v>
       </c>
       <c r="M93">
-        <v>743.9633838000001</v>
+        <v>752.1388056000001</v>
       </c>
       <c r="N93">
-        <v>-489.1883838000001</v>
+        <v>-497.3638056000001</v>
       </c>
       <c r="O93">
-        <v>-136.972747464</v>
+        <v>-139.261865568</v>
       </c>
       <c r="P93">
-        <v>-352.2156363360001</v>
+        <v>-358.101940032</v>
       </c>
       <c r="Q93">
-        <v>-211.6156363360001</v>
+        <v>-217.501940032</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2408605905301166</v>
+        <v>0.2652431643463812</v>
       </c>
       <c r="T93">
-        <v>4.504863522635487</v>
+        <v>5.067971462964925</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09588778366433362</v>
+        <v>0.09484552514624305</v>
       </c>
       <c r="W93">
-        <v>0.2131896606119502</v>
+        <v>0.2134354251705159</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3424563702297628</v>
+        <v>0.3387340183794394</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2175800443045851</v>
+        <v>0.2194800443045851</v>
       </c>
       <c r="C94">
-        <v>-2837.625929617646</v>
+        <v>-2875.633591213093</v>
       </c>
       <c r="D94">
-        <v>305.0060703823536</v>
+        <v>301.6694087869077</v>
       </c>
       <c r="E94">
-        <v>1906.832</v>
+        <v>1941.503</v>
       </c>
       <c r="F94">
-        <v>3189.732</v>
+        <v>3224.403</v>
       </c>
       <c r="G94">
         <v>47.1</v>
@@ -9001,37 +9001,37 @@
         <v>254.775</v>
       </c>
       <c r="M94">
-        <v>752.1388056000001</v>
+        <v>760.3142274</v>
       </c>
       <c r="N94">
-        <v>-497.3638056000001</v>
+        <v>-505.5392274000001</v>
       </c>
       <c r="O94">
-        <v>-139.261865568</v>
+        <v>-141.550983672</v>
       </c>
       <c r="P94">
-        <v>-358.101940032</v>
+        <v>-363.988243728</v>
       </c>
       <c r="Q94">
-        <v>-217.501940032</v>
+        <v>-223.388243728</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2652431643463812</v>
+        <v>0.2965921878244357</v>
       </c>
       <c r="T94">
-        <v>5.067971462964925</v>
+        <v>5.791967386245629</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09484552514624305</v>
+        <v>0.09382568078983182</v>
       </c>
       <c r="W94">
-        <v>0.2134354251705159</v>
+        <v>0.2136759044697577</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3387340183794394</v>
+        <v>0.3350917171065422</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2194800443045851</v>
+        <v>0.2213800443045851</v>
       </c>
       <c r="C95">
-        <v>-2875.633591213093</v>
+        <v>-2913.569038940995</v>
       </c>
       <c r="D95">
-        <v>301.6694087869077</v>
+        <v>298.4049610590052</v>
       </c>
       <c r="E95">
-        <v>1941.503</v>
+        <v>1976.174</v>
       </c>
       <c r="F95">
-        <v>3224.403</v>
+        <v>3259.074</v>
       </c>
       <c r="G95">
         <v>47.1</v>
@@ -9083,37 +9083,37 @@
         <v>254.775</v>
       </c>
       <c r="M95">
-        <v>760.3142274</v>
+        <v>768.4896492</v>
       </c>
       <c r="N95">
-        <v>-505.5392274000001</v>
+        <v>-513.7146492000001</v>
       </c>
       <c r="O95">
-        <v>-141.550983672</v>
+        <v>-143.840101776</v>
       </c>
       <c r="P95">
-        <v>-363.988243728</v>
+        <v>-369.874547424</v>
       </c>
       <c r="Q95">
-        <v>-223.388243728</v>
+        <v>-229.274547424</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.2965921878244357</v>
+        <v>0.338390885795175</v>
       </c>
       <c r="T95">
-        <v>5.791967386245629</v>
+        <v>6.757295283953235</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09382568078983182</v>
+        <v>0.09282753524951447</v>
       </c>
       <c r="W95">
-        <v>0.2136759044697577</v>
+        <v>0.2139112671881645</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3350917171065422</v>
+        <v>0.3315269116054087</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2213800443045851</v>
+        <v>0.2232800443045851</v>
       </c>
       <c r="C96">
-        <v>-2913.569038940995</v>
+        <v>-2951.434592042634</v>
       </c>
       <c r="D96">
-        <v>298.4049610590052</v>
+        <v>295.2104079573666</v>
       </c>
       <c r="E96">
-        <v>1976.174</v>
+        <v>2010.845</v>
       </c>
       <c r="F96">
-        <v>3259.074</v>
+        <v>3293.745</v>
       </c>
       <c r="G96">
         <v>47.1</v>
@@ -9165,37 +9165,37 @@
         <v>254.775</v>
       </c>
       <c r="M96">
-        <v>768.4896492</v>
+        <v>776.6650710000001</v>
       </c>
       <c r="N96">
-        <v>-513.7146492000001</v>
+        <v>-521.8900710000001</v>
       </c>
       <c r="O96">
-        <v>-143.840101776</v>
+        <v>-146.1292198800001</v>
       </c>
       <c r="P96">
-        <v>-369.874547424</v>
+        <v>-375.7608511200001</v>
       </c>
       <c r="Q96">
-        <v>-229.274547424</v>
+        <v>-235.1608511200001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.338390885795175</v>
+        <v>0.3969090629542102</v>
       </c>
       <c r="T96">
-        <v>6.757295283953235</v>
+        <v>8.108754340743886</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09282753524951447</v>
+        <v>0.09185040329951956</v>
       </c>
       <c r="W96">
-        <v>0.2139112671881645</v>
+        <v>0.2141416749019733</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3315269116054087</v>
+        <v>0.3280371546411412</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2232800443045851</v>
+        <v>0.2251800443045851</v>
       </c>
       <c r="C97">
-        <v>-2951.434592042634</v>
+        <v>-2989.232471497332</v>
       </c>
       <c r="D97">
-        <v>295.2104079573666</v>
+        <v>292.0835285026677</v>
       </c>
       <c r="E97">
-        <v>2010.845</v>
+        <v>2045.516</v>
       </c>
       <c r="F97">
-        <v>3293.745</v>
+        <v>3328.416</v>
       </c>
       <c r="G97">
         <v>47.1</v>
@@ -9247,37 +9247,37 @@
         <v>254.775</v>
       </c>
       <c r="M97">
-        <v>776.6650710000001</v>
+        <v>784.8404928000001</v>
       </c>
       <c r="N97">
-        <v>-521.8900710000001</v>
+        <v>-530.0654928000001</v>
       </c>
       <c r="O97">
-        <v>-146.1292198800001</v>
+        <v>-148.4183379840001</v>
       </c>
       <c r="P97">
-        <v>-375.7608511200001</v>
+        <v>-381.6471548160001</v>
       </c>
       <c r="Q97">
-        <v>-235.1608511200001</v>
+        <v>-241.0471548160001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.3969090629542102</v>
+        <v>0.484686328692763</v>
       </c>
       <c r="T97">
-        <v>8.108754340743886</v>
+        <v>10.13594292592986</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09185040329951956</v>
+        <v>0.09089362826514956</v>
       </c>
       <c r="W97">
-        <v>0.2141416749019733</v>
+        <v>0.2143672824550777</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3280371546411412</v>
+        <v>0.3246201009469627</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2251800443045851</v>
+        <v>0.2270800443045851</v>
       </c>
       <c r="C98">
-        <v>-2989.232471497332</v>
+        <v>-3026.96480517189</v>
       </c>
       <c r="D98">
-        <v>292.0835285026677</v>
+        <v>289.0221948281096</v>
       </c>
       <c r="E98">
-        <v>2045.516</v>
+        <v>2080.187</v>
       </c>
       <c r="F98">
-        <v>3328.416</v>
+        <v>3363.087</v>
       </c>
       <c r="G98">
         <v>47.1</v>
@@ -9329,37 +9329,37 @@
         <v>254.775</v>
       </c>
       <c r="M98">
-        <v>784.8404928</v>
+        <v>793.0159146</v>
       </c>
       <c r="N98">
-        <v>-530.0654928</v>
+        <v>-538.2409146</v>
       </c>
       <c r="O98">
-        <v>-148.418337984</v>
+        <v>-150.707456088</v>
       </c>
       <c r="P98">
-        <v>-381.647154816</v>
+        <v>-387.533458512</v>
       </c>
       <c r="Q98">
-        <v>-241.047154816</v>
+        <v>-246.933458512</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.4846863286927618</v>
+        <v>0.630981771590349</v>
       </c>
       <c r="T98">
-        <v>10.13594292592984</v>
+        <v>13.51459056790645</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09089362826514957</v>
+        <v>0.08995658055107587</v>
       </c>
       <c r="W98">
-        <v>0.2143672824550777</v>
+        <v>0.2145882383060563</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3246201009469627</v>
+        <v>0.3212735019681281</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2270800443045851</v>
+        <v>0.2289800443045851</v>
       </c>
       <c r="C99">
-        <v>-3026.96480517189</v>
+        <v>-3064.63363264954</v>
       </c>
       <c r="D99">
-        <v>289.0221948281096</v>
+        <v>286.0243673504597</v>
       </c>
       <c r="E99">
-        <v>2080.187</v>
+        <v>2114.858</v>
       </c>
       <c r="F99">
-        <v>3363.087</v>
+        <v>3397.758</v>
       </c>
       <c r="G99">
         <v>47.1</v>
@@ -9411,37 +9411,37 @@
         <v>254.775</v>
       </c>
       <c r="M99">
-        <v>793.0159146</v>
+        <v>801.1913364</v>
       </c>
       <c r="N99">
-        <v>-538.2409146</v>
+        <v>-546.4163364</v>
       </c>
       <c r="O99">
-        <v>-150.707456088</v>
+        <v>-152.996574192</v>
       </c>
       <c r="P99">
-        <v>-387.533458512</v>
+        <v>-393.419762208</v>
       </c>
       <c r="Q99">
-        <v>-246.933458512</v>
+        <v>-252.819762208</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.630981771590349</v>
+        <v>0.9235726573855234</v>
       </c>
       <c r="T99">
-        <v>13.51459056790645</v>
+        <v>20.27188585185967</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08995658055107587</v>
+        <v>0.08903865625973836</v>
       </c>
       <c r="W99">
-        <v>0.2145882383060563</v>
+        <v>0.2148046848539537</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3212735019681281</v>
+        <v>0.317995200927637</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2289800443045851</v>
+        <v>0.2308800443045851</v>
       </c>
       <c r="C100">
-        <v>-3064.63363264954</v>
+        <v>-3102.240909761467</v>
       </c>
       <c r="D100">
-        <v>286.0243673504597</v>
+        <v>283.088090238533</v>
       </c>
       <c r="E100">
-        <v>2114.858</v>
+        <v>2149.529</v>
       </c>
       <c r="F100">
-        <v>3397.758</v>
+        <v>3432.429</v>
       </c>
       <c r="G100">
         <v>47.1</v>
@@ -9493,37 +9493,37 @@
         <v>254.775</v>
       </c>
       <c r="M100">
-        <v>801.1913364</v>
+        <v>809.3667582</v>
       </c>
       <c r="N100">
-        <v>-546.4163364</v>
+        <v>-554.5917582000001</v>
       </c>
       <c r="O100">
-        <v>-152.996574192</v>
+        <v>-155.285692296</v>
       </c>
       <c r="P100">
-        <v>-393.419762208</v>
+        <v>-399.306065904</v>
       </c>
       <c r="Q100">
-        <v>-252.819762208</v>
+        <v>-258.7060659040001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>0.9235726573855234</v>
+        <v>1.801345314771047</v>
       </c>
       <c r="T100">
-        <v>20.27188585185967</v>
+        <v>40.54377170371934</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08903865625973836</v>
+        <v>0.08813927589347838</v>
       </c>
       <c r="W100">
-        <v>0.2148046848539537</v>
+        <v>0.2150167587443178</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.317995200927637</v>
+        <v>0.3147831281909942</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2308800443045851</v>
-      </c>
-      <c r="C101">
-        <v>-3102.240909761467</v>
-      </c>
-      <c r="D101">
-        <v>283.088090238533</v>
-      </c>
-      <c r="E101">
-        <v>2149.529</v>
-      </c>
-      <c r="F101">
-        <v>3432.429</v>
-      </c>
-      <c r="G101">
-        <v>47.1</v>
-      </c>
-      <c r="H101">
-        <v>2184.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>395.375</v>
-      </c>
-      <c r="K101">
-        <v>140.6</v>
-      </c>
-      <c r="L101">
-        <v>254.775</v>
-      </c>
-      <c r="M101">
-        <v>809.3667582</v>
-      </c>
-      <c r="N101">
-        <v>-554.5917582000001</v>
-      </c>
-      <c r="O101">
-        <v>-155.285692296</v>
-      </c>
-      <c r="P101">
-        <v>-399.306065904</v>
-      </c>
-      <c r="Q101">
-        <v>-258.7060659040001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>1.801345314771047</v>
-      </c>
-      <c r="T101">
-        <v>40.54377170371934</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08813927589347838</v>
-      </c>
-      <c r="W101">
-        <v>0.2150167587443178</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3147831281909942</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
